--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\BCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD4CDBB5-DCCA-42CD-B7CF-80F0AB20833C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999D7867-60B9-40C5-9EDF-D7A44AA77B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12645" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="151">
   <si>
     <t>Year</t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>Battery Energy Cost per Unit Capacity : NDC</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1655,7 @@
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1971,7 +1968,6 @@
     <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4614,30 +4610,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="67.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="142">
-        <v>45531</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4645,57 +4635,57 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>2014</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>2013</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>12</v>
       </c>
@@ -4911,19 +4901,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="165" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="M1" s="3" t="s">
         <v>68</v>
       </c>
@@ -5053,12 +5043,12 @@
     </row>
     <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="167" t="s">
+      <c r="L4" s="166" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L5" s="168"/>
+      <c r="L5" s="167"/>
     </row>
     <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
@@ -5090,23 +5080,23 @@
       <c r="B7" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="162" t="s">
+      <c r="C7" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="162"/>
-      <c r="K7" s="162"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
-      <c r="N7" s="162"/>
-      <c r="O7" s="162"/>
-      <c r="P7" s="162"/>
-      <c r="Q7" s="162"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5124,43 +5114,43 @@
     </row>
     <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="168" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="170" t="s">
+      <c r="D9" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="171"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="173">
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="172">
         <v>2021</v>
       </c>
-      <c r="H9" s="174"/>
-      <c r="I9" s="174"/>
-      <c r="J9" s="174"/>
-      <c r="K9" s="175"/>
-      <c r="L9" s="175"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="174"/>
+      <c r="L9" s="174"/>
     </row>
     <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="169"/>
+      <c r="B10" s="168"/>
       <c r="D10" s="53" t="s">
         <v>76</v>
       </c>
       <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="169"/>
-      <c r="D11" s="176" t="s">
+      <c r="B11" s="168"/>
+      <c r="D11" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="177"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="177"/>
-      <c r="H11" s="177"/>
-      <c r="I11" s="177"/>
-      <c r="J11" s="177"/>
-      <c r="K11" s="177"/>
-      <c r="L11" s="177"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
@@ -5168,18 +5158,18 @@
       <c r="AA11" s="55"/>
     </row>
     <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="169"/>
-      <c r="D12" s="178" t="s">
+      <c r="B12" s="168"/>
+      <c r="D12" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="179"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="179"/>
-      <c r="I12" s="179"/>
-      <c r="J12" s="179"/>
-      <c r="K12" s="179"/>
-      <c r="L12" s="180"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="178"/>
+      <c r="H12" s="178"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="179"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5188,16 +5178,16 @@
       <c r="AA12" s="55"/>
     </row>
     <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="169"/>
-      <c r="D13" s="181"/>
-      <c r="E13" s="182"/>
-      <c r="F13" s="182"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="182"/>
-      <c r="I13" s="182"/>
-      <c r="J13" s="182"/>
-      <c r="K13" s="182"/>
-      <c r="L13" s="183"/>
+      <c r="B13" s="168"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="182"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
@@ -5205,49 +5195,49 @@
       <c r="AA13" s="55"/>
     </row>
     <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="169"/>
+      <c r="B14" s="168"/>
     </row>
     <row r="15" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B15" s="169"/>
-      <c r="C15" s="184" t="s">
+      <c r="B15" s="168"/>
+      <c r="C15" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
-      <c r="F15" s="184"/>
-      <c r="G15" s="184"/>
-      <c r="H15" s="184"/>
-      <c r="I15" s="184"/>
-      <c r="J15" s="184"/>
-      <c r="K15" s="184"/>
-      <c r="L15" s="184"/>
-      <c r="M15" s="184"/>
-      <c r="N15" s="184"/>
-      <c r="O15" s="184"/>
-      <c r="P15" s="184"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
       <c r="Q15" s="57"/>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B16" s="169"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="184"/>
-      <c r="L16" s="184"/>
-      <c r="M16" s="184"/>
-      <c r="N16" s="184"/>
-      <c r="O16" s="184"/>
-      <c r="P16" s="184"/>
+      <c r="B16" s="168"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="183"/>
     </row>
     <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="169"/>
+      <c r="B17" s="168"/>
       <c r="C17" s="58"/>
-      <c r="D17" s="159" t="s">
+      <c r="D17" s="158" t="s">
         <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -5255,9 +5245,9 @@
       </c>
     </row>
     <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="169"/>
+      <c r="B18" s="168"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="160"/>
+      <c r="D18" s="159"/>
       <c r="F18" s="1">
         <v>2021</v>
       </c>
@@ -5350,9 +5340,9 @@
       </c>
     </row>
     <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="169"/>
+      <c r="B19" s="168"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="160"/>
+      <c r="D19" s="159"/>
       <c r="E19" t="s">
         <v>82</v>
       </c>
@@ -5448,9 +5438,9 @@
       </c>
     </row>
     <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="169"/>
+      <c r="B20" s="168"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="161"/>
+      <c r="D20" s="160"/>
       <c r="E20" t="s">
         <v>83</v>
       </c>
@@ -5546,9 +5536,9 @@
       </c>
     </row>
     <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="169"/>
+      <c r="B21" s="168"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="161"/>
+      <c r="D21" s="160"/>
       <c r="E21" t="s">
         <v>84</v>
       </c>
@@ -5644,9 +5634,9 @@
       </c>
     </row>
     <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="169"/>
+      <c r="B22" s="168"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="161"/>
+      <c r="D22" s="160"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5679,18 +5669,18 @@
       <c r="AI22" s="5"/>
     </row>
     <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="169"/>
+      <c r="B23" s="168"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="161"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F23" s="60"/>
     </row>
     <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="169"/>
+      <c r="B24" s="168"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="161"/>
+      <c r="D24" s="160"/>
       <c r="F24" s="1">
         <v>2021</v>
       </c>
@@ -5783,9 +5773,9 @@
       </c>
     </row>
     <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="169"/>
+      <c r="B25" s="168"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="161"/>
+      <c r="D25" s="160"/>
       <c r="E25" t="s">
         <v>82</v>
       </c>
@@ -5881,9 +5871,9 @@
       </c>
     </row>
     <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="169"/>
+      <c r="B26" s="168"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="161"/>
+      <c r="D26" s="160"/>
       <c r="E26" t="s">
         <v>83</v>
       </c>
@@ -5979,9 +5969,9 @@
       </c>
     </row>
     <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="169"/>
+      <c r="B27" s="168"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="161"/>
+      <c r="D27" s="160"/>
       <c r="E27" t="s">
         <v>84</v>
       </c>
@@ -6077,7 +6067,7 @@
       </c>
     </row>
     <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="169"/>
+      <c r="B28" s="168"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6115,7 +6105,7 @@
       <c r="AM28" s="5"/>
     </row>
     <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="169"/>
+      <c r="B29" s="168"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
@@ -6157,7 +6147,7 @@
       <c r="AM29" s="5"/>
     </row>
     <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="169"/>
+      <c r="B30" s="168"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6197,9 +6187,9 @@
       <c r="AM30" s="5"/>
     </row>
     <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="169"/>
+      <c r="B31" s="168"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="160" t="s">
+      <c r="D31" s="159" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="61" t="s">
@@ -6249,9 +6239,9 @@
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="169"/>
+      <c r="B32" s="168"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="160"/>
+      <c r="D32" s="159"/>
       <c r="E32" s="66" t="s">
         <v>93</v>
       </c>
@@ -6299,9 +6289,9 @@
       <c r="AM32" s="5"/>
     </row>
     <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="169"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="160"/>
+      <c r="D33" s="159"/>
       <c r="E33" s="69" t="s">
         <v>98</v>
       </c>
@@ -6349,9 +6339,9 @@
       <c r="AM33" s="5"/>
     </row>
     <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="169"/>
+      <c r="B34" s="168"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="160"/>
+      <c r="D34" s="159"/>
       <c r="E34" s="72" t="s">
         <v>100</v>
       </c>
@@ -6399,9 +6389,9 @@
       <c r="AM34" s="5"/>
     </row>
     <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="169"/>
+      <c r="B35" s="168"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="160"/>
+      <c r="D35" s="159"/>
       <c r="E35" s="69" t="s">
         <v>102</v>
       </c>
@@ -6449,9 +6439,9 @@
       <c r="AM35" s="5"/>
     </row>
     <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="169"/>
+      <c r="B36" s="168"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="160"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="75" t="s">
         <v>104</v>
       </c>
@@ -6538,23 +6528,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="162" t="s">
+      <c r="C38" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="162"/>
-      <c r="N38" s="162"/>
-      <c r="O38" s="162"/>
-      <c r="P38" s="162"/>
-      <c r="Q38" s="162"/>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+      <c r="P38" s="161"/>
+      <c r="Q38" s="161"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6687,10 +6677,10 @@
       </c>
     </row>
     <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="164" t="s">
+      <c r="B43" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="159" t="s">
+      <c r="D43" s="158" t="s">
         <v>109</v>
       </c>
       <c r="E43" s="79" t="s">
@@ -6792,8 +6782,8 @@
       </c>
     </row>
     <row r="44" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B44" s="164"/>
-      <c r="D44" s="160"/>
+      <c r="B44" s="163"/>
+      <c r="D44" s="159"/>
       <c r="E44" s="82" t="s">
         <v>93</v>
       </c>
@@ -6893,8 +6883,8 @@
       </c>
     </row>
     <row r="45" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B45" s="164"/>
-      <c r="D45" s="160"/>
+      <c r="B45" s="163"/>
+      <c r="D45" s="159"/>
       <c r="E45" s="83" t="s">
         <v>93</v>
       </c>
@@ -6994,8 +6984,8 @@
       </c>
     </row>
     <row r="46" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B46" s="164"/>
-      <c r="D46" s="161"/>
+      <c r="B46" s="163"/>
+      <c r="D46" s="160"/>
       <c r="E46" s="79" t="s">
         <v>98</v>
       </c>
@@ -7128,8 +7118,8 @@
       <c r="BV46" s="5"/>
     </row>
     <row r="47" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B47" s="164"/>
-      <c r="D47" s="161"/>
+      <c r="B47" s="163"/>
+      <c r="D47" s="160"/>
       <c r="E47" s="79" t="s">
         <v>98</v>
       </c>
@@ -7262,8 +7252,8 @@
       <c r="BV47" s="5"/>
     </row>
     <row r="48" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B48" s="164"/>
-      <c r="D48" s="161"/>
+      <c r="B48" s="163"/>
+      <c r="D48" s="160"/>
       <c r="E48" s="79" t="s">
         <v>98</v>
       </c>
@@ -7396,8 +7386,8 @@
       <c r="BV48" s="5"/>
     </row>
     <row r="49" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B49" s="164"/>
-      <c r="D49" s="161"/>
+      <c r="B49" s="163"/>
+      <c r="D49" s="160"/>
       <c r="E49" s="79" t="s">
         <v>100</v>
       </c>
@@ -7530,8 +7520,8 @@
       <c r="BV49" s="5"/>
     </row>
     <row r="50" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B50" s="164"/>
-      <c r="D50" s="161"/>
+      <c r="B50" s="163"/>
+      <c r="D50" s="160"/>
       <c r="E50" s="79" t="s">
         <v>100</v>
       </c>
@@ -7664,8 +7654,8 @@
       <c r="BV50" s="5"/>
     </row>
     <row r="51" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B51" s="164"/>
-      <c r="D51" s="161"/>
+      <c r="B51" s="163"/>
+      <c r="D51" s="160"/>
       <c r="E51" s="79" t="s">
         <v>100</v>
       </c>
@@ -7798,8 +7788,8 @@
       <c r="BV51" s="5"/>
     </row>
     <row r="52" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B52" s="164"/>
-      <c r="D52" s="161"/>
+      <c r="B52" s="163"/>
+      <c r="D52" s="160"/>
       <c r="E52" s="79" t="s">
         <v>102</v>
       </c>
@@ -7932,8 +7922,8 @@
       <c r="BV52" s="5"/>
     </row>
     <row r="53" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B53" s="164"/>
-      <c r="D53" s="161"/>
+      <c r="B53" s="163"/>
+      <c r="D53" s="160"/>
       <c r="E53" s="79" t="s">
         <v>102</v>
       </c>
@@ -8066,8 +8056,8 @@
       <c r="BV53" s="5"/>
     </row>
     <row r="54" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B54" s="164"/>
-      <c r="D54" s="161"/>
+      <c r="B54" s="163"/>
+      <c r="D54" s="160"/>
       <c r="E54" s="79" t="s">
         <v>102</v>
       </c>
@@ -8200,8 +8190,8 @@
       <c r="BV54" s="5"/>
     </row>
     <row r="55" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B55" s="164"/>
-      <c r="D55" s="161"/>
+      <c r="B55" s="163"/>
+      <c r="D55" s="160"/>
       <c r="E55" s="79" t="s">
         <v>104</v>
       </c>
@@ -8334,8 +8324,8 @@
       <c r="BV55" s="5"/>
     </row>
     <row r="56" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B56" s="164"/>
-      <c r="D56" s="161"/>
+      <c r="B56" s="163"/>
+      <c r="D56" s="160"/>
       <c r="E56" s="79" t="s">
         <v>104</v>
       </c>
@@ -8468,8 +8458,8 @@
       <c r="BV56" s="5"/>
     </row>
     <row r="57" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B57" s="164"/>
-      <c r="D57" s="161"/>
+      <c r="B57" s="163"/>
+      <c r="D57" s="160"/>
       <c r="E57" s="79" t="s">
         <v>104</v>
       </c>
@@ -8602,7 +8592,7 @@
       <c r="BV57" s="5"/>
     </row>
     <row r="58" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B58" s="164"/>
+      <c r="B58" s="163"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8671,7 +8661,7 @@
       <c r="BV58" s="5"/>
     </row>
     <row r="59" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B59" s="164"/>
+      <c r="B59" s="163"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8740,7 +8730,7 @@
       <c r="BV59" s="5"/>
     </row>
     <row r="60" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B60" s="164"/>
+      <c r="B60" s="163"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8809,7 +8799,7 @@
       <c r="BV60" s="5"/>
     </row>
     <row r="61" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B61" s="164"/>
+      <c r="B61" s="163"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
@@ -8905,8 +8895,8 @@
       </c>
     </row>
     <row r="62" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B62" s="164"/>
-      <c r="D62" s="159" t="s">
+      <c r="B62" s="163"/>
+      <c r="D62" s="158" t="s">
         <v>110</v>
       </c>
       <c r="E62" s="79" t="s">
@@ -9008,8 +8998,8 @@
       </c>
     </row>
     <row r="63" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B63" s="164"/>
-      <c r="D63" s="160"/>
+      <c r="B63" s="163"/>
+      <c r="D63" s="159"/>
       <c r="E63" s="82" t="s">
         <v>93</v>
       </c>
@@ -9109,8 +9099,8 @@
       </c>
     </row>
     <row r="64" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B64" s="164"/>
-      <c r="D64" s="160"/>
+      <c r="B64" s="163"/>
+      <c r="D64" s="159"/>
       <c r="E64" s="83" t="s">
         <v>93</v>
       </c>
@@ -9210,8 +9200,8 @@
       </c>
     </row>
     <row r="65" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B65" s="164"/>
-      <c r="D65" s="161"/>
+      <c r="B65" s="163"/>
+      <c r="D65" s="160"/>
       <c r="E65" s="79" t="s">
         <v>98</v>
       </c>
@@ -9311,8 +9301,8 @@
       </c>
     </row>
     <row r="66" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B66" s="164"/>
-      <c r="D66" s="161"/>
+      <c r="B66" s="163"/>
+      <c r="D66" s="160"/>
       <c r="E66" s="79" t="s">
         <v>98</v>
       </c>
@@ -9412,8 +9402,8 @@
       </c>
     </row>
     <row r="67" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B67" s="164"/>
-      <c r="D67" s="161"/>
+      <c r="B67" s="163"/>
+      <c r="D67" s="160"/>
       <c r="E67" s="79" t="s">
         <v>98</v>
       </c>
@@ -9513,8 +9503,8 @@
       </c>
     </row>
     <row r="68" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B68" s="164"/>
-      <c r="D68" s="161"/>
+      <c r="B68" s="163"/>
+      <c r="D68" s="160"/>
       <c r="E68" s="79" t="s">
         <v>100</v>
       </c>
@@ -9614,8 +9604,8 @@
       </c>
     </row>
     <row r="69" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B69" s="164"/>
-      <c r="D69" s="161"/>
+      <c r="B69" s="163"/>
+      <c r="D69" s="160"/>
       <c r="E69" s="79" t="s">
         <v>100</v>
       </c>
@@ -9715,8 +9705,8 @@
       </c>
     </row>
     <row r="70" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B70" s="164"/>
-      <c r="D70" s="161"/>
+      <c r="B70" s="163"/>
+      <c r="D70" s="160"/>
       <c r="E70" s="79" t="s">
         <v>100</v>
       </c>
@@ -9816,8 +9806,8 @@
       </c>
     </row>
     <row r="71" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B71" s="164"/>
-      <c r="D71" s="161"/>
+      <c r="B71" s="163"/>
+      <c r="D71" s="160"/>
       <c r="E71" s="79" t="s">
         <v>102</v>
       </c>
@@ -9950,8 +9940,8 @@
       <c r="BV71" s="5"/>
     </row>
     <row r="72" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B72" s="164"/>
-      <c r="D72" s="161"/>
+      <c r="B72" s="163"/>
+      <c r="D72" s="160"/>
       <c r="E72" s="79" t="s">
         <v>102</v>
       </c>
@@ -10084,8 +10074,8 @@
       <c r="BV72" s="5"/>
     </row>
     <row r="73" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B73" s="164"/>
-      <c r="D73" s="161"/>
+      <c r="B73" s="163"/>
+      <c r="D73" s="160"/>
       <c r="E73" s="79" t="s">
         <v>102</v>
       </c>
@@ -10218,8 +10208,8 @@
       <c r="BV73" s="5"/>
     </row>
     <row r="74" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B74" s="164"/>
-      <c r="D74" s="161"/>
+      <c r="B74" s="163"/>
+      <c r="D74" s="160"/>
       <c r="E74" s="79" t="s">
         <v>104</v>
       </c>
@@ -10352,8 +10342,8 @@
       <c r="BV74" s="5"/>
     </row>
     <row r="75" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B75" s="164"/>
-      <c r="D75" s="161"/>
+      <c r="B75" s="163"/>
+      <c r="D75" s="160"/>
       <c r="E75" s="79" t="s">
         <v>104</v>
       </c>
@@ -10486,8 +10476,8 @@
       <c r="BV75" s="5"/>
     </row>
     <row r="76" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B76" s="164"/>
-      <c r="D76" s="161"/>
+      <c r="B76" s="163"/>
+      <c r="D76" s="160"/>
       <c r="E76" s="79" t="s">
         <v>104</v>
       </c>
@@ -10620,13 +10610,13 @@
       <c r="BV76" s="5"/>
     </row>
     <row r="77" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B77" s="164"/>
+      <c r="B77" s="163"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
     <row r="78" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B78" s="164"/>
+      <c r="B78" s="163"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
@@ -10722,8 +10712,8 @@
       </c>
     </row>
     <row r="79" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B79" s="164"/>
-      <c r="D79" s="159" t="s">
+      <c r="B79" s="163"/>
+      <c r="D79" s="158" t="s">
         <v>111</v>
       </c>
       <c r="E79" s="79" t="s">
@@ -10825,8 +10815,8 @@
       <c r="AO79" s="1"/>
     </row>
     <row r="80" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B80" s="164"/>
-      <c r="D80" s="160"/>
+      <c r="B80" s="163"/>
+      <c r="D80" s="159"/>
       <c r="E80" s="82" t="s">
         <v>93</v>
       </c>
@@ -10926,8 +10916,8 @@
       <c r="AO80" s="1"/>
     </row>
     <row r="81" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B81" s="164"/>
-      <c r="D81" s="160"/>
+      <c r="B81" s="163"/>
+      <c r="D81" s="159"/>
       <c r="E81" s="83" t="s">
         <v>93</v>
       </c>
@@ -11027,8 +11017,8 @@
       <c r="AO81" s="1"/>
     </row>
     <row r="82" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B82" s="165"/>
-      <c r="D82" s="161"/>
+      <c r="B82" s="164"/>
+      <c r="D82" s="160"/>
       <c r="E82" s="79" t="s">
         <v>98</v>
       </c>
@@ -11127,8 +11117,8 @@
       </c>
     </row>
     <row r="83" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B83" s="165"/>
-      <c r="D83" s="161"/>
+      <c r="B83" s="164"/>
+      <c r="D83" s="160"/>
       <c r="E83" s="79" t="s">
         <v>98</v>
       </c>
@@ -11227,8 +11217,8 @@
       </c>
     </row>
     <row r="84" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B84" s="165"/>
-      <c r="D84" s="161"/>
+      <c r="B84" s="164"/>
+      <c r="D84" s="160"/>
       <c r="E84" s="79" t="s">
         <v>98</v>
       </c>
@@ -11329,8 +11319,8 @@
       <c r="AL84" s="5"/>
     </row>
     <row r="85" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B85" s="165"/>
-      <c r="D85" s="161"/>
+      <c r="B85" s="164"/>
+      <c r="D85" s="160"/>
       <c r="E85" s="79" t="s">
         <v>100</v>
       </c>
@@ -11431,8 +11421,8 @@
       <c r="AL85" s="5"/>
     </row>
     <row r="86" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B86" s="165"/>
-      <c r="D86" s="161"/>
+      <c r="B86" s="164"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="79" t="s">
         <v>100</v>
       </c>
@@ -11533,8 +11523,8 @@
       <c r="AL86" s="5"/>
     </row>
     <row r="87" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B87" s="165"/>
-      <c r="D87" s="161"/>
+      <c r="B87" s="164"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="79" t="s">
         <v>100</v>
       </c>
@@ -11635,8 +11625,8 @@
       <c r="AL87" s="5"/>
     </row>
     <row r="88" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B88" s="165"/>
-      <c r="D88" s="161"/>
+      <c r="B88" s="164"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="79" t="s">
         <v>102</v>
       </c>
@@ -11737,8 +11727,8 @@
       <c r="AL88" s="5"/>
     </row>
     <row r="89" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B89" s="165"/>
-      <c r="D89" s="161"/>
+      <c r="B89" s="164"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="79" t="s">
         <v>102</v>
       </c>
@@ -11839,8 +11829,8 @@
       <c r="AL89" s="5"/>
     </row>
     <row r="90" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B90" s="165"/>
-      <c r="D90" s="161"/>
+      <c r="B90" s="164"/>
+      <c r="D90" s="160"/>
       <c r="E90" s="79" t="s">
         <v>102</v>
       </c>
@@ -11941,8 +11931,8 @@
       <c r="AL90" s="5"/>
     </row>
     <row r="91" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B91" s="165"/>
-      <c r="D91" s="161"/>
+      <c r="B91" s="164"/>
+      <c r="D91" s="160"/>
       <c r="E91" s="79" t="s">
         <v>104</v>
       </c>
@@ -12043,8 +12033,8 @@
       <c r="AL91" s="5"/>
     </row>
     <row r="92" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B92" s="165"/>
-      <c r="D92" s="161"/>
+      <c r="B92" s="164"/>
+      <c r="D92" s="160"/>
       <c r="E92" s="79" t="s">
         <v>104</v>
       </c>
@@ -12145,8 +12135,8 @@
       <c r="AL92" s="5"/>
     </row>
     <row r="93" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B93" s="165"/>
-      <c r="D93" s="161"/>
+      <c r="B93" s="164"/>
+      <c r="D93" s="160"/>
       <c r="E93" s="79" t="s">
         <v>104</v>
       </c>
@@ -12247,10 +12237,10 @@
       <c r="AL93" s="5"/>
     </row>
     <row r="94" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B94" s="165"/>
+      <c r="B94" s="164"/>
     </row>
     <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="165"/>
+      <c r="B95" s="164"/>
       <c r="G95" s="1">
         <v>2021</v>
       </c>
@@ -12343,8 +12333,8 @@
       </c>
     </row>
     <row r="96" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B96" s="165"/>
-      <c r="D96" s="159" t="s">
+      <c r="B96" s="164"/>
+      <c r="D96" s="158" t="s">
         <v>112</v>
       </c>
       <c r="E96" s="79" t="s">
@@ -12445,8 +12435,8 @@
       </c>
     </row>
     <row r="97" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B97" s="165"/>
-      <c r="D97" s="160"/>
+      <c r="B97" s="164"/>
+      <c r="D97" s="159"/>
       <c r="E97" s="82" t="s">
         <v>93</v>
       </c>
@@ -12545,8 +12535,8 @@
       </c>
     </row>
     <row r="98" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B98" s="165"/>
-      <c r="D98" s="160"/>
+      <c r="B98" s="164"/>
+      <c r="D98" s="159"/>
       <c r="E98" s="83" t="s">
         <v>93</v>
       </c>
@@ -12645,8 +12635,8 @@
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B99" s="165"/>
-      <c r="D99" s="161"/>
+      <c r="B99" s="164"/>
+      <c r="D99" s="160"/>
       <c r="E99" s="79" t="s">
         <v>98</v>
       </c>
@@ -12745,8 +12735,8 @@
       </c>
     </row>
     <row r="100" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B100" s="165"/>
-      <c r="D100" s="161"/>
+      <c r="B100" s="164"/>
+      <c r="D100" s="160"/>
       <c r="E100" s="79" t="s">
         <v>98</v>
       </c>
@@ -12845,8 +12835,8 @@
       </c>
     </row>
     <row r="101" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B101" s="165"/>
-      <c r="D101" s="161"/>
+      <c r="B101" s="164"/>
+      <c r="D101" s="160"/>
       <c r="E101" s="79" t="s">
         <v>98</v>
       </c>
@@ -12945,8 +12935,8 @@
       </c>
     </row>
     <row r="102" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B102" s="165"/>
-      <c r="D102" s="161"/>
+      <c r="B102" s="164"/>
+      <c r="D102" s="160"/>
       <c r="E102" s="79" t="s">
         <v>100</v>
       </c>
@@ -13045,8 +13035,8 @@
       </c>
     </row>
     <row r="103" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B103" s="165"/>
-      <c r="D103" s="161"/>
+      <c r="B103" s="164"/>
+      <c r="D103" s="160"/>
       <c r="E103" s="79" t="s">
         <v>100</v>
       </c>
@@ -13145,8 +13135,8 @@
       </c>
     </row>
     <row r="104" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B104" s="165"/>
-      <c r="D104" s="161"/>
+      <c r="B104" s="164"/>
+      <c r="D104" s="160"/>
       <c r="E104" s="79" t="s">
         <v>100</v>
       </c>
@@ -13245,8 +13235,8 @@
       </c>
     </row>
     <row r="105" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B105" s="165"/>
-      <c r="D105" s="161"/>
+      <c r="B105" s="164"/>
+      <c r="D105" s="160"/>
       <c r="E105" s="79" t="s">
         <v>102</v>
       </c>
@@ -13345,8 +13335,8 @@
       </c>
     </row>
     <row r="106" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B106" s="165"/>
-      <c r="D106" s="161"/>
+      <c r="B106" s="164"/>
+      <c r="D106" s="160"/>
       <c r="E106" s="79" t="s">
         <v>102</v>
       </c>
@@ -13445,8 +13435,8 @@
       </c>
     </row>
     <row r="107" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B107" s="165"/>
-      <c r="D107" s="161"/>
+      <c r="B107" s="164"/>
+      <c r="D107" s="160"/>
       <c r="E107" s="79" t="s">
         <v>102</v>
       </c>
@@ -13545,8 +13535,8 @@
       </c>
     </row>
     <row r="108" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B108" s="165"/>
-      <c r="D108" s="161"/>
+      <c r="B108" s="164"/>
+      <c r="D108" s="160"/>
       <c r="E108" s="79" t="s">
         <v>104</v>
       </c>
@@ -13645,8 +13635,8 @@
       </c>
     </row>
     <row r="109" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B109" s="165"/>
-      <c r="D109" s="161"/>
+      <c r="B109" s="164"/>
+      <c r="D109" s="160"/>
       <c r="E109" s="79" t="s">
         <v>104</v>
       </c>
@@ -13745,8 +13735,8 @@
       </c>
     </row>
     <row r="110" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B110" s="165"/>
-      <c r="D110" s="161"/>
+      <c r="B110" s="164"/>
+      <c r="D110" s="160"/>
       <c r="E110" s="79" t="s">
         <v>104</v>
       </c>
@@ -13845,10 +13835,10 @@
       </c>
     </row>
     <row r="111" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B111" s="165"/>
+      <c r="B111" s="164"/>
     </row>
     <row r="112" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B112" s="165"/>
+      <c r="B112" s="164"/>
       <c r="G112" s="1">
         <v>2021</v>
       </c>
@@ -13941,8 +13931,8 @@
       </c>
     </row>
     <row r="113" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B113" s="165"/>
-      <c r="D113" s="159" t="s">
+      <c r="B113" s="164"/>
+      <c r="D113" s="158" t="s">
         <v>113</v>
       </c>
       <c r="E113" s="79" t="s">
@@ -14044,8 +14034,8 @@
       </c>
     </row>
     <row r="114" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B114" s="165"/>
-      <c r="D114" s="160"/>
+      <c r="B114" s="164"/>
+      <c r="D114" s="159"/>
       <c r="E114" s="82" t="s">
         <v>93</v>
       </c>
@@ -14145,8 +14135,8 @@
       </c>
     </row>
     <row r="115" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B115" s="165"/>
-      <c r="D115" s="160"/>
+      <c r="B115" s="164"/>
+      <c r="D115" s="159"/>
       <c r="E115" s="83" t="s">
         <v>93</v>
       </c>
@@ -14246,8 +14236,8 @@
       </c>
     </row>
     <row r="116" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B116" s="165"/>
-      <c r="D116" s="161"/>
+      <c r="B116" s="164"/>
+      <c r="D116" s="160"/>
       <c r="E116" s="79" t="s">
         <v>98</v>
       </c>
@@ -14347,8 +14337,8 @@
       </c>
     </row>
     <row r="117" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B117" s="165"/>
-      <c r="D117" s="161"/>
+      <c r="B117" s="164"/>
+      <c r="D117" s="160"/>
       <c r="E117" s="79" t="s">
         <v>98</v>
       </c>
@@ -14448,8 +14438,8 @@
       </c>
     </row>
     <row r="118" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B118" s="165"/>
-      <c r="D118" s="161"/>
+      <c r="B118" s="164"/>
+      <c r="D118" s="160"/>
       <c r="E118" s="79" t="s">
         <v>98</v>
       </c>
@@ -14549,8 +14539,8 @@
       </c>
     </row>
     <row r="119" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B119" s="165"/>
-      <c r="D119" s="161"/>
+      <c r="B119" s="164"/>
+      <c r="D119" s="160"/>
       <c r="E119" s="79" t="s">
         <v>100</v>
       </c>
@@ -14650,8 +14640,8 @@
       </c>
     </row>
     <row r="120" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B120" s="165"/>
-      <c r="D120" s="161"/>
+      <c r="B120" s="164"/>
+      <c r="D120" s="160"/>
       <c r="E120" s="79" t="s">
         <v>100</v>
       </c>
@@ -14751,8 +14741,8 @@
       </c>
     </row>
     <row r="121" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B121" s="165"/>
-      <c r="D121" s="161"/>
+      <c r="B121" s="164"/>
+      <c r="D121" s="160"/>
       <c r="E121" s="79" t="s">
         <v>100</v>
       </c>
@@ -14852,8 +14842,8 @@
       </c>
     </row>
     <row r="122" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B122" s="165"/>
-      <c r="D122" s="161"/>
+      <c r="B122" s="164"/>
+      <c r="D122" s="160"/>
       <c r="E122" s="79" t="s">
         <v>102</v>
       </c>
@@ -14953,8 +14943,8 @@
       </c>
     </row>
     <row r="123" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B123" s="165"/>
-      <c r="D123" s="161"/>
+      <c r="B123" s="164"/>
+      <c r="D123" s="160"/>
       <c r="E123" s="79" t="s">
         <v>102</v>
       </c>
@@ -15054,8 +15044,8 @@
       </c>
     </row>
     <row r="124" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B124" s="165"/>
-      <c r="D124" s="161"/>
+      <c r="B124" s="164"/>
+      <c r="D124" s="160"/>
       <c r="E124" s="79" t="s">
         <v>102</v>
       </c>
@@ -15155,8 +15145,8 @@
       </c>
     </row>
     <row r="125" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B125" s="165"/>
-      <c r="D125" s="161"/>
+      <c r="B125" s="164"/>
+      <c r="D125" s="160"/>
       <c r="E125" s="79" t="s">
         <v>104</v>
       </c>
@@ -15256,8 +15246,8 @@
       </c>
     </row>
     <row r="126" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B126" s="165"/>
-      <c r="D126" s="161"/>
+      <c r="B126" s="164"/>
+      <c r="D126" s="160"/>
       <c r="E126" s="79" t="s">
         <v>104</v>
       </c>
@@ -15357,8 +15347,8 @@
       </c>
     </row>
     <row r="127" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B127" s="165"/>
-      <c r="D127" s="161"/>
+      <c r="B127" s="164"/>
+      <c r="D127" s="160"/>
       <c r="E127" s="79" t="s">
         <v>104</v>
       </c>
@@ -15461,23 +15451,23 @@
       <c r="B128" s="87"/>
     </row>
     <row r="129" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B129" s="163" t="s">
+      <c r="B129" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="162"/>
-      <c r="D129" s="162"/>
-      <c r="E129" s="162"/>
-      <c r="F129" s="162"/>
-      <c r="G129" s="162"/>
-      <c r="H129" s="162"/>
-      <c r="I129" s="162"/>
-      <c r="J129" s="162"/>
-      <c r="K129" s="162"/>
-      <c r="L129" s="162"/>
-      <c r="M129" s="162"/>
-      <c r="N129" s="162"/>
-      <c r="O129" s="162"/>
-      <c r="P129" s="162"/>
+      <c r="C129" s="161"/>
+      <c r="D129" s="161"/>
+      <c r="E129" s="161"/>
+      <c r="F129" s="161"/>
+      <c r="G129" s="161"/>
+      <c r="H129" s="161"/>
+      <c r="I129" s="161"/>
+      <c r="J129" s="161"/>
+      <c r="K129" s="161"/>
+      <c r="L129" s="161"/>
+      <c r="M129" s="161"/>
+      <c r="N129" s="161"/>
+      <c r="O129" s="161"/>
+      <c r="P129" s="161"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15512,21 +15502,21 @@
     </row>
     <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="40"/>
-      <c r="C131" s="153" t="s">
+      <c r="C131" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="D131" s="154"/>
-      <c r="E131" s="154"/>
-      <c r="F131" s="154"/>
-      <c r="G131" s="154"/>
-      <c r="H131" s="154"/>
-      <c r="I131" s="156" t="s">
+      <c r="D131" s="153"/>
+      <c r="E131" s="153"/>
+      <c r="F131" s="153"/>
+      <c r="G131" s="153"/>
+      <c r="H131" s="153"/>
+      <c r="I131" s="155" t="s">
         <v>116</v>
       </c>
-      <c r="J131" s="157"/>
-      <c r="K131" s="157"/>
-      <c r="L131" s="157"/>
-      <c r="M131" s="158"/>
+      <c r="J131" s="156"/>
+      <c r="K131" s="156"/>
+      <c r="L131" s="156"/>
+      <c r="M131" s="157"/>
       <c r="N131" s="89" t="s">
         <v>117</v>
       </c>
@@ -15544,14 +15534,14 @@
     </row>
     <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="40"/>
-      <c r="C132" s="143" t="s">
+      <c r="C132" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="D132" s="144"/>
-      <c r="E132" s="144"/>
-      <c r="F132" s="144"/>
-      <c r="G132" s="144"/>
-      <c r="H132" s="145"/>
+      <c r="D132" s="143"/>
+      <c r="E132" s="143"/>
+      <c r="F132" s="143"/>
+      <c r="G132" s="143"/>
+      <c r="H132" s="144"/>
       <c r="I132" t="s">
         <v>95</v>
       </c>
@@ -15562,14 +15552,14 @@
     </row>
     <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="40"/>
-      <c r="C133" s="143" t="s">
+      <c r="C133" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D133" s="144"/>
-      <c r="E133" s="144"/>
-      <c r="F133" s="144"/>
-      <c r="G133" s="144"/>
-      <c r="H133" s="145"/>
+      <c r="D133" s="143"/>
+      <c r="E133" s="143"/>
+      <c r="F133" s="143"/>
+      <c r="G133" s="143"/>
+      <c r="H133" s="144"/>
       <c r="I133" s="100" t="s">
         <v>95</v>
       </c>
@@ -15592,21 +15582,21 @@
     </row>
     <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="40"/>
-      <c r="C134" s="143" t="s">
+      <c r="C134" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="D134" s="144"/>
-      <c r="E134" s="144"/>
-      <c r="F134" s="144"/>
-      <c r="G134" s="144"/>
-      <c r="H134" s="145"/>
-      <c r="I134" s="149" t="s">
+      <c r="D134" s="143"/>
+      <c r="E134" s="143"/>
+      <c r="F134" s="143"/>
+      <c r="G134" s="143"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="148" t="s">
         <v>122</v>
       </c>
-      <c r="J134" s="150"/>
-      <c r="K134" s="150"/>
-      <c r="L134" s="150"/>
-      <c r="M134" s="151"/>
+      <c r="J134" s="149"/>
+      <c r="K134" s="149"/>
+      <c r="L134" s="149"/>
+      <c r="M134" s="150"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15620,21 +15610,21 @@
     </row>
     <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="40"/>
-      <c r="C135" s="143" t="s">
+      <c r="C135" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D135" s="144"/>
-      <c r="E135" s="144"/>
-      <c r="F135" s="144"/>
-      <c r="G135" s="144"/>
-      <c r="H135" s="145"/>
-      <c r="I135" s="149" t="s">
+      <c r="D135" s="143"/>
+      <c r="E135" s="143"/>
+      <c r="F135" s="143"/>
+      <c r="G135" s="143"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="148" t="s">
         <v>124</v>
       </c>
-      <c r="J135" s="150"/>
-      <c r="K135" s="150"/>
-      <c r="L135" s="150"/>
-      <c r="M135" s="151"/>
+      <c r="J135" s="149"/>
+      <c r="K135" s="149"/>
+      <c r="L135" s="149"/>
+      <c r="M135" s="150"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15648,14 +15638,14 @@
     </row>
     <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="40"/>
-      <c r="C136" s="143" t="s">
+      <c r="C136" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D136" s="144"/>
-      <c r="E136" s="144"/>
-      <c r="F136" s="144"/>
-      <c r="G136" s="144"/>
-      <c r="H136" s="145"/>
+      <c r="D136" s="143"/>
+      <c r="E136" s="143"/>
+      <c r="F136" s="143"/>
+      <c r="G136" s="143"/>
+      <c r="H136" s="144"/>
       <c r="I136" s="108" t="s">
         <v>95</v>
       </c>
@@ -15676,14 +15666,14 @@
     </row>
     <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="40"/>
-      <c r="C137" s="146" t="s">
+      <c r="C137" s="145" t="s">
         <v>126</v>
       </c>
-      <c r="D137" s="147"/>
-      <c r="E137" s="147"/>
-      <c r="F137" s="147"/>
-      <c r="G137" s="147"/>
-      <c r="H137" s="148"/>
+      <c r="D137" s="146"/>
+      <c r="E137" s="146"/>
+      <c r="F137" s="146"/>
+      <c r="G137" s="146"/>
+      <c r="H137" s="147"/>
       <c r="I137" s="112" t="s">
         <v>95</v>
       </c>
@@ -15704,12 +15694,12 @@
     </row>
     <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="40"/>
-      <c r="C138" s="152"/>
-      <c r="D138" s="152"/>
-      <c r="E138" s="152"/>
-      <c r="F138" s="152"/>
-      <c r="G138" s="152"/>
-      <c r="H138" s="152"/>
+      <c r="C138" s="151"/>
+      <c r="D138" s="151"/>
+      <c r="E138" s="151"/>
+      <c r="F138" s="151"/>
+      <c r="G138" s="151"/>
+      <c r="H138" s="151"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15728,21 +15718,21 @@
     </row>
     <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" s="40"/>
-      <c r="C139" s="153" t="s">
+      <c r="C139" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="D139" s="154"/>
-      <c r="E139" s="154"/>
-      <c r="F139" s="154"/>
-      <c r="G139" s="154"/>
-      <c r="H139" s="155"/>
-      <c r="I139" s="156" t="s">
+      <c r="D139" s="153"/>
+      <c r="E139" s="153"/>
+      <c r="F139" s="153"/>
+      <c r="G139" s="153"/>
+      <c r="H139" s="154"/>
+      <c r="I139" s="155" t="s">
         <v>116</v>
       </c>
-      <c r="J139" s="157"/>
-      <c r="K139" s="157"/>
-      <c r="L139" s="157"/>
-      <c r="M139" s="158"/>
+      <c r="J139" s="156"/>
+      <c r="K139" s="156"/>
+      <c r="L139" s="156"/>
+      <c r="M139" s="157"/>
       <c r="N139" s="89" t="s">
         <v>117</v>
       </c>
@@ -15760,14 +15750,14 @@
     </row>
     <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="40"/>
-      <c r="C140" s="143" t="s">
+      <c r="C140" s="142" t="s">
         <v>120</v>
       </c>
-      <c r="D140" s="144"/>
-      <c r="E140" s="144"/>
-      <c r="F140" s="144"/>
-      <c r="G140" s="144"/>
-      <c r="H140" s="145"/>
+      <c r="D140" s="143"/>
+      <c r="E140" s="143"/>
+      <c r="F140" s="143"/>
+      <c r="G140" s="143"/>
+      <c r="H140" s="144"/>
       <c r="I140" s="100" t="s">
         <v>95</v>
       </c>
@@ -15851,14 +15841,14 @@
     </row>
     <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" s="40"/>
-      <c r="C143" s="143" t="s">
+      <c r="C143" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D143" s="144"/>
-      <c r="E143" s="144"/>
-      <c r="F143" s="144"/>
-      <c r="G143" s="144"/>
-      <c r="H143" s="145"/>
+      <c r="D143" s="143"/>
+      <c r="E143" s="143"/>
+      <c r="F143" s="143"/>
+      <c r="G143" s="143"/>
+      <c r="H143" s="144"/>
       <c r="I143" s="122" t="s">
         <v>128</v>
       </c>
@@ -15879,14 +15869,14 @@
     </row>
     <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" s="40"/>
-      <c r="C144" s="143" t="s">
+      <c r="C144" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="D144" s="144"/>
-      <c r="E144" s="144"/>
-      <c r="F144" s="144"/>
-      <c r="G144" s="144"/>
-      <c r="H144" s="145"/>
+      <c r="D144" s="143"/>
+      <c r="E144" s="143"/>
+      <c r="F144" s="143"/>
+      <c r="G144" s="143"/>
+      <c r="H144" s="144"/>
       <c r="I144" s="122" t="s">
         <v>128</v>
       </c>
@@ -15907,14 +15897,14 @@
     </row>
     <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="40"/>
-      <c r="C145" s="146" t="s">
+      <c r="C145" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="D145" s="147"/>
-      <c r="E145" s="147"/>
-      <c r="F145" s="147"/>
-      <c r="G145" s="147"/>
-      <c r="H145" s="148"/>
+      <c r="D145" s="146"/>
+      <c r="E145" s="146"/>
+      <c r="F145" s="146"/>
+      <c r="G145" s="146"/>
+      <c r="H145" s="147"/>
       <c r="I145" s="112" t="s">
         <v>95</v>
       </c>
@@ -16245,27 +16235,27 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="187"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="186"/>
       <c r="E2" s="39"/>
-      <c r="F2" s="185" t="s">
+      <c r="F2" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="186"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="185" t="s">
+      <c r="G2" s="185"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="186"/>
-      <c r="K2" s="187"/>
-      <c r="L2" s="185" t="s">
+      <c r="J2" s="185"/>
+      <c r="K2" s="186"/>
+      <c r="L2" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="186"/>
-      <c r="N2" s="187"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">

--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999D7867-60B9-40C5-9EDF-D7A44AA77B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D865-6970-43AC-AAE4-3A52F19D49FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,13 +505,13 @@
     <t>Raw Data (2022 $)</t>
   </si>
   <si>
-    <t>Battery Power Cost per Unit Capacity : NDC</t>
-  </si>
-  <si>
     <t>Time (Year)</t>
   </si>
   <si>
-    <t>Battery Energy Cost per Unit Capacity : NDC</t>
+    <t>Battery Energy Cost per Unit Capacity : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Battery Power Cost per Unit Capacity : MostRecentRun</t>
   </si>
 </sst>
 </file>
@@ -1968,69 +1968,15 @@
     <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2077,6 +2023,60 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2224,85 +2224,85 @@
                   <c:v>303546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>277345</c:v>
+                  <c:v>275720</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>256728</c:v>
+                  <c:v>254008</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>240275</c:v>
+                  <c:v>237399</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>226464</c:v>
+                  <c:v>223663</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>214618</c:v>
+                  <c:v>212018</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>204553</c:v>
+                  <c:v>202332</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>196075</c:v>
+                  <c:v>194107</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>188655</c:v>
+                  <c:v>186872</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>182183</c:v>
+                  <c:v>180500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>176401</c:v>
+                  <c:v>174745</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>171611</c:v>
+                  <c:v>169959</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>167430</c:v>
+                  <c:v>165780</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>163809</c:v>
+                  <c:v>162166</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>160633</c:v>
+                  <c:v>159002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>157780</c:v>
+                  <c:v>156172</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>155218</c:v>
+                  <c:v>153632</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>152921</c:v>
+                  <c:v>151363</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>150890</c:v>
+                  <c:v>149361</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>149018</c:v>
+                  <c:v>147535</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>147310</c:v>
+                  <c:v>145853</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>145744</c:v>
+                  <c:v>144309</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>144287</c:v>
+                  <c:v>142883</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>142963</c:v>
+                  <c:v>141583</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>141726</c:v>
+                  <c:v>140367</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>140576</c:v>
+                  <c:v>139237</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>139495</c:v>
+                  <c:v>138175</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>138485</c:v>
+                  <c:v>137182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4901,19 +4901,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="142" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
       <c r="M1" s="3" t="s">
         <v>68</v>
       </c>
@@ -5043,12 +5043,12 @@
     </row>
     <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="166" t="s">
+      <c r="L4" s="143" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L5" s="167"/>
+      <c r="L5" s="144"/>
     </row>
     <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
@@ -5080,23 +5080,23 @@
       <c r="B7" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="161" t="s">
+      <c r="C7" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="161"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="161"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="161"/>
-      <c r="P7" s="161"/>
-      <c r="Q7" s="161"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="145"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="145"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5114,43 +5114,43 @@
     </row>
     <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="168" t="s">
+      <c r="B9" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="169" t="s">
+      <c r="D9" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="170"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="172">
+      <c r="E9" s="148"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="150">
         <v>2021</v>
       </c>
-      <c r="H9" s="173"/>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="174"/>
-      <c r="L9" s="174"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="151"/>
+      <c r="K9" s="152"/>
+      <c r="L9" s="152"/>
     </row>
     <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="168"/>
+      <c r="B10" s="146"/>
       <c r="D10" s="53" t="s">
         <v>76</v>
       </c>
       <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="168"/>
-      <c r="D11" s="175" t="s">
+      <c r="B11" s="146"/>
+      <c r="D11" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="176"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
+      <c r="L11" s="154"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
@@ -5158,18 +5158,18 @@
       <c r="AA11" s="55"/>
     </row>
     <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="168"/>
-      <c r="D12" s="177" t="s">
+      <c r="B12" s="146"/>
+      <c r="D12" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="178"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="178"/>
-      <c r="J12" s="178"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="179"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="157"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5178,16 +5178,16 @@
       <c r="AA12" s="55"/>
     </row>
     <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="168"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="181"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="181"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="181"/>
-      <c r="L13" s="182"/>
+      <c r="B13" s="146"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="160"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
@@ -5195,49 +5195,49 @@
       <c r="AA13" s="55"/>
     </row>
     <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="168"/>
+      <c r="B14" s="146"/>
     </row>
     <row r="15" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B15" s="168"/>
-      <c r="C15" s="183" t="s">
+      <c r="B15" s="146"/>
+      <c r="C15" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="183"/>
-      <c r="L15" s="183"/>
-      <c r="M15" s="183"/>
-      <c r="N15" s="183"/>
-      <c r="O15" s="183"/>
-      <c r="P15" s="183"/>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="161"/>
+      <c r="K15" s="161"/>
+      <c r="L15" s="161"/>
+      <c r="M15" s="161"/>
+      <c r="N15" s="161"/>
+      <c r="O15" s="161"/>
+      <c r="P15" s="161"/>
       <c r="Q15" s="57"/>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B16" s="168"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="183"/>
-      <c r="K16" s="183"/>
-      <c r="L16" s="183"/>
-      <c r="M16" s="183"/>
-      <c r="N16" s="183"/>
-      <c r="O16" s="183"/>
-      <c r="P16" s="183"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
+      <c r="M16" s="161"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="161"/>
+      <c r="P16" s="161"/>
     </row>
     <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="168"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="58"/>
-      <c r="D17" s="158" t="s">
+      <c r="D17" s="168" t="s">
         <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -5245,9 +5245,9 @@
       </c>
     </row>
     <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="168"/>
+      <c r="B18" s="146"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="159"/>
+      <c r="D18" s="169"/>
       <c r="F18" s="1">
         <v>2021</v>
       </c>
@@ -5340,9 +5340,9 @@
       </c>
     </row>
     <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="168"/>
+      <c r="B19" s="146"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="159"/>
+      <c r="D19" s="169"/>
       <c r="E19" t="s">
         <v>82</v>
       </c>
@@ -5438,9 +5438,9 @@
       </c>
     </row>
     <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="168"/>
+      <c r="B20" s="146"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="160"/>
+      <c r="D20" s="170"/>
       <c r="E20" t="s">
         <v>83</v>
       </c>
@@ -5536,9 +5536,9 @@
       </c>
     </row>
     <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="168"/>
+      <c r="B21" s="146"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="160"/>
+      <c r="D21" s="170"/>
       <c r="E21" t="s">
         <v>84</v>
       </c>
@@ -5634,9 +5634,9 @@
       </c>
     </row>
     <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="168"/>
+      <c r="B22" s="146"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="160"/>
+      <c r="D22" s="170"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5669,18 +5669,18 @@
       <c r="AI22" s="5"/>
     </row>
     <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="168"/>
+      <c r="B23" s="146"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="160"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
       <c r="F23" s="60"/>
     </row>
     <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="168"/>
+      <c r="B24" s="146"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="160"/>
+      <c r="D24" s="170"/>
       <c r="F24" s="1">
         <v>2021</v>
       </c>
@@ -5773,9 +5773,9 @@
       </c>
     </row>
     <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="168"/>
+      <c r="B25" s="146"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="160"/>
+      <c r="D25" s="170"/>
       <c r="E25" t="s">
         <v>82</v>
       </c>
@@ -5871,9 +5871,9 @@
       </c>
     </row>
     <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="168"/>
+      <c r="B26" s="146"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="160"/>
+      <c r="D26" s="170"/>
       <c r="E26" t="s">
         <v>83</v>
       </c>
@@ -5969,9 +5969,9 @@
       </c>
     </row>
     <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="168"/>
+      <c r="B27" s="146"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="160"/>
+      <c r="D27" s="170"/>
       <c r="E27" t="s">
         <v>84</v>
       </c>
@@ -6067,7 +6067,7 @@
       </c>
     </row>
     <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="168"/>
+      <c r="B28" s="146"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6105,7 +6105,7 @@
       <c r="AM28" s="5"/>
     </row>
     <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="168"/>
+      <c r="B29" s="146"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
@@ -6147,7 +6147,7 @@
       <c r="AM29" s="5"/>
     </row>
     <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="168"/>
+      <c r="B30" s="146"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6187,9 +6187,9 @@
       <c r="AM30" s="5"/>
     </row>
     <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="168"/>
+      <c r="B31" s="146"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="159" t="s">
+      <c r="D31" s="169" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="61" t="s">
@@ -6239,9 +6239,9 @@
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="168"/>
+      <c r="B32" s="146"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="159"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="66" t="s">
         <v>93</v>
       </c>
@@ -6289,9 +6289,9 @@
       <c r="AM32" s="5"/>
     </row>
     <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="168"/>
+      <c r="B33" s="146"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="159"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="69" t="s">
         <v>98</v>
       </c>
@@ -6339,9 +6339,9 @@
       <c r="AM33" s="5"/>
     </row>
     <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="168"/>
+      <c r="B34" s="146"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="159"/>
+      <c r="D34" s="169"/>
       <c r="E34" s="72" t="s">
         <v>100</v>
       </c>
@@ -6389,9 +6389,9 @@
       <c r="AM34" s="5"/>
     </row>
     <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="168"/>
+      <c r="B35" s="146"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="159"/>
+      <c r="D35" s="169"/>
       <c r="E35" s="69" t="s">
         <v>102</v>
       </c>
@@ -6439,9 +6439,9 @@
       <c r="AM35" s="5"/>
     </row>
     <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="168"/>
+      <c r="B36" s="146"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="159"/>
+      <c r="D36" s="169"/>
       <c r="E36" s="75" t="s">
         <v>104</v>
       </c>
@@ -6528,23 +6528,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="161" t="s">
+      <c r="C38" s="145" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
-      <c r="P38" s="161"/>
-      <c r="Q38" s="161"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="145"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="145"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
+      <c r="Q38" s="145"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6677,10 +6677,10 @@
       </c>
     </row>
     <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="163" t="s">
+      <c r="B43" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="158" t="s">
+      <c r="D43" s="168" t="s">
         <v>109</v>
       </c>
       <c r="E43" s="79" t="s">
@@ -6782,8 +6782,8 @@
       </c>
     </row>
     <row r="44" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B44" s="163"/>
-      <c r="D44" s="159"/>
+      <c r="B44" s="177"/>
+      <c r="D44" s="169"/>
       <c r="E44" s="82" t="s">
         <v>93</v>
       </c>
@@ -6883,8 +6883,8 @@
       </c>
     </row>
     <row r="45" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B45" s="163"/>
-      <c r="D45" s="159"/>
+      <c r="B45" s="177"/>
+      <c r="D45" s="169"/>
       <c r="E45" s="83" t="s">
         <v>93</v>
       </c>
@@ -6984,8 +6984,8 @@
       </c>
     </row>
     <row r="46" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B46" s="163"/>
-      <c r="D46" s="160"/>
+      <c r="B46" s="177"/>
+      <c r="D46" s="170"/>
       <c r="E46" s="79" t="s">
         <v>98</v>
       </c>
@@ -7118,8 +7118,8 @@
       <c r="BV46" s="5"/>
     </row>
     <row r="47" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B47" s="163"/>
-      <c r="D47" s="160"/>
+      <c r="B47" s="177"/>
+      <c r="D47" s="170"/>
       <c r="E47" s="79" t="s">
         <v>98</v>
       </c>
@@ -7252,8 +7252,8 @@
       <c r="BV47" s="5"/>
     </row>
     <row r="48" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B48" s="163"/>
-      <c r="D48" s="160"/>
+      <c r="B48" s="177"/>
+      <c r="D48" s="170"/>
       <c r="E48" s="79" t="s">
         <v>98</v>
       </c>
@@ -7386,8 +7386,8 @@
       <c r="BV48" s="5"/>
     </row>
     <row r="49" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B49" s="163"/>
-      <c r="D49" s="160"/>
+      <c r="B49" s="177"/>
+      <c r="D49" s="170"/>
       <c r="E49" s="79" t="s">
         <v>100</v>
       </c>
@@ -7520,8 +7520,8 @@
       <c r="BV49" s="5"/>
     </row>
     <row r="50" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B50" s="163"/>
-      <c r="D50" s="160"/>
+      <c r="B50" s="177"/>
+      <c r="D50" s="170"/>
       <c r="E50" s="79" t="s">
         <v>100</v>
       </c>
@@ -7654,8 +7654,8 @@
       <c r="BV50" s="5"/>
     </row>
     <row r="51" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B51" s="163"/>
-      <c r="D51" s="160"/>
+      <c r="B51" s="177"/>
+      <c r="D51" s="170"/>
       <c r="E51" s="79" t="s">
         <v>100</v>
       </c>
@@ -7788,8 +7788,8 @@
       <c r="BV51" s="5"/>
     </row>
     <row r="52" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B52" s="163"/>
-      <c r="D52" s="160"/>
+      <c r="B52" s="177"/>
+      <c r="D52" s="170"/>
       <c r="E52" s="79" t="s">
         <v>102</v>
       </c>
@@ -7922,8 +7922,8 @@
       <c r="BV52" s="5"/>
     </row>
     <row r="53" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B53" s="163"/>
-      <c r="D53" s="160"/>
+      <c r="B53" s="177"/>
+      <c r="D53" s="170"/>
       <c r="E53" s="79" t="s">
         <v>102</v>
       </c>
@@ -8056,8 +8056,8 @@
       <c r="BV53" s="5"/>
     </row>
     <row r="54" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B54" s="163"/>
-      <c r="D54" s="160"/>
+      <c r="B54" s="177"/>
+      <c r="D54" s="170"/>
       <c r="E54" s="79" t="s">
         <v>102</v>
       </c>
@@ -8190,8 +8190,8 @@
       <c r="BV54" s="5"/>
     </row>
     <row r="55" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B55" s="163"/>
-      <c r="D55" s="160"/>
+      <c r="B55" s="177"/>
+      <c r="D55" s="170"/>
       <c r="E55" s="79" t="s">
         <v>104</v>
       </c>
@@ -8324,8 +8324,8 @@
       <c r="BV55" s="5"/>
     </row>
     <row r="56" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B56" s="163"/>
-      <c r="D56" s="160"/>
+      <c r="B56" s="177"/>
+      <c r="D56" s="170"/>
       <c r="E56" s="79" t="s">
         <v>104</v>
       </c>
@@ -8458,8 +8458,8 @@
       <c r="BV56" s="5"/>
     </row>
     <row r="57" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B57" s="163"/>
-      <c r="D57" s="160"/>
+      <c r="B57" s="177"/>
+      <c r="D57" s="170"/>
       <c r="E57" s="79" t="s">
         <v>104</v>
       </c>
@@ -8592,7 +8592,7 @@
       <c r="BV57" s="5"/>
     </row>
     <row r="58" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B58" s="163"/>
+      <c r="B58" s="177"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8661,7 +8661,7 @@
       <c r="BV58" s="5"/>
     </row>
     <row r="59" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B59" s="163"/>
+      <c r="B59" s="177"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8730,7 +8730,7 @@
       <c r="BV59" s="5"/>
     </row>
     <row r="60" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B60" s="163"/>
+      <c r="B60" s="177"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8799,7 +8799,7 @@
       <c r="BV60" s="5"/>
     </row>
     <row r="61" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B61" s="163"/>
+      <c r="B61" s="177"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
@@ -8895,8 +8895,8 @@
       </c>
     </row>
     <row r="62" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B62" s="163"/>
-      <c r="D62" s="158" t="s">
+      <c r="B62" s="177"/>
+      <c r="D62" s="168" t="s">
         <v>110</v>
       </c>
       <c r="E62" s="79" t="s">
@@ -8998,8 +8998,8 @@
       </c>
     </row>
     <row r="63" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B63" s="163"/>
-      <c r="D63" s="159"/>
+      <c r="B63" s="177"/>
+      <c r="D63" s="169"/>
       <c r="E63" s="82" t="s">
         <v>93</v>
       </c>
@@ -9099,8 +9099,8 @@
       </c>
     </row>
     <row r="64" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B64" s="163"/>
-      <c r="D64" s="159"/>
+      <c r="B64" s="177"/>
+      <c r="D64" s="169"/>
       <c r="E64" s="83" t="s">
         <v>93</v>
       </c>
@@ -9200,8 +9200,8 @@
       </c>
     </row>
     <row r="65" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B65" s="163"/>
-      <c r="D65" s="160"/>
+      <c r="B65" s="177"/>
+      <c r="D65" s="170"/>
       <c r="E65" s="79" t="s">
         <v>98</v>
       </c>
@@ -9301,8 +9301,8 @@
       </c>
     </row>
     <row r="66" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B66" s="163"/>
-      <c r="D66" s="160"/>
+      <c r="B66" s="177"/>
+      <c r="D66" s="170"/>
       <c r="E66" s="79" t="s">
         <v>98</v>
       </c>
@@ -9402,8 +9402,8 @@
       </c>
     </row>
     <row r="67" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B67" s="163"/>
-      <c r="D67" s="160"/>
+      <c r="B67" s="177"/>
+      <c r="D67" s="170"/>
       <c r="E67" s="79" t="s">
         <v>98</v>
       </c>
@@ -9503,8 +9503,8 @@
       </c>
     </row>
     <row r="68" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B68" s="163"/>
-      <c r="D68" s="160"/>
+      <c r="B68" s="177"/>
+      <c r="D68" s="170"/>
       <c r="E68" s="79" t="s">
         <v>100</v>
       </c>
@@ -9604,8 +9604,8 @@
       </c>
     </row>
     <row r="69" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B69" s="163"/>
-      <c r="D69" s="160"/>
+      <c r="B69" s="177"/>
+      <c r="D69" s="170"/>
       <c r="E69" s="79" t="s">
         <v>100</v>
       </c>
@@ -9705,8 +9705,8 @@
       </c>
     </row>
     <row r="70" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B70" s="163"/>
-      <c r="D70" s="160"/>
+      <c r="B70" s="177"/>
+      <c r="D70" s="170"/>
       <c r="E70" s="79" t="s">
         <v>100</v>
       </c>
@@ -9806,8 +9806,8 @@
       </c>
     </row>
     <row r="71" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B71" s="163"/>
-      <c r="D71" s="160"/>
+      <c r="B71" s="177"/>
+      <c r="D71" s="170"/>
       <c r="E71" s="79" t="s">
         <v>102</v>
       </c>
@@ -9940,8 +9940,8 @@
       <c r="BV71" s="5"/>
     </row>
     <row r="72" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B72" s="163"/>
-      <c r="D72" s="160"/>
+      <c r="B72" s="177"/>
+      <c r="D72" s="170"/>
       <c r="E72" s="79" t="s">
         <v>102</v>
       </c>
@@ -10074,8 +10074,8 @@
       <c r="BV72" s="5"/>
     </row>
     <row r="73" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B73" s="163"/>
-      <c r="D73" s="160"/>
+      <c r="B73" s="177"/>
+      <c r="D73" s="170"/>
       <c r="E73" s="79" t="s">
         <v>102</v>
       </c>
@@ -10208,8 +10208,8 @@
       <c r="BV73" s="5"/>
     </row>
     <row r="74" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B74" s="163"/>
-      <c r="D74" s="160"/>
+      <c r="B74" s="177"/>
+      <c r="D74" s="170"/>
       <c r="E74" s="79" t="s">
         <v>104</v>
       </c>
@@ -10342,8 +10342,8 @@
       <c r="BV74" s="5"/>
     </row>
     <row r="75" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B75" s="163"/>
-      <c r="D75" s="160"/>
+      <c r="B75" s="177"/>
+      <c r="D75" s="170"/>
       <c r="E75" s="79" t="s">
         <v>104</v>
       </c>
@@ -10476,8 +10476,8 @@
       <c r="BV75" s="5"/>
     </row>
     <row r="76" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B76" s="163"/>
-      <c r="D76" s="160"/>
+      <c r="B76" s="177"/>
+      <c r="D76" s="170"/>
       <c r="E76" s="79" t="s">
         <v>104</v>
       </c>
@@ -10610,13 +10610,13 @@
       <c r="BV76" s="5"/>
     </row>
     <row r="77" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B77" s="163"/>
+      <c r="B77" s="177"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
     <row r="78" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B78" s="163"/>
+      <c r="B78" s="177"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
@@ -10712,8 +10712,8 @@
       </c>
     </row>
     <row r="79" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B79" s="163"/>
-      <c r="D79" s="158" t="s">
+      <c r="B79" s="177"/>
+      <c r="D79" s="168" t="s">
         <v>111</v>
       </c>
       <c r="E79" s="79" t="s">
@@ -10815,8 +10815,8 @@
       <c r="AO79" s="1"/>
     </row>
     <row r="80" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B80" s="163"/>
-      <c r="D80" s="159"/>
+      <c r="B80" s="177"/>
+      <c r="D80" s="169"/>
       <c r="E80" s="82" t="s">
         <v>93</v>
       </c>
@@ -10916,8 +10916,8 @@
       <c r="AO80" s="1"/>
     </row>
     <row r="81" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B81" s="163"/>
-      <c r="D81" s="159"/>
+      <c r="B81" s="177"/>
+      <c r="D81" s="169"/>
       <c r="E81" s="83" t="s">
         <v>93</v>
       </c>
@@ -11017,8 +11017,8 @@
       <c r="AO81" s="1"/>
     </row>
     <row r="82" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B82" s="164"/>
-      <c r="D82" s="160"/>
+      <c r="B82" s="178"/>
+      <c r="D82" s="170"/>
       <c r="E82" s="79" t="s">
         <v>98</v>
       </c>
@@ -11117,8 +11117,8 @@
       </c>
     </row>
     <row r="83" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B83" s="164"/>
-      <c r="D83" s="160"/>
+      <c r="B83" s="178"/>
+      <c r="D83" s="170"/>
       <c r="E83" s="79" t="s">
         <v>98</v>
       </c>
@@ -11217,8 +11217,8 @@
       </c>
     </row>
     <row r="84" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B84" s="164"/>
-      <c r="D84" s="160"/>
+      <c r="B84" s="178"/>
+      <c r="D84" s="170"/>
       <c r="E84" s="79" t="s">
         <v>98</v>
       </c>
@@ -11319,8 +11319,8 @@
       <c r="AL84" s="5"/>
     </row>
     <row r="85" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B85" s="164"/>
-      <c r="D85" s="160"/>
+      <c r="B85" s="178"/>
+      <c r="D85" s="170"/>
       <c r="E85" s="79" t="s">
         <v>100</v>
       </c>
@@ -11421,8 +11421,8 @@
       <c r="AL85" s="5"/>
     </row>
     <row r="86" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B86" s="164"/>
-      <c r="D86" s="160"/>
+      <c r="B86" s="178"/>
+      <c r="D86" s="170"/>
       <c r="E86" s="79" t="s">
         <v>100</v>
       </c>
@@ -11523,8 +11523,8 @@
       <c r="AL86" s="5"/>
     </row>
     <row r="87" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B87" s="164"/>
-      <c r="D87" s="160"/>
+      <c r="B87" s="178"/>
+      <c r="D87" s="170"/>
       <c r="E87" s="79" t="s">
         <v>100</v>
       </c>
@@ -11625,8 +11625,8 @@
       <c r="AL87" s="5"/>
     </row>
     <row r="88" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B88" s="164"/>
-      <c r="D88" s="160"/>
+      <c r="B88" s="178"/>
+      <c r="D88" s="170"/>
       <c r="E88" s="79" t="s">
         <v>102</v>
       </c>
@@ -11727,8 +11727,8 @@
       <c r="AL88" s="5"/>
     </row>
     <row r="89" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B89" s="164"/>
-      <c r="D89" s="160"/>
+      <c r="B89" s="178"/>
+      <c r="D89" s="170"/>
       <c r="E89" s="79" t="s">
         <v>102</v>
       </c>
@@ -11829,8 +11829,8 @@
       <c r="AL89" s="5"/>
     </row>
     <row r="90" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B90" s="164"/>
-      <c r="D90" s="160"/>
+      <c r="B90" s="178"/>
+      <c r="D90" s="170"/>
       <c r="E90" s="79" t="s">
         <v>102</v>
       </c>
@@ -11931,8 +11931,8 @@
       <c r="AL90" s="5"/>
     </row>
     <row r="91" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B91" s="164"/>
-      <c r="D91" s="160"/>
+      <c r="B91" s="178"/>
+      <c r="D91" s="170"/>
       <c r="E91" s="79" t="s">
         <v>104</v>
       </c>
@@ -12033,8 +12033,8 @@
       <c r="AL91" s="5"/>
     </row>
     <row r="92" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B92" s="164"/>
-      <c r="D92" s="160"/>
+      <c r="B92" s="178"/>
+      <c r="D92" s="170"/>
       <c r="E92" s="79" t="s">
         <v>104</v>
       </c>
@@ -12135,8 +12135,8 @@
       <c r="AL92" s="5"/>
     </row>
     <row r="93" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B93" s="164"/>
-      <c r="D93" s="160"/>
+      <c r="B93" s="178"/>
+      <c r="D93" s="170"/>
       <c r="E93" s="79" t="s">
         <v>104</v>
       </c>
@@ -12237,10 +12237,10 @@
       <c r="AL93" s="5"/>
     </row>
     <row r="94" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B94" s="164"/>
+      <c r="B94" s="178"/>
     </row>
     <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="164"/>
+      <c r="B95" s="178"/>
       <c r="G95" s="1">
         <v>2021</v>
       </c>
@@ -12333,8 +12333,8 @@
       </c>
     </row>
     <row r="96" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B96" s="164"/>
-      <c r="D96" s="158" t="s">
+      <c r="B96" s="178"/>
+      <c r="D96" s="168" t="s">
         <v>112</v>
       </c>
       <c r="E96" s="79" t="s">
@@ -12435,8 +12435,8 @@
       </c>
     </row>
     <row r="97" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B97" s="164"/>
-      <c r="D97" s="159"/>
+      <c r="B97" s="178"/>
+      <c r="D97" s="169"/>
       <c r="E97" s="82" t="s">
         <v>93</v>
       </c>
@@ -12535,8 +12535,8 @@
       </c>
     </row>
     <row r="98" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B98" s="164"/>
-      <c r="D98" s="159"/>
+      <c r="B98" s="178"/>
+      <c r="D98" s="169"/>
       <c r="E98" s="83" t="s">
         <v>93</v>
       </c>
@@ -12635,8 +12635,8 @@
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B99" s="164"/>
-      <c r="D99" s="160"/>
+      <c r="B99" s="178"/>
+      <c r="D99" s="170"/>
       <c r="E99" s="79" t="s">
         <v>98</v>
       </c>
@@ -12735,8 +12735,8 @@
       </c>
     </row>
     <row r="100" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B100" s="164"/>
-      <c r="D100" s="160"/>
+      <c r="B100" s="178"/>
+      <c r="D100" s="170"/>
       <c r="E100" s="79" t="s">
         <v>98</v>
       </c>
@@ -12835,8 +12835,8 @@
       </c>
     </row>
     <row r="101" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B101" s="164"/>
-      <c r="D101" s="160"/>
+      <c r="B101" s="178"/>
+      <c r="D101" s="170"/>
       <c r="E101" s="79" t="s">
         <v>98</v>
       </c>
@@ -12935,8 +12935,8 @@
       </c>
     </row>
     <row r="102" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B102" s="164"/>
-      <c r="D102" s="160"/>
+      <c r="B102" s="178"/>
+      <c r="D102" s="170"/>
       <c r="E102" s="79" t="s">
         <v>100</v>
       </c>
@@ -13035,8 +13035,8 @@
       </c>
     </row>
     <row r="103" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B103" s="164"/>
-      <c r="D103" s="160"/>
+      <c r="B103" s="178"/>
+      <c r="D103" s="170"/>
       <c r="E103" s="79" t="s">
         <v>100</v>
       </c>
@@ -13135,8 +13135,8 @@
       </c>
     </row>
     <row r="104" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B104" s="164"/>
-      <c r="D104" s="160"/>
+      <c r="B104" s="178"/>
+      <c r="D104" s="170"/>
       <c r="E104" s="79" t="s">
         <v>100</v>
       </c>
@@ -13235,8 +13235,8 @@
       </c>
     </row>
     <row r="105" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B105" s="164"/>
-      <c r="D105" s="160"/>
+      <c r="B105" s="178"/>
+      <c r="D105" s="170"/>
       <c r="E105" s="79" t="s">
         <v>102</v>
       </c>
@@ -13335,8 +13335,8 @@
       </c>
     </row>
     <row r="106" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B106" s="164"/>
-      <c r="D106" s="160"/>
+      <c r="B106" s="178"/>
+      <c r="D106" s="170"/>
       <c r="E106" s="79" t="s">
         <v>102</v>
       </c>
@@ -13435,8 +13435,8 @@
       </c>
     </row>
     <row r="107" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B107" s="164"/>
-      <c r="D107" s="160"/>
+      <c r="B107" s="178"/>
+      <c r="D107" s="170"/>
       <c r="E107" s="79" t="s">
         <v>102</v>
       </c>
@@ -13535,8 +13535,8 @@
       </c>
     </row>
     <row r="108" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B108" s="164"/>
-      <c r="D108" s="160"/>
+      <c r="B108" s="178"/>
+      <c r="D108" s="170"/>
       <c r="E108" s="79" t="s">
         <v>104</v>
       </c>
@@ -13635,8 +13635,8 @@
       </c>
     </row>
     <row r="109" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B109" s="164"/>
-      <c r="D109" s="160"/>
+      <c r="B109" s="178"/>
+      <c r="D109" s="170"/>
       <c r="E109" s="79" t="s">
         <v>104</v>
       </c>
@@ -13735,8 +13735,8 @@
       </c>
     </row>
     <row r="110" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B110" s="164"/>
-      <c r="D110" s="160"/>
+      <c r="B110" s="178"/>
+      <c r="D110" s="170"/>
       <c r="E110" s="79" t="s">
         <v>104</v>
       </c>
@@ -13835,10 +13835,10 @@
       </c>
     </row>
     <row r="111" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B111" s="164"/>
+      <c r="B111" s="178"/>
     </row>
     <row r="112" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B112" s="164"/>
+      <c r="B112" s="178"/>
       <c r="G112" s="1">
         <v>2021</v>
       </c>
@@ -13931,8 +13931,8 @@
       </c>
     </row>
     <row r="113" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B113" s="164"/>
-      <c r="D113" s="158" t="s">
+      <c r="B113" s="178"/>
+      <c r="D113" s="168" t="s">
         <v>113</v>
       </c>
       <c r="E113" s="79" t="s">
@@ -14034,8 +14034,8 @@
       </c>
     </row>
     <row r="114" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B114" s="164"/>
-      <c r="D114" s="159"/>
+      <c r="B114" s="178"/>
+      <c r="D114" s="169"/>
       <c r="E114" s="82" t="s">
         <v>93</v>
       </c>
@@ -14135,8 +14135,8 @@
       </c>
     </row>
     <row r="115" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B115" s="164"/>
-      <c r="D115" s="159"/>
+      <c r="B115" s="178"/>
+      <c r="D115" s="169"/>
       <c r="E115" s="83" t="s">
         <v>93</v>
       </c>
@@ -14236,8 +14236,8 @@
       </c>
     </row>
     <row r="116" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B116" s="164"/>
-      <c r="D116" s="160"/>
+      <c r="B116" s="178"/>
+      <c r="D116" s="170"/>
       <c r="E116" s="79" t="s">
         <v>98</v>
       </c>
@@ -14337,8 +14337,8 @@
       </c>
     </row>
     <row r="117" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B117" s="164"/>
-      <c r="D117" s="160"/>
+      <c r="B117" s="178"/>
+      <c r="D117" s="170"/>
       <c r="E117" s="79" t="s">
         <v>98</v>
       </c>
@@ -14438,8 +14438,8 @@
       </c>
     </row>
     <row r="118" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B118" s="164"/>
-      <c r="D118" s="160"/>
+      <c r="B118" s="178"/>
+      <c r="D118" s="170"/>
       <c r="E118" s="79" t="s">
         <v>98</v>
       </c>
@@ -14539,8 +14539,8 @@
       </c>
     </row>
     <row r="119" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B119" s="164"/>
-      <c r="D119" s="160"/>
+      <c r="B119" s="178"/>
+      <c r="D119" s="170"/>
       <c r="E119" s="79" t="s">
         <v>100</v>
       </c>
@@ -14640,8 +14640,8 @@
       </c>
     </row>
     <row r="120" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B120" s="164"/>
-      <c r="D120" s="160"/>
+      <c r="B120" s="178"/>
+      <c r="D120" s="170"/>
       <c r="E120" s="79" t="s">
         <v>100</v>
       </c>
@@ -14741,8 +14741,8 @@
       </c>
     </row>
     <row r="121" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B121" s="164"/>
-      <c r="D121" s="160"/>
+      <c r="B121" s="178"/>
+      <c r="D121" s="170"/>
       <c r="E121" s="79" t="s">
         <v>100</v>
       </c>
@@ -14842,8 +14842,8 @@
       </c>
     </row>
     <row r="122" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B122" s="164"/>
-      <c r="D122" s="160"/>
+      <c r="B122" s="178"/>
+      <c r="D122" s="170"/>
       <c r="E122" s="79" t="s">
         <v>102</v>
       </c>
@@ -14943,8 +14943,8 @@
       </c>
     </row>
     <row r="123" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B123" s="164"/>
-      <c r="D123" s="160"/>
+      <c r="B123" s="178"/>
+      <c r="D123" s="170"/>
       <c r="E123" s="79" t="s">
         <v>102</v>
       </c>
@@ -15044,8 +15044,8 @@
       </c>
     </row>
     <row r="124" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B124" s="164"/>
-      <c r="D124" s="160"/>
+      <c r="B124" s="178"/>
+      <c r="D124" s="170"/>
       <c r="E124" s="79" t="s">
         <v>102</v>
       </c>
@@ -15145,8 +15145,8 @@
       </c>
     </row>
     <row r="125" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B125" s="164"/>
-      <c r="D125" s="160"/>
+      <c r="B125" s="178"/>
+      <c r="D125" s="170"/>
       <c r="E125" s="79" t="s">
         <v>104</v>
       </c>
@@ -15246,8 +15246,8 @@
       </c>
     </row>
     <row r="126" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B126" s="164"/>
-      <c r="D126" s="160"/>
+      <c r="B126" s="178"/>
+      <c r="D126" s="170"/>
       <c r="E126" s="79" t="s">
         <v>104</v>
       </c>
@@ -15347,8 +15347,8 @@
       </c>
     </row>
     <row r="127" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B127" s="164"/>
-      <c r="D127" s="160"/>
+      <c r="B127" s="178"/>
+      <c r="D127" s="170"/>
       <c r="E127" s="79" t="s">
         <v>104</v>
       </c>
@@ -15451,23 +15451,23 @@
       <c r="B128" s="87"/>
     </row>
     <row r="129" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B129" s="162" t="s">
+      <c r="B129" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="161"/>
-      <c r="D129" s="161"/>
-      <c r="E129" s="161"/>
-      <c r="F129" s="161"/>
-      <c r="G129" s="161"/>
-      <c r="H129" s="161"/>
-      <c r="I129" s="161"/>
-      <c r="J129" s="161"/>
-      <c r="K129" s="161"/>
-      <c r="L129" s="161"/>
-      <c r="M129" s="161"/>
-      <c r="N129" s="161"/>
-      <c r="O129" s="161"/>
-      <c r="P129" s="161"/>
+      <c r="C129" s="145"/>
+      <c r="D129" s="145"/>
+      <c r="E129" s="145"/>
+      <c r="F129" s="145"/>
+      <c r="G129" s="145"/>
+      <c r="H129" s="145"/>
+      <c r="I129" s="145"/>
+      <c r="J129" s="145"/>
+      <c r="K129" s="145"/>
+      <c r="L129" s="145"/>
+      <c r="M129" s="145"/>
+      <c r="N129" s="145"/>
+      <c r="O129" s="145"/>
+      <c r="P129" s="145"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15502,21 +15502,21 @@
     </row>
     <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="40"/>
-      <c r="C131" s="152" t="s">
+      <c r="C131" s="172" t="s">
         <v>115</v>
       </c>
-      <c r="D131" s="153"/>
-      <c r="E131" s="153"/>
-      <c r="F131" s="153"/>
-      <c r="G131" s="153"/>
-      <c r="H131" s="153"/>
-      <c r="I131" s="155" t="s">
+      <c r="D131" s="173"/>
+      <c r="E131" s="173"/>
+      <c r="F131" s="173"/>
+      <c r="G131" s="173"/>
+      <c r="H131" s="173"/>
+      <c r="I131" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="J131" s="156"/>
-      <c r="K131" s="156"/>
-      <c r="L131" s="156"/>
-      <c r="M131" s="157"/>
+      <c r="J131" s="175"/>
+      <c r="K131" s="175"/>
+      <c r="L131" s="175"/>
+      <c r="M131" s="176"/>
       <c r="N131" s="89" t="s">
         <v>117</v>
       </c>
@@ -15534,14 +15534,14 @@
     </row>
     <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="40"/>
-      <c r="C132" s="142" t="s">
+      <c r="C132" s="162" t="s">
         <v>119</v>
       </c>
-      <c r="D132" s="143"/>
-      <c r="E132" s="143"/>
-      <c r="F132" s="143"/>
-      <c r="G132" s="143"/>
-      <c r="H132" s="144"/>
+      <c r="D132" s="163"/>
+      <c r="E132" s="163"/>
+      <c r="F132" s="163"/>
+      <c r="G132" s="163"/>
+      <c r="H132" s="164"/>
       <c r="I132" t="s">
         <v>95</v>
       </c>
@@ -15552,14 +15552,14 @@
     </row>
     <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="40"/>
-      <c r="C133" s="142" t="s">
+      <c r="C133" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="D133" s="143"/>
-      <c r="E133" s="143"/>
-      <c r="F133" s="143"/>
-      <c r="G133" s="143"/>
-      <c r="H133" s="144"/>
+      <c r="D133" s="163"/>
+      <c r="E133" s="163"/>
+      <c r="F133" s="163"/>
+      <c r="G133" s="163"/>
+      <c r="H133" s="164"/>
       <c r="I133" s="100" t="s">
         <v>95</v>
       </c>
@@ -15582,21 +15582,21 @@
     </row>
     <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="40"/>
-      <c r="C134" s="142" t="s">
+      <c r="C134" s="162" t="s">
         <v>109</v>
       </c>
-      <c r="D134" s="143"/>
-      <c r="E134" s="143"/>
-      <c r="F134" s="143"/>
-      <c r="G134" s="143"/>
-      <c r="H134" s="144"/>
-      <c r="I134" s="148" t="s">
+      <c r="D134" s="163"/>
+      <c r="E134" s="163"/>
+      <c r="F134" s="163"/>
+      <c r="G134" s="163"/>
+      <c r="H134" s="164"/>
+      <c r="I134" s="165" t="s">
         <v>122</v>
       </c>
-      <c r="J134" s="149"/>
-      <c r="K134" s="149"/>
-      <c r="L134" s="149"/>
-      <c r="M134" s="150"/>
+      <c r="J134" s="166"/>
+      <c r="K134" s="166"/>
+      <c r="L134" s="166"/>
+      <c r="M134" s="167"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15610,21 +15610,21 @@
     </row>
     <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="40"/>
-      <c r="C135" s="142" t="s">
+      <c r="C135" s="162" t="s">
         <v>123</v>
       </c>
-      <c r="D135" s="143"/>
-      <c r="E135" s="143"/>
-      <c r="F135" s="143"/>
-      <c r="G135" s="143"/>
-      <c r="H135" s="144"/>
-      <c r="I135" s="148" t="s">
+      <c r="D135" s="163"/>
+      <c r="E135" s="163"/>
+      <c r="F135" s="163"/>
+      <c r="G135" s="163"/>
+      <c r="H135" s="164"/>
+      <c r="I135" s="165" t="s">
         <v>124</v>
       </c>
-      <c r="J135" s="149"/>
-      <c r="K135" s="149"/>
-      <c r="L135" s="149"/>
-      <c r="M135" s="150"/>
+      <c r="J135" s="166"/>
+      <c r="K135" s="166"/>
+      <c r="L135" s="166"/>
+      <c r="M135" s="167"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15638,14 +15638,14 @@
     </row>
     <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="40"/>
-      <c r="C136" s="142" t="s">
+      <c r="C136" s="162" t="s">
         <v>125</v>
       </c>
-      <c r="D136" s="143"/>
-      <c r="E136" s="143"/>
-      <c r="F136" s="143"/>
-      <c r="G136" s="143"/>
-      <c r="H136" s="144"/>
+      <c r="D136" s="163"/>
+      <c r="E136" s="163"/>
+      <c r="F136" s="163"/>
+      <c r="G136" s="163"/>
+      <c r="H136" s="164"/>
       <c r="I136" s="108" t="s">
         <v>95</v>
       </c>
@@ -15666,14 +15666,14 @@
     </row>
     <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="40"/>
-      <c r="C137" s="145" t="s">
+      <c r="C137" s="179" t="s">
         <v>126</v>
       </c>
-      <c r="D137" s="146"/>
-      <c r="E137" s="146"/>
-      <c r="F137" s="146"/>
-      <c r="G137" s="146"/>
-      <c r="H137" s="147"/>
+      <c r="D137" s="180"/>
+      <c r="E137" s="180"/>
+      <c r="F137" s="180"/>
+      <c r="G137" s="180"/>
+      <c r="H137" s="181"/>
       <c r="I137" s="112" t="s">
         <v>95</v>
       </c>
@@ -15694,12 +15694,12 @@
     </row>
     <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="40"/>
-      <c r="C138" s="151"/>
-      <c r="D138" s="151"/>
-      <c r="E138" s="151"/>
-      <c r="F138" s="151"/>
-      <c r="G138" s="151"/>
-      <c r="H138" s="151"/>
+      <c r="C138" s="182"/>
+      <c r="D138" s="182"/>
+      <c r="E138" s="182"/>
+      <c r="F138" s="182"/>
+      <c r="G138" s="182"/>
+      <c r="H138" s="182"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15718,21 +15718,21 @@
     </row>
     <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" s="40"/>
-      <c r="C139" s="152" t="s">
+      <c r="C139" s="172" t="s">
         <v>127</v>
       </c>
-      <c r="D139" s="153"/>
-      <c r="E139" s="153"/>
-      <c r="F139" s="153"/>
-      <c r="G139" s="153"/>
-      <c r="H139" s="154"/>
-      <c r="I139" s="155" t="s">
+      <c r="D139" s="173"/>
+      <c r="E139" s="173"/>
+      <c r="F139" s="173"/>
+      <c r="G139" s="173"/>
+      <c r="H139" s="183"/>
+      <c r="I139" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="J139" s="156"/>
-      <c r="K139" s="156"/>
-      <c r="L139" s="156"/>
-      <c r="M139" s="157"/>
+      <c r="J139" s="175"/>
+      <c r="K139" s="175"/>
+      <c r="L139" s="175"/>
+      <c r="M139" s="176"/>
       <c r="N139" s="89" t="s">
         <v>117</v>
       </c>
@@ -15750,14 +15750,14 @@
     </row>
     <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="40"/>
-      <c r="C140" s="142" t="s">
+      <c r="C140" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="D140" s="143"/>
-      <c r="E140" s="143"/>
-      <c r="F140" s="143"/>
-      <c r="G140" s="143"/>
-      <c r="H140" s="144"/>
+      <c r="D140" s="163"/>
+      <c r="E140" s="163"/>
+      <c r="F140" s="163"/>
+      <c r="G140" s="163"/>
+      <c r="H140" s="164"/>
       <c r="I140" s="100" t="s">
         <v>95</v>
       </c>
@@ -15841,14 +15841,14 @@
     </row>
     <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" s="40"/>
-      <c r="C143" s="142" t="s">
+      <c r="C143" s="162" t="s">
         <v>123</v>
       </c>
-      <c r="D143" s="143"/>
-      <c r="E143" s="143"/>
-      <c r="F143" s="143"/>
-      <c r="G143" s="143"/>
-      <c r="H143" s="144"/>
+      <c r="D143" s="163"/>
+      <c r="E143" s="163"/>
+      <c r="F143" s="163"/>
+      <c r="G143" s="163"/>
+      <c r="H143" s="164"/>
       <c r="I143" s="122" t="s">
         <v>128</v>
       </c>
@@ -15869,14 +15869,14 @@
     </row>
     <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" s="40"/>
-      <c r="C144" s="142" t="s">
+      <c r="C144" s="162" t="s">
         <v>125</v>
       </c>
-      <c r="D144" s="143"/>
-      <c r="E144" s="143"/>
-      <c r="F144" s="143"/>
-      <c r="G144" s="143"/>
-      <c r="H144" s="144"/>
+      <c r="D144" s="163"/>
+      <c r="E144" s="163"/>
+      <c r="F144" s="163"/>
+      <c r="G144" s="163"/>
+      <c r="H144" s="164"/>
       <c r="I144" s="122" t="s">
         <v>128</v>
       </c>
@@ -15897,14 +15897,14 @@
     </row>
     <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="40"/>
-      <c r="C145" s="145" t="s">
+      <c r="C145" s="179" t="s">
         <v>131</v>
       </c>
-      <c r="D145" s="146"/>
-      <c r="E145" s="146"/>
-      <c r="F145" s="146"/>
-      <c r="G145" s="146"/>
-      <c r="H145" s="147"/>
+      <c r="D145" s="180"/>
+      <c r="E145" s="180"/>
+      <c r="F145" s="180"/>
+      <c r="G145" s="180"/>
+      <c r="H145" s="181"/>
       <c r="I145" s="112" t="s">
         <v>95</v>
       </c>
@@ -16156,16 +16156,17 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="C7:Q7"/>
-    <mergeCell ref="B9:B36"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D13:L13"/>
-    <mergeCell ref="C15:P16"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="I135:M135"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="I139:M139"/>
     <mergeCell ref="C134:H134"/>
     <mergeCell ref="I134:M134"/>
     <mergeCell ref="D17:D27"/>
@@ -16182,17 +16183,16 @@
     <mergeCell ref="D79:D93"/>
     <mergeCell ref="D96:D110"/>
     <mergeCell ref="D113:D127"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="I139:M139"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="B9:B36"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C15:P16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M1" r:id="rId1" display="https://atb.nrel.gov/electricity/2022/utility-scale_battery_storage" xr:uid="{7816EC9A-0454-4087-A6E1-F971C99AA20E}"/>
@@ -17045,12 +17045,12 @@
   <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -17145,7 +17145,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2">
         <v>272875</v>
@@ -17157,85 +17157,85 @@
         <v>303546</v>
       </c>
       <c r="E2">
-        <v>277345</v>
+        <v>275720</v>
       </c>
       <c r="F2">
-        <v>256728</v>
+        <v>254008</v>
       </c>
       <c r="G2">
-        <v>240275</v>
+        <v>237399</v>
       </c>
       <c r="H2">
-        <v>226464</v>
+        <v>223663</v>
       </c>
       <c r="I2">
-        <v>214618</v>
+        <v>212018</v>
       </c>
       <c r="J2">
-        <v>204553</v>
+        <v>202332</v>
       </c>
       <c r="K2">
-        <v>196075</v>
+        <v>194107</v>
       </c>
       <c r="L2">
-        <v>188655</v>
+        <v>186872</v>
       </c>
       <c r="M2">
-        <v>182183</v>
+        <v>180500</v>
       </c>
       <c r="N2">
-        <v>176401</v>
+        <v>174745</v>
       </c>
       <c r="O2">
-        <v>171611</v>
+        <v>169959</v>
       </c>
       <c r="P2">
-        <v>167430</v>
+        <v>165780</v>
       </c>
       <c r="Q2">
-        <v>163809</v>
+        <v>162166</v>
       </c>
       <c r="R2">
-        <v>160633</v>
+        <v>159002</v>
       </c>
       <c r="S2">
-        <v>157780</v>
+        <v>156172</v>
       </c>
       <c r="T2">
-        <v>155218</v>
+        <v>153632</v>
       </c>
       <c r="U2">
-        <v>152921</v>
+        <v>151363</v>
       </c>
       <c r="V2">
-        <v>150890</v>
+        <v>149361</v>
       </c>
       <c r="W2">
-        <v>149018</v>
+        <v>147535</v>
       </c>
       <c r="X2">
-        <v>147310</v>
+        <v>145853</v>
       </c>
       <c r="Y2">
-        <v>145744</v>
+        <v>144309</v>
       </c>
       <c r="Z2">
-        <v>144287</v>
+        <v>142883</v>
       </c>
       <c r="AA2">
-        <v>142963</v>
+        <v>141583</v>
       </c>
       <c r="AB2">
-        <v>141726</v>
+        <v>140367</v>
       </c>
       <c r="AC2">
-        <v>140576</v>
+        <v>139237</v>
       </c>
       <c r="AD2">
-        <v>139495</v>
+        <v>138175</v>
       </c>
       <c r="AE2">
-        <v>138485</v>
+        <v>137182</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -17358,7 +17358,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -17453,7 +17453,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>253384</v>

--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F6D865-6970-43AC-AAE4-3A52F19D49FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2023F6E8-4F57-4EF1-831B-D65E2CCCF5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="152">
   <si>
     <t>Year</t>
   </si>
@@ -270,9 +270,6 @@
     <t>Base Year:</t>
   </si>
   <si>
-    <t>All values are given in 2021 U.S. dollars, see references at the bottom of this worksheet for dollar year conversions where source dollar years don't match 2021.</t>
-  </si>
-  <si>
     <t>Utility Scale Battery Storage</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
       </rPr>
       <t xml:space="preserve"> storage (4 hours)</t>
     </r>
-  </si>
-  <si>
-    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf. Note that values are converted to 2021$ for the ATB.</t>
   </si>
   <si>
     <t>Capital Cost ($/kWh)</t>
@@ -380,9 +374,6 @@
   </si>
   <si>
     <t>Future Projections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All values are given in 2021 U.S. dollars, using the Consumer Price Index (BLS, 2022) for dollar year conversions. </t>
   </si>
   <si>
     <t>For 15-year technical life (values in 2021$):</t>
@@ -512,6 +503,18 @@
   </si>
   <si>
     <t>Battery Power Cost per Unit Capacity : MostRecentRun</t>
+  </si>
+  <si>
+    <t>2021 (from 2023 ATB)</t>
+  </si>
+  <si>
+    <t>All values are given in 2022 U.S. dollars except 2021 data.</t>
+  </si>
+  <si>
+    <t>Reference: Battery Storage cost values from W. Cole and A. Karmakar, “Cost Projections for Utility-scale Battery Storage: 2023 Update,” NREL/TP-6A40-85332. Golden, CO: National Renewable Energy Laboratory. https://www.nrel.gov/docs/fy23osti/85332.pdf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All values are given in 2022 U.S. dollars except for 2021 values from ATB 2023 </t>
   </si>
 </sst>
 </file>
@@ -1968,15 +1971,69 @@
     <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2023,60 +2080,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4610,7 +4613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -4624,7 +4627,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4712,7 +4715,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4757,12 +4760,12 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4772,12 +4775,12 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4787,7 +4790,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4802,7 +4805,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4831,7 +4834,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>0.89805481563188172</v>
       </c>
@@ -4839,7 +4842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>0.88711067149387013</v>
       </c>
@@ -4847,30 +4850,34 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>0.84730412960844359</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="C51">
+        <f>cpi_2022_to_2012/A51</f>
+        <v>0.92590251319813455</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>0.78452102304761584</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -4901,19 +4908,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="165" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="M1" s="3" t="s">
         <v>68</v>
       </c>
@@ -5043,12 +5050,12 @@
     </row>
     <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="143" t="s">
+      <c r="L4" s="166" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L5" s="144"/>
+      <c r="L5" s="167"/>
     </row>
     <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
@@ -5080,23 +5087,23 @@
       <c r="B7" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="145" t="s">
+      <c r="C7" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="145"/>
-      <c r="K7" s="145"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="145"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
+      <c r="D7" s="161"/>
+      <c r="E7" s="161"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5114,43 +5121,43 @@
     </row>
     <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="168" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="147" t="s">
+      <c r="D9" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="150">
-        <v>2021</v>
-      </c>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="152"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="172">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="174"/>
+      <c r="L9" s="174"/>
     </row>
     <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="146"/>
+      <c r="B10" s="168"/>
       <c r="D10" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="J10" s="52"/>
+    </row>
+    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="168"/>
+      <c r="D11" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="146"/>
-      <c r="D11" s="153" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="154"/>
-      <c r="K11" s="154"/>
-      <c r="L11" s="154"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
@@ -5158,18 +5165,18 @@
       <c r="AA11" s="55"/>
     </row>
     <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="146"/>
-      <c r="D12" s="155" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="157"/>
+      <c r="B12" s="168"/>
+      <c r="D12" s="177" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="178"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="178"/>
+      <c r="H12" s="178"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
+      <c r="K12" s="178"/>
+      <c r="L12" s="179"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5178,16 +5185,16 @@
       <c r="AA12" s="55"/>
     </row>
     <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="146"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="159"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="159"/>
-      <c r="J13" s="159"/>
-      <c r="K13" s="159"/>
-      <c r="L13" s="160"/>
+      <c r="B13" s="168"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="182"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
@@ -5195,61 +5202,61 @@
       <c r="AA13" s="55"/>
     </row>
     <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="146"/>
-    </row>
-    <row r="15" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B15" s="146"/>
-      <c r="C15" s="161" t="s">
+      <c r="B14" s="168"/>
+    </row>
+    <row r="15" spans="1:108" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="168"/>
+      <c r="C15" s="183" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="183"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="183"/>
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="57"/>
+    </row>
+    <row r="16" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="B16" s="168"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="183"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="183"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="183"/>
+      <c r="M16" s="183"/>
+      <c r="N16" s="183"/>
+      <c r="O16" s="183"/>
+      <c r="P16" s="183"/>
+    </row>
+    <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="168"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="158" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="161"/>
-      <c r="E15" s="161"/>
-      <c r="F15" s="161"/>
-      <c r="G15" s="161"/>
-      <c r="H15" s="161"/>
-      <c r="I15" s="161"/>
-      <c r="J15" s="161"/>
-      <c r="K15" s="161"/>
-      <c r="L15" s="161"/>
-      <c r="M15" s="161"/>
-      <c r="N15" s="161"/>
-      <c r="O15" s="161"/>
-      <c r="P15" s="161"/>
-      <c r="Q15" s="57"/>
-    </row>
-    <row r="16" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B16" s="146"/>
-      <c r="C16" s="161"/>
-      <c r="D16" s="161"/>
-      <c r="E16" s="161"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
-      <c r="I16" s="161"/>
-      <c r="J16" s="161"/>
-      <c r="K16" s="161"/>
-      <c r="L16" s="161"/>
-      <c r="M16" s="161"/>
-      <c r="N16" s="161"/>
-      <c r="O16" s="161"/>
-      <c r="P16" s="161"/>
-    </row>
-    <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="146"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="168" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="146"/>
+      <c r="B18" s="168"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="169"/>
-      <c r="F18" s="1">
-        <v>2021</v>
+      <c r="D18" s="159"/>
+      <c r="F18" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="G18" s="1">
         <v>2022</v>
@@ -5340,11 +5347,11 @@
       </c>
     </row>
     <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="146"/>
+      <c r="B19" s="168"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="169"/>
+      <c r="D19" s="159"/>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F19" s="59">
         <v>322.051049922</v>
@@ -5438,11 +5445,11 @@
       </c>
     </row>
     <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="146"/>
+      <c r="B20" s="168"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="170"/>
+      <c r="D20" s="160"/>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F20" s="59">
         <v>322.051049922</v>
@@ -5536,11 +5543,11 @@
       </c>
     </row>
     <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="146"/>
+      <c r="B21" s="168"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="170"/>
+      <c r="D21" s="160"/>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F21" s="59">
         <v>322.051049922</v>
@@ -5634,9 +5641,9 @@
       </c>
     </row>
     <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="146"/>
+      <c r="B22" s="168"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="170"/>
+      <c r="D22" s="160"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5669,20 +5676,20 @@
       <c r="AI22" s="5"/>
     </row>
     <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="146"/>
+      <c r="B23" s="168"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="170"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F23" s="60"/>
     </row>
     <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="146"/>
+      <c r="B24" s="168"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="170"/>
-      <c r="F24" s="1">
-        <v>2021</v>
+      <c r="D24" s="160"/>
+      <c r="F24" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="G24" s="1">
         <v>2022</v>
@@ -5773,11 +5780,11 @@
       </c>
     </row>
     <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="146"/>
+      <c r="B25" s="168"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="170"/>
+      <c r="D25" s="160"/>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" s="59">
         <v>299.04780031199999</v>
@@ -5871,11 +5878,11 @@
       </c>
     </row>
     <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="146"/>
+      <c r="B26" s="168"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="170"/>
+      <c r="D26" s="160"/>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F26" s="59">
         <v>299.04780031199999</v>
@@ -5969,11 +5976,11 @@
       </c>
     </row>
     <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="146"/>
+      <c r="B27" s="168"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="170"/>
+      <c r="D27" s="160"/>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F27" s="59">
         <v>299.04780031199999</v>
@@ -6067,7 +6074,7 @@
       </c>
     </row>
     <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="146"/>
+      <c r="B28" s="168"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6105,11 +6112,11 @@
       <c r="AM28" s="5"/>
     </row>
     <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="146"/>
+      <c r="B29" s="168"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
@@ -6147,7 +6154,7 @@
       <c r="AM29" s="5"/>
     </row>
     <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="146"/>
+      <c r="B30" s="168"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6187,25 +6194,25 @@
       <c r="AM30" s="5"/>
     </row>
     <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="146"/>
+      <c r="B31" s="168"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="169" t="s">
+      <c r="D31" s="159" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="61" t="s">
+      <c r="G31" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="62" t="s">
+      <c r="H31" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="62" t="s">
+      <c r="I31" s="63" t="s">
         <v>90</v>
-      </c>
-      <c r="H31" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="63" t="s">
-        <v>92</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="64"/>
@@ -6239,23 +6246,23 @@
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="146"/>
+      <c r="B32" s="168"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="169"/>
+      <c r="D32" s="159"/>
       <c r="E32" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="67" t="s">
+      <c r="H32" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="G32" s="67" t="s">
+      <c r="I32" s="68" t="s">
         <v>95</v>
-      </c>
-      <c r="H32" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="I32" s="68" t="s">
-        <v>97</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="64"/>
@@ -6289,23 +6296,23 @@
       <c r="AM32" s="5"/>
     </row>
     <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="146"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="169"/>
+      <c r="D33" s="159"/>
       <c r="E33" s="69" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F33" s="70" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G33" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" s="71" t="s">
         <v>95</v>
-      </c>
-      <c r="H33" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="I33" s="71" t="s">
-        <v>97</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="64"/>
@@ -6339,23 +6346,23 @@
       <c r="AM33" s="5"/>
     </row>
     <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="146"/>
+      <c r="B34" s="168"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="169"/>
+      <c r="D34" s="159"/>
       <c r="E34" s="72" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F34" s="73" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G34" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="74" t="s">
         <v>95</v>
-      </c>
-      <c r="H34" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34" s="74" t="s">
-        <v>97</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="64"/>
@@ -6389,23 +6396,23 @@
       <c r="AM34" s="5"/>
     </row>
     <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="146"/>
+      <c r="B35" s="168"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="169"/>
+      <c r="D35" s="159"/>
       <c r="E35" s="69" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" s="70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G35" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="H35" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="71" t="s">
         <v>95</v>
-      </c>
-      <c r="H35" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="I35" s="71" t="s">
-        <v>97</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="64"/>
@@ -6439,23 +6446,23 @@
       <c r="AM35" s="5"/>
     </row>
     <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="146"/>
+      <c r="B36" s="168"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="169"/>
+      <c r="D36" s="159"/>
       <c r="E36" s="75" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G36" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="77" t="s">
         <v>95</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>96</v>
-      </c>
-      <c r="I36" s="77" t="s">
-        <v>97</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="64"/>
@@ -6528,23 +6535,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="145" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="145"/>
-      <c r="H38" s="145"/>
-      <c r="I38" s="145"/>
-      <c r="J38" s="145"/>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="145"/>
-      <c r="N38" s="145"/>
-      <c r="O38" s="145"/>
-      <c r="P38" s="145"/>
-      <c r="Q38" s="145"/>
+      <c r="C38" s="161" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+      <c r="P38" s="161"/>
+      <c r="Q38" s="161"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6576,17 +6583,17 @@
     <row r="39" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D40" s="53" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="2:74" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="G42" s="1">
-        <v>2021</v>
+      <c r="G42" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H42" s="1">
         <v>2022</v>
@@ -6677,17 +6684,17 @@
       </c>
     </row>
     <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="177" t="s">
+      <c r="B43" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="168" t="s">
-        <v>109</v>
+      <c r="D43" s="158" t="s">
+        <v>106</v>
       </c>
       <c r="E43" s="79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F43" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G43" s="81">
         <f>F19*2+F25</f>
@@ -6782,13 +6789,13 @@
       </c>
     </row>
     <row r="44" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B44" s="177"/>
-      <c r="D44" s="169"/>
+      <c r="B44" s="163"/>
+      <c r="D44" s="159"/>
       <c r="E44" s="82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F44" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G44" s="81">
         <f t="shared" ref="G44:G45" si="0">F20*2+F26</f>
@@ -6883,13 +6890,13 @@
       </c>
     </row>
     <row r="45" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B45" s="177"/>
-      <c r="D45" s="169"/>
+      <c r="B45" s="163"/>
+      <c r="D45" s="159"/>
       <c r="E45" s="83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F45" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G45" s="81">
         <f t="shared" si="0"/>
@@ -6984,13 +6991,13 @@
       </c>
     </row>
     <row r="46" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B46" s="177"/>
-      <c r="D46" s="170"/>
+      <c r="B46" s="163"/>
+      <c r="D46" s="160"/>
       <c r="E46" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F46" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G46" s="81">
         <f>F19*4+F25</f>
@@ -7118,13 +7125,13 @@
       <c r="BV46" s="5"/>
     </row>
     <row r="47" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B47" s="177"/>
-      <c r="D47" s="170"/>
+      <c r="B47" s="163"/>
+      <c r="D47" s="160"/>
       <c r="E47" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F47" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G47" s="81">
         <f>F20*4+F26</f>
@@ -7252,13 +7259,13 @@
       <c r="BV47" s="5"/>
     </row>
     <row r="48" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B48" s="177"/>
-      <c r="D48" s="170"/>
+      <c r="B48" s="163"/>
+      <c r="D48" s="160"/>
       <c r="E48" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F48" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G48" s="81">
         <f t="shared" ref="G48" si="1">F21*4+F27</f>
@@ -7386,13 +7393,13 @@
       <c r="BV48" s="5"/>
     </row>
     <row r="49" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B49" s="177"/>
-      <c r="D49" s="170"/>
+      <c r="B49" s="163"/>
+      <c r="D49" s="160"/>
       <c r="E49" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F49" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G49" s="81">
         <f t="shared" ref="G49:G51" si="2">F19*6+F25</f>
@@ -7520,13 +7527,13 @@
       <c r="BV49" s="5"/>
     </row>
     <row r="50" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B50" s="177"/>
-      <c r="D50" s="170"/>
+      <c r="B50" s="163"/>
+      <c r="D50" s="160"/>
       <c r="E50" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F50" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G50" s="81">
         <f t="shared" si="2"/>
@@ -7654,13 +7661,13 @@
       <c r="BV50" s="5"/>
     </row>
     <row r="51" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B51" s="177"/>
-      <c r="D51" s="170"/>
+      <c r="B51" s="163"/>
+      <c r="D51" s="160"/>
       <c r="E51" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F51" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G51" s="81">
         <f t="shared" si="2"/>
@@ -7788,13 +7795,13 @@
       <c r="BV51" s="5"/>
     </row>
     <row r="52" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B52" s="177"/>
-      <c r="D52" s="170"/>
+      <c r="B52" s="163"/>
+      <c r="D52" s="160"/>
       <c r="E52" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F52" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G52" s="81">
         <f t="shared" ref="G52:G54" si="3">F19*8+F25</f>
@@ -7922,13 +7929,13 @@
       <c r="BV52" s="5"/>
     </row>
     <row r="53" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B53" s="177"/>
-      <c r="D53" s="170"/>
+      <c r="B53" s="163"/>
+      <c r="D53" s="160"/>
       <c r="E53" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F53" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G53" s="81">
         <f t="shared" si="3"/>
@@ -8056,13 +8063,13 @@
       <c r="BV53" s="5"/>
     </row>
     <row r="54" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B54" s="177"/>
-      <c r="D54" s="170"/>
+      <c r="B54" s="163"/>
+      <c r="D54" s="160"/>
       <c r="E54" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F54" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G54" s="81">
         <f t="shared" si="3"/>
@@ -8190,13 +8197,13 @@
       <c r="BV54" s="5"/>
     </row>
     <row r="55" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B55" s="177"/>
-      <c r="D55" s="170"/>
+      <c r="B55" s="163"/>
+      <c r="D55" s="160"/>
       <c r="E55" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F55" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G55" s="81">
         <f t="shared" ref="G55:G57" si="4">F19*10+F25</f>
@@ -8324,13 +8331,13 @@
       <c r="BV55" s="5"/>
     </row>
     <row r="56" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B56" s="177"/>
-      <c r="D56" s="170"/>
+      <c r="B56" s="163"/>
+      <c r="D56" s="160"/>
       <c r="E56" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F56" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G56" s="81">
         <f t="shared" si="4"/>
@@ -8458,13 +8465,13 @@
       <c r="BV56" s="5"/>
     </row>
     <row r="57" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B57" s="177"/>
-      <c r="D57" s="170"/>
+      <c r="B57" s="163"/>
+      <c r="D57" s="160"/>
       <c r="E57" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F57" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G57" s="81">
         <f t="shared" si="4"/>
@@ -8592,7 +8599,7 @@
       <c r="BV57" s="5"/>
     </row>
     <row r="58" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B58" s="177"/>
+      <c r="B58" s="163"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8661,7 +8668,7 @@
       <c r="BV58" s="5"/>
     </row>
     <row r="59" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B59" s="177"/>
+      <c r="B59" s="163"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8730,7 +8737,7 @@
       <c r="BV59" s="5"/>
     </row>
     <row r="60" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B60" s="177"/>
+      <c r="B60" s="163"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8799,12 +8806,12 @@
       <c r="BV60" s="5"/>
     </row>
     <row r="61" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B61" s="177"/>
+      <c r="B61" s="163"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
-      <c r="G61" s="1">
-        <v>2021</v>
+      <c r="G61" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H61" s="1">
         <v>2022</v>
@@ -8895,15 +8902,15 @@
       </c>
     </row>
     <row r="62" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B62" s="177"/>
-      <c r="D62" s="168" t="s">
-        <v>110</v>
+      <c r="B62" s="163"/>
+      <c r="D62" s="158" t="s">
+        <v>107</v>
       </c>
       <c r="E62" s="79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F62" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G62" s="81">
         <f t="shared" ref="G62:G70" si="5">0.025*G43</f>
@@ -8998,13 +9005,13 @@
       </c>
     </row>
     <row r="63" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B63" s="177"/>
-      <c r="D63" s="169"/>
+      <c r="B63" s="163"/>
+      <c r="D63" s="159"/>
       <c r="E63" s="82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F63" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G63" s="81">
         <f t="shared" si="5"/>
@@ -9099,13 +9106,13 @@
       </c>
     </row>
     <row r="64" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B64" s="177"/>
-      <c r="D64" s="169"/>
+      <c r="B64" s="163"/>
+      <c r="D64" s="159"/>
       <c r="E64" s="83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F64" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G64" s="81">
         <f t="shared" si="5"/>
@@ -9200,13 +9207,13 @@
       </c>
     </row>
     <row r="65" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B65" s="177"/>
-      <c r="D65" s="170"/>
+      <c r="B65" s="163"/>
+      <c r="D65" s="160"/>
       <c r="E65" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F65" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G65" s="81">
         <f t="shared" si="5"/>
@@ -9301,13 +9308,13 @@
       </c>
     </row>
     <row r="66" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B66" s="177"/>
-      <c r="D66" s="170"/>
+      <c r="B66" s="163"/>
+      <c r="D66" s="160"/>
       <c r="E66" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F66" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G66" s="81">
         <f t="shared" si="5"/>
@@ -9402,13 +9409,13 @@
       </c>
     </row>
     <row r="67" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B67" s="177"/>
-      <c r="D67" s="170"/>
+      <c r="B67" s="163"/>
+      <c r="D67" s="160"/>
       <c r="E67" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F67" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G67" s="81">
         <f t="shared" si="5"/>
@@ -9503,13 +9510,13 @@
       </c>
     </row>
     <row r="68" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B68" s="177"/>
-      <c r="D68" s="170"/>
+      <c r="B68" s="163"/>
+      <c r="D68" s="160"/>
       <c r="E68" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F68" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G68" s="81">
         <f t="shared" si="5"/>
@@ -9604,13 +9611,13 @@
       </c>
     </row>
     <row r="69" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B69" s="177"/>
-      <c r="D69" s="170"/>
+      <c r="B69" s="163"/>
+      <c r="D69" s="160"/>
       <c r="E69" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F69" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G69" s="81">
         <f t="shared" si="5"/>
@@ -9705,13 +9712,13 @@
       </c>
     </row>
     <row r="70" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B70" s="177"/>
-      <c r="D70" s="170"/>
+      <c r="B70" s="163"/>
+      <c r="D70" s="160"/>
       <c r="E70" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F70" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G70" s="81">
         <f t="shared" si="5"/>
@@ -9806,13 +9813,13 @@
       </c>
     </row>
     <row r="71" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B71" s="177"/>
-      <c r="D71" s="170"/>
+      <c r="B71" s="163"/>
+      <c r="D71" s="160"/>
       <c r="E71" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F71" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G71" s="81">
         <f t="shared" ref="G71:G76" si="6">0.025*G52</f>
@@ -9940,13 +9947,13 @@
       <c r="BV71" s="5"/>
     </row>
     <row r="72" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B72" s="177"/>
-      <c r="D72" s="170"/>
+      <c r="B72" s="163"/>
+      <c r="D72" s="160"/>
       <c r="E72" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F72" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G72" s="81">
         <f t="shared" si="6"/>
@@ -10074,13 +10081,13 @@
       <c r="BV72" s="5"/>
     </row>
     <row r="73" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B73" s="177"/>
-      <c r="D73" s="170"/>
+      <c r="B73" s="163"/>
+      <c r="D73" s="160"/>
       <c r="E73" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F73" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G73" s="81">
         <f t="shared" si="6"/>
@@ -10208,13 +10215,13 @@
       <c r="BV73" s="5"/>
     </row>
     <row r="74" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B74" s="177"/>
-      <c r="D74" s="170"/>
+      <c r="B74" s="163"/>
+      <c r="D74" s="160"/>
       <c r="E74" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F74" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G74" s="81">
         <f t="shared" si="6"/>
@@ -10342,13 +10349,13 @@
       <c r="BV74" s="5"/>
     </row>
     <row r="75" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B75" s="177"/>
-      <c r="D75" s="170"/>
+      <c r="B75" s="163"/>
+      <c r="D75" s="160"/>
       <c r="E75" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F75" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G75" s="81">
         <f t="shared" si="6"/>
@@ -10476,13 +10483,13 @@
       <c r="BV75" s="5"/>
     </row>
     <row r="76" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B76" s="177"/>
-      <c r="D76" s="170"/>
+      <c r="B76" s="163"/>
+      <c r="D76" s="160"/>
       <c r="E76" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F76" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G76" s="81">
         <f t="shared" si="6"/>
@@ -10610,18 +10617,18 @@
       <c r="BV76" s="5"/>
     </row>
     <row r="77" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B77" s="177"/>
+      <c r="B77" s="163"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
     <row r="78" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B78" s="177"/>
+      <c r="B78" s="163"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
-      <c r="G78" s="1">
-        <v>2021</v>
+      <c r="G78" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H78" s="1">
         <v>2022</v>
@@ -10712,218 +10719,218 @@
       </c>
     </row>
     <row r="79" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B79" s="177"/>
-      <c r="D79" s="168" t="s">
-        <v>111</v>
+      <c r="B79" s="163"/>
+      <c r="D79" s="158" t="s">
+        <v>108</v>
       </c>
       <c r="E79" s="79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F79" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G79" s="59">
+        <v>0</v>
+      </c>
+      <c r="H79" s="139">
+        <v>0</v>
+      </c>
+      <c r="I79" s="139">
+        <v>0</v>
+      </c>
+      <c r="J79" s="139">
+        <v>0</v>
+      </c>
+      <c r="K79" s="139">
+        <v>0</v>
+      </c>
+      <c r="L79" s="139">
+        <v>0</v>
+      </c>
+      <c r="M79" s="139">
+        <v>0</v>
+      </c>
+      <c r="N79" s="139">
+        <v>0</v>
+      </c>
+      <c r="O79" s="139">
+        <v>0</v>
+      </c>
+      <c r="P79" s="139">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="139">
+        <v>0</v>
+      </c>
+      <c r="R79" s="139">
+        <v>0</v>
+      </c>
+      <c r="S79" s="139">
+        <v>0</v>
+      </c>
+      <c r="T79" s="139">
+        <v>0</v>
+      </c>
+      <c r="U79" s="139">
+        <v>0</v>
+      </c>
+      <c r="V79" s="139">
+        <v>0</v>
+      </c>
+      <c r="W79" s="139">
+        <v>0</v>
+      </c>
+      <c r="X79" s="139">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="139">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="139">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="1"/>
+    </row>
+    <row r="80" spans="2:74" x14ac:dyDescent="0.25">
+      <c r="B80" s="163"/>
+      <c r="D80" s="159"/>
+      <c r="E80" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="F80" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G80" s="59">
+        <v>0</v>
+      </c>
+      <c r="H80" s="139">
+        <v>0</v>
+      </c>
+      <c r="I80" s="139">
+        <v>0</v>
+      </c>
+      <c r="J80" s="139">
+        <v>0</v>
+      </c>
+      <c r="K80" s="139">
+        <v>0</v>
+      </c>
+      <c r="L80" s="139">
+        <v>0</v>
+      </c>
+      <c r="M80" s="139">
+        <v>0</v>
+      </c>
+      <c r="N80" s="139">
+        <v>0</v>
+      </c>
+      <c r="O80" s="139">
+        <v>0</v>
+      </c>
+      <c r="P80" s="139">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="139">
+        <v>0</v>
+      </c>
+      <c r="R80" s="139">
+        <v>0</v>
+      </c>
+      <c r="S80" s="139">
+        <v>0</v>
+      </c>
+      <c r="T80" s="139">
+        <v>0</v>
+      </c>
+      <c r="U80" s="139">
+        <v>0</v>
+      </c>
+      <c r="V80" s="139">
+        <v>0</v>
+      </c>
+      <c r="W80" s="139">
+        <v>0</v>
+      </c>
+      <c r="X80" s="139">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="139">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="139">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="1"/>
+    </row>
+    <row r="81" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B81" s="163"/>
+      <c r="D81" s="159"/>
+      <c r="E81" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G79" s="59">
-        <v>0</v>
-      </c>
-      <c r="H79" s="139">
-        <v>0</v>
-      </c>
-      <c r="I79" s="139">
-        <v>0</v>
-      </c>
-      <c r="J79" s="139">
-        <v>0</v>
-      </c>
-      <c r="K79" s="139">
-        <v>0</v>
-      </c>
-      <c r="L79" s="139">
-        <v>0</v>
-      </c>
-      <c r="M79" s="139">
-        <v>0</v>
-      </c>
-      <c r="N79" s="139">
-        <v>0</v>
-      </c>
-      <c r="O79" s="139">
-        <v>0</v>
-      </c>
-      <c r="P79" s="139">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="139">
-        <v>0</v>
-      </c>
-      <c r="R79" s="139">
-        <v>0</v>
-      </c>
-      <c r="S79" s="139">
-        <v>0</v>
-      </c>
-      <c r="T79" s="139">
-        <v>0</v>
-      </c>
-      <c r="U79" s="139">
-        <v>0</v>
-      </c>
-      <c r="V79" s="139">
-        <v>0</v>
-      </c>
-      <c r="W79" s="139">
-        <v>0</v>
-      </c>
-      <c r="X79" s="139">
-        <v>0</v>
-      </c>
-      <c r="Y79" s="139">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AC79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AD79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AH79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AI79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AJ79" s="139">
-        <v>0</v>
-      </c>
-      <c r="AO79" s="1"/>
-    </row>
-    <row r="80" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B80" s="177"/>
-      <c r="D80" s="169"/>
-      <c r="E80" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="F80" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G80" s="59">
-        <v>0</v>
-      </c>
-      <c r="H80" s="139">
-        <v>0</v>
-      </c>
-      <c r="I80" s="139">
-        <v>0</v>
-      </c>
-      <c r="J80" s="139">
-        <v>0</v>
-      </c>
-      <c r="K80" s="139">
-        <v>0</v>
-      </c>
-      <c r="L80" s="139">
-        <v>0</v>
-      </c>
-      <c r="M80" s="139">
-        <v>0</v>
-      </c>
-      <c r="N80" s="139">
-        <v>0</v>
-      </c>
-      <c r="O80" s="139">
-        <v>0</v>
-      </c>
-      <c r="P80" s="139">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="139">
-        <v>0</v>
-      </c>
-      <c r="R80" s="139">
-        <v>0</v>
-      </c>
-      <c r="S80" s="139">
-        <v>0</v>
-      </c>
-      <c r="T80" s="139">
-        <v>0</v>
-      </c>
-      <c r="U80" s="139">
-        <v>0</v>
-      </c>
-      <c r="V80" s="139">
-        <v>0</v>
-      </c>
-      <c r="W80" s="139">
-        <v>0</v>
-      </c>
-      <c r="X80" s="139">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="139">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AI80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="139">
-        <v>0</v>
-      </c>
-      <c r="AO80" s="1"/>
-    </row>
-    <row r="81" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B81" s="177"/>
-      <c r="D81" s="169"/>
-      <c r="E81" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="F81" s="80" t="s">
-        <v>84</v>
-      </c>
       <c r="G81" s="59">
         <v>0</v>
       </c>
@@ -11017,213 +11024,213 @@
       <c r="AO81" s="1"/>
     </row>
     <row r="82" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B82" s="178"/>
-      <c r="D82" s="170"/>
+      <c r="B82" s="164"/>
+      <c r="D82" s="160"/>
       <c r="E82" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F82" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G82" s="59">
+        <v>0</v>
+      </c>
+      <c r="H82" s="139">
+        <v>0</v>
+      </c>
+      <c r="I82" s="139">
+        <v>0</v>
+      </c>
+      <c r="J82" s="139">
+        <v>0</v>
+      </c>
+      <c r="K82" s="139">
+        <v>0</v>
+      </c>
+      <c r="L82" s="139">
+        <v>0</v>
+      </c>
+      <c r="M82" s="139">
+        <v>0</v>
+      </c>
+      <c r="N82" s="139">
+        <v>0</v>
+      </c>
+      <c r="O82" s="139">
+        <v>0</v>
+      </c>
+      <c r="P82" s="139">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="139">
+        <v>0</v>
+      </c>
+      <c r="R82" s="139">
+        <v>0</v>
+      </c>
+      <c r="S82" s="139">
+        <v>0</v>
+      </c>
+      <c r="T82" s="139">
+        <v>0</v>
+      </c>
+      <c r="U82" s="139">
+        <v>0</v>
+      </c>
+      <c r="V82" s="139">
+        <v>0</v>
+      </c>
+      <c r="W82" s="139">
+        <v>0</v>
+      </c>
+      <c r="X82" s="139">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="139">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="139">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B83" s="164"/>
+      <c r="D83" s="160"/>
+      <c r="E83" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="F83" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G83" s="59">
+        <v>0</v>
+      </c>
+      <c r="H83" s="139">
+        <v>0</v>
+      </c>
+      <c r="I83" s="139">
+        <v>0</v>
+      </c>
+      <c r="J83" s="139">
+        <v>0</v>
+      </c>
+      <c r="K83" s="139">
+        <v>0</v>
+      </c>
+      <c r="L83" s="139">
+        <v>0</v>
+      </c>
+      <c r="M83" s="139">
+        <v>0</v>
+      </c>
+      <c r="N83" s="139">
+        <v>0</v>
+      </c>
+      <c r="O83" s="139">
+        <v>0</v>
+      </c>
+      <c r="P83" s="139">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="139">
+        <v>0</v>
+      </c>
+      <c r="R83" s="139">
+        <v>0</v>
+      </c>
+      <c r="S83" s="139">
+        <v>0</v>
+      </c>
+      <c r="T83" s="139">
+        <v>0</v>
+      </c>
+      <c r="U83" s="139">
+        <v>0</v>
+      </c>
+      <c r="V83" s="139">
+        <v>0</v>
+      </c>
+      <c r="W83" s="139">
+        <v>0</v>
+      </c>
+      <c r="X83" s="139">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="139">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="139">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="B84" s="164"/>
+      <c r="D84" s="160"/>
+      <c r="E84" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="F84" s="80" t="s">
         <v>82</v>
-      </c>
-      <c r="G82" s="59">
-        <v>0</v>
-      </c>
-      <c r="H82" s="139">
-        <v>0</v>
-      </c>
-      <c r="I82" s="139">
-        <v>0</v>
-      </c>
-      <c r="J82" s="139">
-        <v>0</v>
-      </c>
-      <c r="K82" s="139">
-        <v>0</v>
-      </c>
-      <c r="L82" s="139">
-        <v>0</v>
-      </c>
-      <c r="M82" s="139">
-        <v>0</v>
-      </c>
-      <c r="N82" s="139">
-        <v>0</v>
-      </c>
-      <c r="O82" s="139">
-        <v>0</v>
-      </c>
-      <c r="P82" s="139">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="139">
-        <v>0</v>
-      </c>
-      <c r="R82" s="139">
-        <v>0</v>
-      </c>
-      <c r="S82" s="139">
-        <v>0</v>
-      </c>
-      <c r="T82" s="139">
-        <v>0</v>
-      </c>
-      <c r="U82" s="139">
-        <v>0</v>
-      </c>
-      <c r="V82" s="139">
-        <v>0</v>
-      </c>
-      <c r="W82" s="139">
-        <v>0</v>
-      </c>
-      <c r="X82" s="139">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="139">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AC82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AD82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AG82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AH82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AI82" s="139">
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B83" s="178"/>
-      <c r="D83" s="170"/>
-      <c r="E83" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="F83" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G83" s="59">
-        <v>0</v>
-      </c>
-      <c r="H83" s="139">
-        <v>0</v>
-      </c>
-      <c r="I83" s="139">
-        <v>0</v>
-      </c>
-      <c r="J83" s="139">
-        <v>0</v>
-      </c>
-      <c r="K83" s="139">
-        <v>0</v>
-      </c>
-      <c r="L83" s="139">
-        <v>0</v>
-      </c>
-      <c r="M83" s="139">
-        <v>0</v>
-      </c>
-      <c r="N83" s="139">
-        <v>0</v>
-      </c>
-      <c r="O83" s="139">
-        <v>0</v>
-      </c>
-      <c r="P83" s="139">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="139">
-        <v>0</v>
-      </c>
-      <c r="R83" s="139">
-        <v>0</v>
-      </c>
-      <c r="S83" s="139">
-        <v>0</v>
-      </c>
-      <c r="T83" s="139">
-        <v>0</v>
-      </c>
-      <c r="U83" s="139">
-        <v>0</v>
-      </c>
-      <c r="V83" s="139">
-        <v>0</v>
-      </c>
-      <c r="W83" s="139">
-        <v>0</v>
-      </c>
-      <c r="X83" s="139">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="139">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AI83" s="139">
-        <v>0</v>
-      </c>
-      <c r="AJ83" s="139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B84" s="178"/>
-      <c r="D84" s="170"/>
-      <c r="E84" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="F84" s="80" t="s">
-        <v>84</v>
       </c>
       <c r="G84" s="59">
         <v>0</v>
@@ -11319,13 +11326,13 @@
       <c r="AL84" s="5"/>
     </row>
     <row r="85" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B85" s="178"/>
-      <c r="D85" s="170"/>
+      <c r="B85" s="164"/>
+      <c r="D85" s="160"/>
       <c r="E85" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F85" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G85" s="59">
         <v>0</v>
@@ -11421,13 +11428,13 @@
       <c r="AL85" s="5"/>
     </row>
     <row r="86" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B86" s="178"/>
-      <c r="D86" s="170"/>
+      <c r="B86" s="164"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F86" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G86" s="59">
         <v>0</v>
@@ -11523,13 +11530,13 @@
       <c r="AL86" s="5"/>
     </row>
     <row r="87" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B87" s="178"/>
-      <c r="D87" s="170"/>
+      <c r="B87" s="164"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F87" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G87" s="59">
         <v>0</v>
@@ -11625,13 +11632,13 @@
       <c r="AL87" s="5"/>
     </row>
     <row r="88" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B88" s="178"/>
-      <c r="D88" s="170"/>
+      <c r="B88" s="164"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F88" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G88" s="59">
         <v>0</v>
@@ -11727,13 +11734,13 @@
       <c r="AL88" s="5"/>
     </row>
     <row r="89" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B89" s="178"/>
-      <c r="D89" s="170"/>
+      <c r="B89" s="164"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F89" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G89" s="59">
         <v>0</v>
@@ -11829,13 +11836,13 @@
       <c r="AL89" s="5"/>
     </row>
     <row r="90" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B90" s="178"/>
-      <c r="D90" s="170"/>
+      <c r="B90" s="164"/>
+      <c r="D90" s="160"/>
       <c r="E90" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F90" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G90" s="59">
         <v>0</v>
@@ -11931,13 +11938,13 @@
       <c r="AL90" s="5"/>
     </row>
     <row r="91" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B91" s="178"/>
-      <c r="D91" s="170"/>
+      <c r="B91" s="164"/>
+      <c r="D91" s="160"/>
       <c r="E91" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F91" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G91" s="59">
         <v>0</v>
@@ -12033,13 +12040,13 @@
       <c r="AL91" s="5"/>
     </row>
     <row r="92" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B92" s="178"/>
-      <c r="D92" s="170"/>
+      <c r="B92" s="164"/>
+      <c r="D92" s="160"/>
       <c r="E92" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F92" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G92" s="59">
         <v>0</v>
@@ -12135,13 +12142,13 @@
       <c r="AL92" s="5"/>
     </row>
     <row r="93" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B93" s="178"/>
-      <c r="D93" s="170"/>
+      <c r="B93" s="164"/>
+      <c r="D93" s="160"/>
       <c r="E93" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F93" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G93" s="59">
         <v>0</v>
@@ -12237,12 +12244,12 @@
       <c r="AL93" s="5"/>
     </row>
     <row r="94" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B94" s="178"/>
+      <c r="B94" s="164"/>
     </row>
     <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="178"/>
-      <c r="G95" s="1">
-        <v>2021</v>
+      <c r="B95" s="164"/>
+      <c r="G95" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H95" s="1">
         <v>2022</v>
@@ -12333,216 +12340,216 @@
       </c>
     </row>
     <row r="96" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B96" s="178"/>
-      <c r="D96" s="168" t="s">
-        <v>112</v>
+      <c r="B96" s="164"/>
+      <c r="D96" s="158" t="s">
+        <v>109</v>
       </c>
       <c r="E96" s="79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F96" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G96" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI96" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ96" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="97" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B97" s="164"/>
+      <c r="D97" s="159"/>
+      <c r="E97" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G97" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI97" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ97" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="98" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B98" s="164"/>
+      <c r="D98" s="159"/>
+      <c r="E98" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F98" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G96" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI96" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ96" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="97" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B97" s="178"/>
-      <c r="D97" s="169"/>
-      <c r="E97" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="F97" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G97" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI97" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ97" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="98" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B98" s="178"/>
-      <c r="D98" s="169"/>
-      <c r="E98" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="F98" s="80" t="s">
-        <v>84</v>
-      </c>
       <c r="G98" s="86">
         <v>0.85</v>
       </c>
@@ -12635,1114 +12642,1114 @@
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B99" s="178"/>
-      <c r="D99" s="170"/>
+      <c r="B99" s="164"/>
+      <c r="D99" s="160"/>
       <c r="E99" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="F99" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G99" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI99" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ99" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="100" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B100" s="164"/>
+      <c r="D100" s="160"/>
+      <c r="E100" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="F100" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G100" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI100" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ100" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="101" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B101" s="164"/>
+      <c r="D101" s="160"/>
+      <c r="E101" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="F101" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="G101" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI101" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ101" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="102" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B102" s="164"/>
+      <c r="D102" s="160"/>
+      <c r="E102" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="F99" s="80" t="s">
+      <c r="F102" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G102" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI102" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ102" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="103" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B103" s="164"/>
+      <c r="D103" s="160"/>
+      <c r="E103" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="F103" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G103" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI103" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ103" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="104" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B104" s="164"/>
+      <c r="D104" s="160"/>
+      <c r="E104" s="79" t="s">
+        <v>98</v>
+      </c>
+      <c r="F104" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G99" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI99" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ99" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="100" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B100" s="178"/>
-      <c r="D100" s="170"/>
-      <c r="E100" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="F100" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G100" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI100" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ100" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="101" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B101" s="178"/>
-      <c r="D101" s="170"/>
-      <c r="E101" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="F101" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="G101" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI101" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ101" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="102" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B102" s="178"/>
-      <c r="D102" s="170"/>
-      <c r="E102" s="79" t="s">
+      <c r="G104" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI104" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ104" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="105" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B105" s="164"/>
+      <c r="D105" s="160"/>
+      <c r="E105" s="79" t="s">
         <v>100</v>
       </c>
-      <c r="F102" s="80" t="s">
+      <c r="F105" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G105" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI105" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ105" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="106" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B106" s="164"/>
+      <c r="D106" s="160"/>
+      <c r="E106" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="F106" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G106" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI106" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ106" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="107" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B107" s="164"/>
+      <c r="D107" s="160"/>
+      <c r="E107" s="79" t="s">
+        <v>100</v>
+      </c>
+      <c r="F107" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G102" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI102" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ102" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="103" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B103" s="178"/>
-      <c r="D103" s="170"/>
-      <c r="E103" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="F103" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G103" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI103" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ103" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="104" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B104" s="178"/>
-      <c r="D104" s="170"/>
-      <c r="E104" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="F104" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="G104" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI104" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ104" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="105" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B105" s="178"/>
-      <c r="D105" s="170"/>
-      <c r="E105" s="79" t="s">
+      <c r="G107" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI107" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ107" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="108" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B108" s="164"/>
+      <c r="D108" s="160"/>
+      <c r="E108" s="79" t="s">
         <v>102</v>
       </c>
-      <c r="F105" s="80" t="s">
+      <c r="F108" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G108" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI108" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ108" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="109" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B109" s="164"/>
+      <c r="D109" s="160"/>
+      <c r="E109" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F109" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="G109" s="86">
+        <v>0.85</v>
+      </c>
+      <c r="H109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="I109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="J109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="K109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="L109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="M109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="N109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="O109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="P109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Q109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="R109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="S109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="T109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="U109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="V109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="W109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="X109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Y109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="Z109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AA109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AB109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AC109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AD109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AE109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AF109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AG109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AH109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AI109" s="141">
+        <v>0.85</v>
+      </c>
+      <c r="AJ109" s="141">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="110" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B110" s="164"/>
+      <c r="D110" s="160"/>
+      <c r="E110" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F110" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="G105" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI105" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ105" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="106" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B106" s="178"/>
-      <c r="D106" s="170"/>
-      <c r="E106" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="F106" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G106" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI106" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ106" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="107" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B107" s="178"/>
-      <c r="D107" s="170"/>
-      <c r="E107" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="F107" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="G107" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI107" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ107" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="108" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B108" s="178"/>
-      <c r="D108" s="170"/>
-      <c r="E108" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="F108" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="G108" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI108" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ108" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="109" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B109" s="178"/>
-      <c r="D109" s="170"/>
-      <c r="E109" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="F109" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="G109" s="86">
-        <v>0.85</v>
-      </c>
-      <c r="H109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="I109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="J109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="K109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="L109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="M109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="N109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="O109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="P109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Q109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="R109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="S109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="T109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="U109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="V109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="W109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="X109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Y109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="Z109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AA109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AB109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AC109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AD109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AE109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AF109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AG109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AH109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AI109" s="141">
-        <v>0.85</v>
-      </c>
-      <c r="AJ109" s="141">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="110" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B110" s="178"/>
-      <c r="D110" s="170"/>
-      <c r="E110" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="F110" s="80" t="s">
-        <v>84</v>
-      </c>
       <c r="G110" s="86">
         <v>0.85</v>
       </c>
@@ -13835,12 +13842,12 @@
       </c>
     </row>
     <row r="111" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B111" s="178"/>
+      <c r="B111" s="164"/>
     </row>
     <row r="112" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B112" s="178"/>
-      <c r="G112" s="1">
-        <v>2021</v>
+      <c r="B112" s="164"/>
+      <c r="G112" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="H112" s="1">
         <v>2022</v>
@@ -13931,15 +13938,15 @@
       </c>
     </row>
     <row r="113" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B113" s="178"/>
-      <c r="D113" s="168" t="s">
-        <v>113</v>
+      <c r="B113" s="164"/>
+      <c r="D113" s="158" t="s">
+        <v>110</v>
       </c>
       <c r="E113" s="79" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F113" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G113" s="86">
         <f>2/24</f>
@@ -14034,13 +14041,13 @@
       </c>
     </row>
     <row r="114" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B114" s="178"/>
-      <c r="D114" s="169"/>
+      <c r="B114" s="164"/>
+      <c r="D114" s="159"/>
       <c r="E114" s="82" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F114" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G114" s="86">
         <f t="shared" ref="G114:G115" si="7">2/24</f>
@@ -14135,13 +14142,13 @@
       </c>
     </row>
     <row r="115" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B115" s="178"/>
-      <c r="D115" s="169"/>
+      <c r="B115" s="164"/>
+      <c r="D115" s="159"/>
       <c r="E115" s="83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F115" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G115" s="86">
         <f t="shared" si="7"/>
@@ -14236,13 +14243,13 @@
       </c>
     </row>
     <row r="116" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B116" s="178"/>
-      <c r="D116" s="170"/>
+      <c r="B116" s="164"/>
+      <c r="D116" s="160"/>
       <c r="E116" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F116" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G116" s="86">
         <f>4/24</f>
@@ -14337,13 +14344,13 @@
       </c>
     </row>
     <row r="117" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B117" s="178"/>
-      <c r="D117" s="170"/>
+      <c r="B117" s="164"/>
+      <c r="D117" s="160"/>
       <c r="E117" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F117" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G117" s="86">
         <f t="shared" ref="G117:G118" si="8">4/24</f>
@@ -14438,13 +14445,13 @@
       </c>
     </row>
     <row r="118" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B118" s="178"/>
-      <c r="D118" s="170"/>
+      <c r="B118" s="164"/>
+      <c r="D118" s="160"/>
       <c r="E118" s="79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F118" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G118" s="86">
         <f t="shared" si="8"/>
@@ -14539,13 +14546,13 @@
       </c>
     </row>
     <row r="119" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B119" s="178"/>
-      <c r="D119" s="170"/>
+      <c r="B119" s="164"/>
+      <c r="D119" s="160"/>
       <c r="E119" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F119" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G119" s="86">
         <f>6/24</f>
@@ -14640,13 +14647,13 @@
       </c>
     </row>
     <row r="120" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B120" s="178"/>
-      <c r="D120" s="170"/>
+      <c r="B120" s="164"/>
+      <c r="D120" s="160"/>
       <c r="E120" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F120" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G120" s="86">
         <f t="shared" ref="G120:G121" si="9">6/24</f>
@@ -14741,13 +14748,13 @@
       </c>
     </row>
     <row r="121" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B121" s="178"/>
-      <c r="D121" s="170"/>
+      <c r="B121" s="164"/>
+      <c r="D121" s="160"/>
       <c r="E121" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F121" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G121" s="86">
         <f t="shared" si="9"/>
@@ -14842,13 +14849,13 @@
       </c>
     </row>
     <row r="122" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B122" s="178"/>
-      <c r="D122" s="170"/>
+      <c r="B122" s="164"/>
+      <c r="D122" s="160"/>
       <c r="E122" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F122" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G122" s="86">
         <f>8/24</f>
@@ -14943,13 +14950,13 @@
       </c>
     </row>
     <row r="123" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B123" s="178"/>
-      <c r="D123" s="170"/>
+      <c r="B123" s="164"/>
+      <c r="D123" s="160"/>
       <c r="E123" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F123" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G123" s="86">
         <f t="shared" ref="G123:G124" si="10">8/24</f>
@@ -15044,13 +15051,13 @@
       </c>
     </row>
     <row r="124" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B124" s="178"/>
-      <c r="D124" s="170"/>
+      <c r="B124" s="164"/>
+      <c r="D124" s="160"/>
       <c r="E124" s="79" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F124" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G124" s="86">
         <f t="shared" si="10"/>
@@ -15145,13 +15152,13 @@
       </c>
     </row>
     <row r="125" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B125" s="178"/>
-      <c r="D125" s="170"/>
+      <c r="B125" s="164"/>
+      <c r="D125" s="160"/>
       <c r="E125" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F125" s="80" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G125" s="86">
         <f>10/24</f>
@@ -15246,13 +15253,13 @@
       </c>
     </row>
     <row r="126" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B126" s="178"/>
-      <c r="D126" s="170"/>
+      <c r="B126" s="164"/>
+      <c r="D126" s="160"/>
       <c r="E126" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F126" s="80" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G126" s="86">
         <f t="shared" ref="G126:G127" si="11">10/24</f>
@@ -15347,13 +15354,13 @@
       </c>
     </row>
     <row r="127" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B127" s="178"/>
-      <c r="D127" s="170"/>
+      <c r="B127" s="164"/>
+      <c r="D127" s="160"/>
       <c r="E127" s="79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F127" s="80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G127" s="86">
         <f t="shared" si="11"/>
@@ -15451,23 +15458,23 @@
       <c r="B128" s="87"/>
     </row>
     <row r="129" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B129" s="171" t="s">
-        <v>114</v>
-      </c>
-      <c r="C129" s="145"/>
-      <c r="D129" s="145"/>
-      <c r="E129" s="145"/>
-      <c r="F129" s="145"/>
-      <c r="G129" s="145"/>
-      <c r="H129" s="145"/>
-      <c r="I129" s="145"/>
-      <c r="J129" s="145"/>
-      <c r="K129" s="145"/>
-      <c r="L129" s="145"/>
-      <c r="M129" s="145"/>
-      <c r="N129" s="145"/>
-      <c r="O129" s="145"/>
-      <c r="P129" s="145"/>
+      <c r="B129" s="162" t="s">
+        <v>111</v>
+      </c>
+      <c r="C129" s="161"/>
+      <c r="D129" s="161"/>
+      <c r="E129" s="161"/>
+      <c r="F129" s="161"/>
+      <c r="G129" s="161"/>
+      <c r="H129" s="161"/>
+      <c r="I129" s="161"/>
+      <c r="J129" s="161"/>
+      <c r="K129" s="161"/>
+      <c r="L129" s="161"/>
+      <c r="M129" s="161"/>
+      <c r="N129" s="161"/>
+      <c r="O129" s="161"/>
+      <c r="P129" s="161"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15502,26 +15509,26 @@
     </row>
     <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="40"/>
-      <c r="C131" s="172" t="s">
+      <c r="C131" s="152" t="s">
+        <v>112</v>
+      </c>
+      <c r="D131" s="153"/>
+      <c r="E131" s="153"/>
+      <c r="F131" s="153"/>
+      <c r="G131" s="153"/>
+      <c r="H131" s="153"/>
+      <c r="I131" s="155" t="s">
+        <v>113</v>
+      </c>
+      <c r="J131" s="156"/>
+      <c r="K131" s="156"/>
+      <c r="L131" s="156"/>
+      <c r="M131" s="157"/>
+      <c r="N131" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="O131" s="90" t="s">
         <v>115</v>
-      </c>
-      <c r="D131" s="173"/>
-      <c r="E131" s="173"/>
-      <c r="F131" s="173"/>
-      <c r="G131" s="173"/>
-      <c r="H131" s="173"/>
-      <c r="I131" s="174" t="s">
-        <v>116</v>
-      </c>
-      <c r="J131" s="175"/>
-      <c r="K131" s="175"/>
-      <c r="L131" s="175"/>
-      <c r="M131" s="176"/>
-      <c r="N131" s="89" t="s">
-        <v>117</v>
-      </c>
-      <c r="O131" s="90" t="s">
-        <v>118</v>
       </c>
       <c r="P131" s="91"/>
       <c r="Q131" s="91"/>
@@ -15534,16 +15541,16 @@
     </row>
     <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="40"/>
-      <c r="C132" s="162" t="s">
-        <v>119</v>
-      </c>
-      <c r="D132" s="163"/>
-      <c r="E132" s="163"/>
-      <c r="F132" s="163"/>
-      <c r="G132" s="163"/>
-      <c r="H132" s="164"/>
+      <c r="C132" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132" s="143"/>
+      <c r="E132" s="143"/>
+      <c r="F132" s="143"/>
+      <c r="G132" s="143"/>
+      <c r="H132" s="144"/>
       <c r="I132" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M132" s="96"/>
       <c r="N132" s="97"/>
@@ -15552,16 +15559,16 @@
     </row>
     <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="40"/>
-      <c r="C133" s="162" t="s">
-        <v>120</v>
-      </c>
-      <c r="D133" s="163"/>
-      <c r="E133" s="163"/>
-      <c r="F133" s="163"/>
-      <c r="G133" s="163"/>
-      <c r="H133" s="164"/>
+      <c r="C133" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="D133" s="143"/>
+      <c r="E133" s="143"/>
+      <c r="F133" s="143"/>
+      <c r="G133" s="143"/>
+      <c r="H133" s="144"/>
       <c r="I133" s="100" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J133" s="101"/>
       <c r="K133" s="101"/>
@@ -15570,7 +15577,7 @@
       <c r="N133" s="103"/>
       <c r="O133" s="103"/>
       <c r="P133" s="101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q133" s="101"/>
       <c r="R133" s="101"/>
@@ -15582,21 +15589,21 @@
     </row>
     <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="40"/>
-      <c r="C134" s="162" t="s">
-        <v>109</v>
-      </c>
-      <c r="D134" s="163"/>
-      <c r="E134" s="163"/>
-      <c r="F134" s="163"/>
-      <c r="G134" s="163"/>
-      <c r="H134" s="164"/>
-      <c r="I134" s="165" t="s">
-        <v>122</v>
-      </c>
-      <c r="J134" s="166"/>
-      <c r="K134" s="166"/>
-      <c r="L134" s="166"/>
-      <c r="M134" s="167"/>
+      <c r="C134" s="142" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" s="143"/>
+      <c r="E134" s="143"/>
+      <c r="F134" s="143"/>
+      <c r="G134" s="143"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="148" t="s">
+        <v>119</v>
+      </c>
+      <c r="J134" s="149"/>
+      <c r="K134" s="149"/>
+      <c r="L134" s="149"/>
+      <c r="M134" s="150"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15610,21 +15617,21 @@
     </row>
     <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="40"/>
-      <c r="C135" s="162" t="s">
-        <v>123</v>
-      </c>
-      <c r="D135" s="163"/>
-      <c r="E135" s="163"/>
-      <c r="F135" s="163"/>
-      <c r="G135" s="163"/>
-      <c r="H135" s="164"/>
-      <c r="I135" s="165" t="s">
-        <v>124</v>
-      </c>
-      <c r="J135" s="166"/>
-      <c r="K135" s="166"/>
-      <c r="L135" s="166"/>
-      <c r="M135" s="167"/>
+      <c r="C135" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" s="143"/>
+      <c r="E135" s="143"/>
+      <c r="F135" s="143"/>
+      <c r="G135" s="143"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="148" t="s">
+        <v>121</v>
+      </c>
+      <c r="J135" s="149"/>
+      <c r="K135" s="149"/>
+      <c r="L135" s="149"/>
+      <c r="M135" s="150"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15638,16 +15645,16 @@
     </row>
     <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="40"/>
-      <c r="C136" s="162" t="s">
-        <v>125</v>
-      </c>
-      <c r="D136" s="163"/>
-      <c r="E136" s="163"/>
-      <c r="F136" s="163"/>
-      <c r="G136" s="163"/>
-      <c r="H136" s="164"/>
+      <c r="C136" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" s="143"/>
+      <c r="E136" s="143"/>
+      <c r="F136" s="143"/>
+      <c r="G136" s="143"/>
+      <c r="H136" s="144"/>
       <c r="I136" s="108" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J136" s="109"/>
       <c r="K136" s="109"/>
@@ -15666,16 +15673,16 @@
     </row>
     <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="40"/>
-      <c r="C137" s="179" t="s">
-        <v>126</v>
-      </c>
-      <c r="D137" s="180"/>
-      <c r="E137" s="180"/>
-      <c r="F137" s="180"/>
-      <c r="G137" s="180"/>
-      <c r="H137" s="181"/>
+      <c r="C137" s="145" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" s="146"/>
+      <c r="E137" s="146"/>
+      <c r="F137" s="146"/>
+      <c r="G137" s="146"/>
+      <c r="H137" s="147"/>
       <c r="I137" s="112" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J137" s="113"/>
       <c r="K137" s="113"/>
@@ -15694,12 +15701,12 @@
     </row>
     <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="40"/>
-      <c r="C138" s="182"/>
-      <c r="D138" s="182"/>
-      <c r="E138" s="182"/>
-      <c r="F138" s="182"/>
-      <c r="G138" s="182"/>
-      <c r="H138" s="182"/>
+      <c r="C138" s="151"/>
+      <c r="D138" s="151"/>
+      <c r="E138" s="151"/>
+      <c r="F138" s="151"/>
+      <c r="G138" s="151"/>
+      <c r="H138" s="151"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15718,26 +15725,26 @@
     </row>
     <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" s="40"/>
-      <c r="C139" s="172" t="s">
-        <v>127</v>
-      </c>
-      <c r="D139" s="173"/>
-      <c r="E139" s="173"/>
-      <c r="F139" s="173"/>
-      <c r="G139" s="173"/>
-      <c r="H139" s="183"/>
-      <c r="I139" s="174" t="s">
-        <v>116</v>
-      </c>
-      <c r="J139" s="175"/>
-      <c r="K139" s="175"/>
-      <c r="L139" s="175"/>
-      <c r="M139" s="176"/>
+      <c r="C139" s="152" t="s">
+        <v>124</v>
+      </c>
+      <c r="D139" s="153"/>
+      <c r="E139" s="153"/>
+      <c r="F139" s="153"/>
+      <c r="G139" s="153"/>
+      <c r="H139" s="154"/>
+      <c r="I139" s="155" t="s">
+        <v>113</v>
+      </c>
+      <c r="J139" s="156"/>
+      <c r="K139" s="156"/>
+      <c r="L139" s="156"/>
+      <c r="M139" s="157"/>
       <c r="N139" s="89" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O139" s="89" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P139" s="118"/>
       <c r="Q139" s="119"/>
@@ -15750,16 +15757,16 @@
     </row>
     <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="40"/>
-      <c r="C140" s="162" t="s">
-        <v>120</v>
-      </c>
-      <c r="D140" s="163"/>
-      <c r="E140" s="163"/>
-      <c r="F140" s="163"/>
-      <c r="G140" s="163"/>
-      <c r="H140" s="164"/>
+      <c r="C140" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="D140" s="143"/>
+      <c r="E140" s="143"/>
+      <c r="F140" s="143"/>
+      <c r="G140" s="143"/>
+      <c r="H140" s="144"/>
       <c r="I140" s="100" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J140" s="101"/>
       <c r="K140" s="101"/>
@@ -15768,7 +15775,7 @@
       <c r="N140" s="103"/>
       <c r="O140" s="103"/>
       <c r="P140" s="101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q140" s="101"/>
       <c r="R140" s="101"/>
@@ -15781,7 +15788,7 @@
     <row r="141" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B141" s="40"/>
       <c r="C141" s="93" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D141" s="94"/>
       <c r="E141" s="94"/>
@@ -15789,7 +15796,7 @@
       <c r="G141" s="94"/>
       <c r="H141" s="95"/>
       <c r="I141" s="122" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J141" s="123"/>
       <c r="K141" s="123"/>
@@ -15808,7 +15815,7 @@
     </row>
     <row r="142" spans="2:28" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="93" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D142" s="94"/>
       <c r="E142" s="94"/>
@@ -15816,7 +15823,7 @@
       <c r="G142" s="94"/>
       <c r="H142" s="95"/>
       <c r="I142" s="127" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J142" s="127"/>
       <c r="K142" s="127"/>
@@ -15824,7 +15831,7 @@
       <c r="M142" s="127"/>
       <c r="O142" s="128"/>
       <c r="P142" s="129" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q142" s="94"/>
       <c r="R142" s="95"/>
@@ -15841,16 +15848,16 @@
     </row>
     <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" s="40"/>
-      <c r="C143" s="162" t="s">
-        <v>123</v>
-      </c>
-      <c r="D143" s="163"/>
-      <c r="E143" s="163"/>
-      <c r="F143" s="163"/>
-      <c r="G143" s="163"/>
-      <c r="H143" s="164"/>
+      <c r="C143" s="142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D143" s="143"/>
+      <c r="E143" s="143"/>
+      <c r="F143" s="143"/>
+      <c r="G143" s="143"/>
+      <c r="H143" s="144"/>
       <c r="I143" s="122" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J143" s="131"/>
       <c r="K143" s="131"/>
@@ -15869,16 +15876,16 @@
     </row>
     <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" s="40"/>
-      <c r="C144" s="162" t="s">
+      <c r="C144" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" s="143"/>
+      <c r="E144" s="143"/>
+      <c r="F144" s="143"/>
+      <c r="G144" s="143"/>
+      <c r="H144" s="144"/>
+      <c r="I144" s="122" t="s">
         <v>125</v>
-      </c>
-      <c r="D144" s="163"/>
-      <c r="E144" s="163"/>
-      <c r="F144" s="163"/>
-      <c r="G144" s="163"/>
-      <c r="H144" s="164"/>
-      <c r="I144" s="122" t="s">
-        <v>128</v>
       </c>
       <c r="J144" s="109"/>
       <c r="K144" s="109"/>
@@ -15897,16 +15904,16 @@
     </row>
     <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="40"/>
-      <c r="C145" s="179" t="s">
-        <v>131</v>
-      </c>
-      <c r="D145" s="180"/>
-      <c r="E145" s="180"/>
-      <c r="F145" s="180"/>
-      <c r="G145" s="180"/>
-      <c r="H145" s="181"/>
+      <c r="C145" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="D145" s="146"/>
+      <c r="E145" s="146"/>
+      <c r="F145" s="146"/>
+      <c r="G145" s="146"/>
+      <c r="H145" s="147"/>
       <c r="I145" s="112" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J145" s="113"/>
       <c r="K145" s="113"/>
@@ -16156,17 +16163,16 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C135:H135"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="I139:M139"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="B9:B36"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C15:P16"/>
     <mergeCell ref="C134:H134"/>
     <mergeCell ref="I134:M134"/>
     <mergeCell ref="D17:D27"/>
@@ -16183,16 +16189,17 @@
     <mergeCell ref="D79:D93"/>
     <mergeCell ref="D96:D110"/>
     <mergeCell ref="D113:D127"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="C7:Q7"/>
-    <mergeCell ref="B9:B36"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D13:L13"/>
-    <mergeCell ref="C15:P16"/>
+    <mergeCell ref="I135:M135"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="I139:M139"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C135:H135"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M1" r:id="rId1" display="https://atb.nrel.gov/electricity/2022/utility-scale_battery_storage" xr:uid="{7816EC9A-0454-4087-A6E1-F971C99AA20E}"/>
@@ -17050,7 +17057,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -17145,7 +17152,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>272875</v>
@@ -17358,7 +17365,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -17453,7 +17460,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>253384</v>
@@ -17666,10 +17673,10 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>390.92859792000002</v>
@@ -17761,10 +17768,10 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>363.00560831999996</v>
@@ -17856,7 +17863,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B12">
         <v>0.78500000000000003</v>
@@ -17886,7 +17893,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -18450,7 +18457,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
         <v>43</v>
@@ -18458,7 +18465,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B2" s="36">
         <v>0.2</v>

--- a/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
+++ b/InputData/elec/BCpUC/Battery Cost per Unit Cap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\elec\BCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2023F6E8-4F57-4EF1-831B-D65E2CCCF5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6724F2-1A41-4679-A919-9BC9B9ABD18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="839" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -490,19 +490,10 @@
     <t>We determine this value via calibration against ATB data.</t>
   </si>
   <si>
-    <t>2022 to 2013 costs</t>
-  </si>
-  <si>
     <t>Raw Data (2022 $)</t>
   </si>
   <si>
     <t>Time (Year)</t>
-  </si>
-  <si>
-    <t>Battery Energy Cost per Unit Capacity : MostRecentRun</t>
-  </si>
-  <si>
-    <t>Battery Power Cost per Unit Capacity : MostRecentRun</t>
   </si>
   <si>
     <t>2021 (from 2023 ATB)</t>
@@ -515,6 +506,15 @@
   </si>
   <si>
     <t xml:space="preserve">All values are given in 2022 U.S. dollars except for 2021 values from ATB 2023 </t>
+  </si>
+  <si>
+    <t>Battery Energy Cost per Unit Capacity : test</t>
+  </si>
+  <si>
+    <t>2022 to 2012 costs</t>
+  </si>
+  <si>
+    <t>Battery Power Cost per Unit Capacity : test</t>
   </si>
 </sst>
 </file>
@@ -1971,69 +1971,15 @@
     <xf numFmtId="5" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="14" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -2080,6 +2026,60 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2227,85 +2227,85 @@
                   <c:v>303546</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>275720</c:v>
+                  <c:v>274986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>254008</c:v>
+                  <c:v>253296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>237399</c:v>
+                  <c:v>236734</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>223663</c:v>
+                  <c:v>223030</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>212018</c:v>
+                  <c:v>211554</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>202332</c:v>
+                  <c:v>201954</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>194107</c:v>
+                  <c:v>193764</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>186872</c:v>
+                  <c:v>186541</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>180500</c:v>
+                  <c:v>180196</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>174745</c:v>
+                  <c:v>174552</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>169959</c:v>
+                  <c:v>169876</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>165780</c:v>
+                  <c:v>165776</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>162166</c:v>
+                  <c:v>162216</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>159002</c:v>
+                  <c:v>159077</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>156172</c:v>
+                  <c:v>156257</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>153632</c:v>
+                  <c:v>153722</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>151363</c:v>
+                  <c:v>151442</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>149361</c:v>
+                  <c:v>149428</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>147535</c:v>
+                  <c:v>147587</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>145853</c:v>
+                  <c:v>145898</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>144309</c:v>
+                  <c:v>144352</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>142883</c:v>
+                  <c:v>142921</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>141583</c:v>
+                  <c:v>141617</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>140367</c:v>
+                  <c:v>140396</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>139237</c:v>
+                  <c:v>139257</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>138175</c:v>
+                  <c:v>138188</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>137182</c:v>
+                  <c:v>137190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4908,19 +4908,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:108" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="142" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="165"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="142"/>
       <c r="M1" s="3" t="s">
         <v>68</v>
       </c>
@@ -5050,12 +5050,12 @@
     </row>
     <row r="4" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D4" s="44"/>
-      <c r="L4" s="166" t="s">
+      <c r="L4" s="143" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:108" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L5" s="167"/>
+      <c r="L5" s="144"/>
     </row>
     <row r="6" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H6" s="45"/>
@@ -5087,23 +5087,23 @@
       <c r="B7" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="161" t="s">
+      <c r="C7" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="161"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="161"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="161"/>
-      <c r="P7" s="161"/>
-      <c r="Q7" s="161"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="145"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="145"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
       <c r="R7" s="50"/>
       <c r="S7" s="50"/>
       <c r="T7" s="50"/>
@@ -5121,43 +5121,43 @@
     </row>
     <row r="9" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9"/>
-      <c r="B9" s="168" t="s">
+      <c r="B9" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="169" t="s">
+      <c r="D9" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="170"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="172">
+      <c r="E9" s="148"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="150">
         <v>2022</v>
       </c>
-      <c r="H9" s="173"/>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="174"/>
-      <c r="L9" s="174"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="151"/>
+      <c r="K9" s="152"/>
+      <c r="L9" s="152"/>
     </row>
     <row r="10" spans="1:108" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="168"/>
+      <c r="B10" s="146"/>
       <c r="D10" s="53" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="168"/>
-      <c r="D11" s="175" t="s">
+      <c r="B11" s="146"/>
+      <c r="D11" s="153" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="176"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="154"/>
+      <c r="I11" s="154"/>
+      <c r="J11" s="154"/>
+      <c r="K11" s="154"/>
+      <c r="L11" s="154"/>
       <c r="W11" s="54"/>
       <c r="X11" s="55"/>
       <c r="Y11" s="55"/>
@@ -5165,18 +5165,18 @@
       <c r="AA11" s="55"/>
     </row>
     <row r="12" spans="1:108" s="40" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="168"/>
-      <c r="D12" s="177" t="s">
+      <c r="B12" s="146"/>
+      <c r="D12" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="178"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="178"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="178"/>
-      <c r="J12" s="178"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="179"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="157"/>
       <c r="M12" s="56"/>
       <c r="W12" s="54"/>
       <c r="X12" s="55"/>
@@ -5185,16 +5185,16 @@
       <c r="AA12" s="55"/>
     </row>
     <row r="13" spans="1:108" s="40" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="168"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="181"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="181"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="181"/>
-      <c r="L13" s="182"/>
+      <c r="B13" s="146"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="160"/>
       <c r="W13" s="54"/>
       <c r="X13" s="55"/>
       <c r="Y13" s="55"/>
@@ -5202,49 +5202,49 @@
       <c r="AA13" s="55"/>
     </row>
     <row r="14" spans="1:108" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="168"/>
+      <c r="B14" s="146"/>
     </row>
     <row r="15" spans="1:108" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="168"/>
-      <c r="C15" s="183" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="183"/>
-      <c r="K15" s="183"/>
-      <c r="L15" s="183"/>
-      <c r="M15" s="183"/>
-      <c r="N15" s="183"/>
-      <c r="O15" s="183"/>
-      <c r="P15" s="183"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="161" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="161"/>
+      <c r="E15" s="161"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="161"/>
+      <c r="H15" s="161"/>
+      <c r="I15" s="161"/>
+      <c r="J15" s="161"/>
+      <c r="K15" s="161"/>
+      <c r="L15" s="161"/>
+      <c r="M15" s="161"/>
+      <c r="N15" s="161"/>
+      <c r="O15" s="161"/>
+      <c r="P15" s="161"/>
       <c r="Q15" s="57"/>
     </row>
     <row r="16" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="B16" s="168"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="183"/>
-      <c r="K16" s="183"/>
-      <c r="L16" s="183"/>
-      <c r="M16" s="183"/>
-      <c r="N16" s="183"/>
-      <c r="O16" s="183"/>
-      <c r="P16" s="183"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="161"/>
+      <c r="H16" s="161"/>
+      <c r="I16" s="161"/>
+      <c r="J16" s="161"/>
+      <c r="K16" s="161"/>
+      <c r="L16" s="161"/>
+      <c r="M16" s="161"/>
+      <c r="N16" s="161"/>
+      <c r="O16" s="161"/>
+      <c r="P16" s="161"/>
     </row>
     <row r="17" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="168"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="58"/>
-      <c r="D17" s="158" t="s">
+      <c r="D17" s="168" t="s">
         <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -5252,11 +5252,11 @@
       </c>
     </row>
     <row r="18" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="168"/>
+      <c r="B18" s="146"/>
       <c r="C18" s="58"/>
-      <c r="D18" s="159"/>
+      <c r="D18" s="169"/>
       <c r="F18" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G18" s="1">
         <v>2022</v>
@@ -5347,9 +5347,9 @@
       </c>
     </row>
     <row r="19" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="168"/>
+      <c r="B19" s="146"/>
       <c r="C19" s="58"/>
-      <c r="D19" s="159"/>
+      <c r="D19" s="169"/>
       <c r="E19" t="s">
         <v>80</v>
       </c>
@@ -5445,9 +5445,9 @@
       </c>
     </row>
     <row r="20" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="168"/>
+      <c r="B20" s="146"/>
       <c r="C20" s="58"/>
-      <c r="D20" s="160"/>
+      <c r="D20" s="170"/>
       <c r="E20" t="s">
         <v>81</v>
       </c>
@@ -5543,9 +5543,9 @@
       </c>
     </row>
     <row r="21" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="168"/>
+      <c r="B21" s="146"/>
       <c r="C21" s="58"/>
-      <c r="D21" s="160"/>
+      <c r="D21" s="170"/>
       <c r="E21" t="s">
         <v>82</v>
       </c>
@@ -5641,9 +5641,9 @@
       </c>
     </row>
     <row r="22" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="168"/>
+      <c r="B22" s="146"/>
       <c r="C22" s="58"/>
-      <c r="D22" s="160"/>
+      <c r="D22" s="170"/>
       <c r="F22" s="60"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
@@ -5676,20 +5676,20 @@
       <c r="AI22" s="5"/>
     </row>
     <row r="23" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="168"/>
+      <c r="B23" s="146"/>
       <c r="C23" s="58"/>
-      <c r="D23" s="160"/>
+      <c r="D23" s="170"/>
       <c r="E23" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F23" s="60"/>
     </row>
     <row r="24" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="168"/>
+      <c r="B24" s="146"/>
       <c r="C24" s="58"/>
-      <c r="D24" s="160"/>
+      <c r="D24" s="170"/>
       <c r="F24" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G24" s="1">
         <v>2022</v>
@@ -5780,9 +5780,9 @@
       </c>
     </row>
     <row r="25" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="168"/>
+      <c r="B25" s="146"/>
       <c r="C25" s="58"/>
-      <c r="D25" s="160"/>
+      <c r="D25" s="170"/>
       <c r="E25" t="s">
         <v>80</v>
       </c>
@@ -5878,9 +5878,9 @@
       </c>
     </row>
     <row r="26" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="168"/>
+      <c r="B26" s="146"/>
       <c r="C26" s="58"/>
-      <c r="D26" s="160"/>
+      <c r="D26" s="170"/>
       <c r="E26" t="s">
         <v>81</v>
       </c>
@@ -5976,9 +5976,9 @@
       </c>
     </row>
     <row r="27" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="168"/>
+      <c r="B27" s="146"/>
       <c r="C27" s="58"/>
-      <c r="D27" s="160"/>
+      <c r="D27" s="170"/>
       <c r="E27" t="s">
         <v>82</v>
       </c>
@@ -6074,7 +6074,7 @@
       </c>
     </row>
     <row r="28" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="168"/>
+      <c r="B28" s="146"/>
       <c r="C28" s="58"/>
       <c r="D28" s="58"/>
       <c r="G28" s="5"/>
@@ -6112,7 +6112,7 @@
       <c r="AM28" s="5"/>
     </row>
     <row r="29" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="168"/>
+      <c r="B29" s="146"/>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
       <c r="E29" s="1" t="s">
@@ -6154,7 +6154,7 @@
       <c r="AM29" s="5"/>
     </row>
     <row r="30" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="168"/>
+      <c r="B30" s="146"/>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
       <c r="E30" s="1"/>
@@ -6194,9 +6194,9 @@
       <c r="AM30" s="5"/>
     </row>
     <row r="31" spans="2:39" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="168"/>
+      <c r="B31" s="146"/>
       <c r="C31" s="58"/>
-      <c r="D31" s="159" t="s">
+      <c r="D31" s="169" t="s">
         <v>85</v>
       </c>
       <c r="E31" s="61" t="s">
@@ -6246,9 +6246,9 @@
       <c r="AM31" s="5"/>
     </row>
     <row r="32" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="168"/>
+      <c r="B32" s="146"/>
       <c r="C32" s="58"/>
-      <c r="D32" s="159"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="66" t="s">
         <v>91</v>
       </c>
@@ -6296,9 +6296,9 @@
       <c r="AM32" s="5"/>
     </row>
     <row r="33" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="168"/>
+      <c r="B33" s="146"/>
       <c r="C33" s="58"/>
-      <c r="D33" s="159"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="69" t="s">
         <v>96</v>
       </c>
@@ -6346,9 +6346,9 @@
       <c r="AM33" s="5"/>
     </row>
     <row r="34" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="168"/>
+      <c r="B34" s="146"/>
       <c r="C34" s="58"/>
-      <c r="D34" s="159"/>
+      <c r="D34" s="169"/>
       <c r="E34" s="72" t="s">
         <v>98</v>
       </c>
@@ -6396,9 +6396,9 @@
       <c r="AM34" s="5"/>
     </row>
     <row r="35" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="168"/>
+      <c r="B35" s="146"/>
       <c r="C35" s="58"/>
-      <c r="D35" s="159"/>
+      <c r="D35" s="169"/>
       <c r="E35" s="69" t="s">
         <v>100</v>
       </c>
@@ -6446,9 +6446,9 @@
       <c r="AM35" s="5"/>
     </row>
     <row r="36" spans="2:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="168"/>
+      <c r="B36" s="146"/>
       <c r="C36" s="58"/>
-      <c r="D36" s="159"/>
+      <c r="D36" s="169"/>
       <c r="E36" s="75" t="s">
         <v>102</v>
       </c>
@@ -6535,23 +6535,23 @@
       <c r="AM37" s="5"/>
     </row>
     <row r="38" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C38" s="161" t="s">
+      <c r="C38" s="145" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
-      <c r="P38" s="161"/>
-      <c r="Q38" s="161"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="145"/>
+      <c r="G38" s="145"/>
+      <c r="H38" s="145"/>
+      <c r="I38" s="145"/>
+      <c r="J38" s="145"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="145"/>
+      <c r="M38" s="145"/>
+      <c r="N38" s="145"/>
+      <c r="O38" s="145"/>
+      <c r="P38" s="145"/>
+      <c r="Q38" s="145"/>
       <c r="R38" s="50"/>
       <c r="S38" s="50"/>
       <c r="T38" s="50"/>
@@ -6583,7 +6583,7 @@
     <row r="39" spans="2:74" s="40" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D40" s="53" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="2:74" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
     </row>
     <row r="42" spans="2:74" x14ac:dyDescent="0.25">
       <c r="G42" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H42" s="1">
         <v>2022</v>
@@ -6684,10 +6684,10 @@
       </c>
     </row>
     <row r="43" spans="2:74" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="163" t="s">
+      <c r="B43" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="158" t="s">
+      <c r="D43" s="168" t="s">
         <v>106</v>
       </c>
       <c r="E43" s="79" t="s">
@@ -6789,8 +6789,8 @@
       </c>
     </row>
     <row r="44" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B44" s="163"/>
-      <c r="D44" s="159"/>
+      <c r="B44" s="177"/>
+      <c r="D44" s="169"/>
       <c r="E44" s="82" t="s">
         <v>91</v>
       </c>
@@ -6890,8 +6890,8 @@
       </c>
     </row>
     <row r="45" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B45" s="163"/>
-      <c r="D45" s="159"/>
+      <c r="B45" s="177"/>
+      <c r="D45" s="169"/>
       <c r="E45" s="83" t="s">
         <v>91</v>
       </c>
@@ -6991,8 +6991,8 @@
       </c>
     </row>
     <row r="46" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B46" s="163"/>
-      <c r="D46" s="160"/>
+      <c r="B46" s="177"/>
+      <c r="D46" s="170"/>
       <c r="E46" s="79" t="s">
         <v>96</v>
       </c>
@@ -7125,8 +7125,8 @@
       <c r="BV46" s="5"/>
     </row>
     <row r="47" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B47" s="163"/>
-      <c r="D47" s="160"/>
+      <c r="B47" s="177"/>
+      <c r="D47" s="170"/>
       <c r="E47" s="79" t="s">
         <v>96</v>
       </c>
@@ -7259,8 +7259,8 @@
       <c r="BV47" s="5"/>
     </row>
     <row r="48" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B48" s="163"/>
-      <c r="D48" s="160"/>
+      <c r="B48" s="177"/>
+      <c r="D48" s="170"/>
       <c r="E48" s="79" t="s">
         <v>96</v>
       </c>
@@ -7393,8 +7393,8 @@
       <c r="BV48" s="5"/>
     </row>
     <row r="49" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B49" s="163"/>
-      <c r="D49" s="160"/>
+      <c r="B49" s="177"/>
+      <c r="D49" s="170"/>
       <c r="E49" s="79" t="s">
         <v>98</v>
       </c>
@@ -7527,8 +7527,8 @@
       <c r="BV49" s="5"/>
     </row>
     <row r="50" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B50" s="163"/>
-      <c r="D50" s="160"/>
+      <c r="B50" s="177"/>
+      <c r="D50" s="170"/>
       <c r="E50" s="79" t="s">
         <v>98</v>
       </c>
@@ -7661,8 +7661,8 @@
       <c r="BV50" s="5"/>
     </row>
     <row r="51" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B51" s="163"/>
-      <c r="D51" s="160"/>
+      <c r="B51" s="177"/>
+      <c r="D51" s="170"/>
       <c r="E51" s="79" t="s">
         <v>98</v>
       </c>
@@ -7795,8 +7795,8 @@
       <c r="BV51" s="5"/>
     </row>
     <row r="52" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B52" s="163"/>
-      <c r="D52" s="160"/>
+      <c r="B52" s="177"/>
+      <c r="D52" s="170"/>
       <c r="E52" s="79" t="s">
         <v>100</v>
       </c>
@@ -7929,8 +7929,8 @@
       <c r="BV52" s="5"/>
     </row>
     <row r="53" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B53" s="163"/>
-      <c r="D53" s="160"/>
+      <c r="B53" s="177"/>
+      <c r="D53" s="170"/>
       <c r="E53" s="79" t="s">
         <v>100</v>
       </c>
@@ -8063,8 +8063,8 @@
       <c r="BV53" s="5"/>
     </row>
     <row r="54" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B54" s="163"/>
-      <c r="D54" s="160"/>
+      <c r="B54" s="177"/>
+      <c r="D54" s="170"/>
       <c r="E54" s="79" t="s">
         <v>100</v>
       </c>
@@ -8197,8 +8197,8 @@
       <c r="BV54" s="5"/>
     </row>
     <row r="55" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B55" s="163"/>
-      <c r="D55" s="160"/>
+      <c r="B55" s="177"/>
+      <c r="D55" s="170"/>
       <c r="E55" s="79" t="s">
         <v>102</v>
       </c>
@@ -8331,8 +8331,8 @@
       <c r="BV55" s="5"/>
     </row>
     <row r="56" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B56" s="163"/>
-      <c r="D56" s="160"/>
+      <c r="B56" s="177"/>
+      <c r="D56" s="170"/>
       <c r="E56" s="79" t="s">
         <v>102</v>
       </c>
@@ -8465,8 +8465,8 @@
       <c r="BV56" s="5"/>
     </row>
     <row r="57" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B57" s="163"/>
-      <c r="D57" s="160"/>
+      <c r="B57" s="177"/>
+      <c r="D57" s="170"/>
       <c r="E57" s="79" t="s">
         <v>102</v>
       </c>
@@ -8599,7 +8599,7 @@
       <c r="BV57" s="5"/>
     </row>
     <row r="58" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B58" s="163"/>
+      <c r="B58" s="177"/>
       <c r="D58" s="58"/>
       <c r="E58" s="82"/>
       <c r="F58" s="82"/>
@@ -8668,7 +8668,7 @@
       <c r="BV58" s="5"/>
     </row>
     <row r="59" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B59" s="163"/>
+      <c r="B59" s="177"/>
       <c r="D59" s="58"/>
       <c r="E59" s="82"/>
       <c r="F59" s="82"/>
@@ -8737,7 +8737,7 @@
       <c r="BV59" s="5"/>
     </row>
     <row r="60" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B60" s="163"/>
+      <c r="B60" s="177"/>
       <c r="D60" s="58"/>
       <c r="E60" s="82"/>
       <c r="F60" s="82"/>
@@ -8806,12 +8806,12 @@
       <c r="BV60" s="5"/>
     </row>
     <row r="61" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B61" s="163"/>
+      <c r="B61" s="177"/>
       <c r="D61" s="84"/>
       <c r="E61" s="82"/>
       <c r="F61" s="82"/>
       <c r="G61" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H61" s="1">
         <v>2022</v>
@@ -8902,8 +8902,8 @@
       </c>
     </row>
     <row r="62" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B62" s="163"/>
-      <c r="D62" s="158" t="s">
+      <c r="B62" s="177"/>
+      <c r="D62" s="168" t="s">
         <v>107</v>
       </c>
       <c r="E62" s="79" t="s">
@@ -9005,8 +9005,8 @@
       </c>
     </row>
     <row r="63" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B63" s="163"/>
-      <c r="D63" s="159"/>
+      <c r="B63" s="177"/>
+      <c r="D63" s="169"/>
       <c r="E63" s="82" t="s">
         <v>91</v>
       </c>
@@ -9106,8 +9106,8 @@
       </c>
     </row>
     <row r="64" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B64" s="163"/>
-      <c r="D64" s="159"/>
+      <c r="B64" s="177"/>
+      <c r="D64" s="169"/>
       <c r="E64" s="83" t="s">
         <v>91</v>
       </c>
@@ -9207,8 +9207,8 @@
       </c>
     </row>
     <row r="65" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B65" s="163"/>
-      <c r="D65" s="160"/>
+      <c r="B65" s="177"/>
+      <c r="D65" s="170"/>
       <c r="E65" s="79" t="s">
         <v>96</v>
       </c>
@@ -9308,8 +9308,8 @@
       </c>
     </row>
     <row r="66" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B66" s="163"/>
-      <c r="D66" s="160"/>
+      <c r="B66" s="177"/>
+      <c r="D66" s="170"/>
       <c r="E66" s="79" t="s">
         <v>96</v>
       </c>
@@ -9409,8 +9409,8 @@
       </c>
     </row>
     <row r="67" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B67" s="163"/>
-      <c r="D67" s="160"/>
+      <c r="B67" s="177"/>
+      <c r="D67" s="170"/>
       <c r="E67" s="79" t="s">
         <v>96</v>
       </c>
@@ -9510,8 +9510,8 @@
       </c>
     </row>
     <row r="68" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B68" s="163"/>
-      <c r="D68" s="160"/>
+      <c r="B68" s="177"/>
+      <c r="D68" s="170"/>
       <c r="E68" s="79" t="s">
         <v>98</v>
       </c>
@@ -9611,8 +9611,8 @@
       </c>
     </row>
     <row r="69" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B69" s="163"/>
-      <c r="D69" s="160"/>
+      <c r="B69" s="177"/>
+      <c r="D69" s="170"/>
       <c r="E69" s="79" t="s">
         <v>98</v>
       </c>
@@ -9712,8 +9712,8 @@
       </c>
     </row>
     <row r="70" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B70" s="163"/>
-      <c r="D70" s="160"/>
+      <c r="B70" s="177"/>
+      <c r="D70" s="170"/>
       <c r="E70" s="79" t="s">
         <v>98</v>
       </c>
@@ -9813,8 +9813,8 @@
       </c>
     </row>
     <row r="71" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B71" s="163"/>
-      <c r="D71" s="160"/>
+      <c r="B71" s="177"/>
+      <c r="D71" s="170"/>
       <c r="E71" s="79" t="s">
         <v>100</v>
       </c>
@@ -9947,8 +9947,8 @@
       <c r="BV71" s="5"/>
     </row>
     <row r="72" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B72" s="163"/>
-      <c r="D72" s="160"/>
+      <c r="B72" s="177"/>
+      <c r="D72" s="170"/>
       <c r="E72" s="79" t="s">
         <v>100</v>
       </c>
@@ -10081,8 +10081,8 @@
       <c r="BV72" s="5"/>
     </row>
     <row r="73" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B73" s="163"/>
-      <c r="D73" s="160"/>
+      <c r="B73" s="177"/>
+      <c r="D73" s="170"/>
       <c r="E73" s="79" t="s">
         <v>100</v>
       </c>
@@ -10215,8 +10215,8 @@
       <c r="BV73" s="5"/>
     </row>
     <row r="74" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B74" s="163"/>
-      <c r="D74" s="160"/>
+      <c r="B74" s="177"/>
+      <c r="D74" s="170"/>
       <c r="E74" s="79" t="s">
         <v>102</v>
       </c>
@@ -10349,8 +10349,8 @@
       <c r="BV74" s="5"/>
     </row>
     <row r="75" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B75" s="163"/>
-      <c r="D75" s="160"/>
+      <c r="B75" s="177"/>
+      <c r="D75" s="170"/>
       <c r="E75" s="79" t="s">
         <v>102</v>
       </c>
@@ -10483,8 +10483,8 @@
       <c r="BV75" s="5"/>
     </row>
     <row r="76" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B76" s="163"/>
-      <c r="D76" s="160"/>
+      <c r="B76" s="177"/>
+      <c r="D76" s="170"/>
       <c r="E76" s="79" t="s">
         <v>102</v>
       </c>
@@ -10617,18 +10617,18 @@
       <c r="BV76" s="5"/>
     </row>
     <row r="77" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B77" s="163"/>
+      <c r="B77" s="177"/>
       <c r="D77" s="84"/>
       <c r="E77" s="82"/>
       <c r="F77" s="82"/>
     </row>
     <row r="78" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B78" s="163"/>
+      <c r="B78" s="177"/>
       <c r="D78" s="40"/>
       <c r="E78" s="85"/>
       <c r="F78" s="85"/>
       <c r="G78" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H78" s="1">
         <v>2022</v>
@@ -10719,8 +10719,8 @@
       </c>
     </row>
     <row r="79" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B79" s="163"/>
-      <c r="D79" s="158" t="s">
+      <c r="B79" s="177"/>
+      <c r="D79" s="168" t="s">
         <v>108</v>
       </c>
       <c r="E79" s="79" t="s">
@@ -10822,8 +10822,8 @@
       <c r="AO79" s="1"/>
     </row>
     <row r="80" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B80" s="163"/>
-      <c r="D80" s="159"/>
+      <c r="B80" s="177"/>
+      <c r="D80" s="169"/>
       <c r="E80" s="82" t="s">
         <v>91</v>
       </c>
@@ -10923,8 +10923,8 @@
       <c r="AO80" s="1"/>
     </row>
     <row r="81" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B81" s="163"/>
-      <c r="D81" s="159"/>
+      <c r="B81" s="177"/>
+      <c r="D81" s="169"/>
       <c r="E81" s="83" t="s">
         <v>91</v>
       </c>
@@ -11024,8 +11024,8 @@
       <c r="AO81" s="1"/>
     </row>
     <row r="82" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B82" s="164"/>
-      <c r="D82" s="160"/>
+      <c r="B82" s="178"/>
+      <c r="D82" s="170"/>
       <c r="E82" s="79" t="s">
         <v>96</v>
       </c>
@@ -11124,8 +11124,8 @@
       </c>
     </row>
     <row r="83" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B83" s="164"/>
-      <c r="D83" s="160"/>
+      <c r="B83" s="178"/>
+      <c r="D83" s="170"/>
       <c r="E83" s="79" t="s">
         <v>96</v>
       </c>
@@ -11224,8 +11224,8 @@
       </c>
     </row>
     <row r="84" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B84" s="164"/>
-      <c r="D84" s="160"/>
+      <c r="B84" s="178"/>
+      <c r="D84" s="170"/>
       <c r="E84" s="79" t="s">
         <v>96</v>
       </c>
@@ -11326,8 +11326,8 @@
       <c r="AL84" s="5"/>
     </row>
     <row r="85" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B85" s="164"/>
-      <c r="D85" s="160"/>
+      <c r="B85" s="178"/>
+      <c r="D85" s="170"/>
       <c r="E85" s="79" t="s">
         <v>98</v>
       </c>
@@ -11428,8 +11428,8 @@
       <c r="AL85" s="5"/>
     </row>
     <row r="86" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B86" s="164"/>
-      <c r="D86" s="160"/>
+      <c r="B86" s="178"/>
+      <c r="D86" s="170"/>
       <c r="E86" s="79" t="s">
         <v>98</v>
       </c>
@@ -11530,8 +11530,8 @@
       <c r="AL86" s="5"/>
     </row>
     <row r="87" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B87" s="164"/>
-      <c r="D87" s="160"/>
+      <c r="B87" s="178"/>
+      <c r="D87" s="170"/>
       <c r="E87" s="79" t="s">
         <v>98</v>
       </c>
@@ -11632,8 +11632,8 @@
       <c r="AL87" s="5"/>
     </row>
     <row r="88" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B88" s="164"/>
-      <c r="D88" s="160"/>
+      <c r="B88" s="178"/>
+      <c r="D88" s="170"/>
       <c r="E88" s="79" t="s">
         <v>100</v>
       </c>
@@ -11734,8 +11734,8 @@
       <c r="AL88" s="5"/>
     </row>
     <row r="89" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B89" s="164"/>
-      <c r="D89" s="160"/>
+      <c r="B89" s="178"/>
+      <c r="D89" s="170"/>
       <c r="E89" s="79" t="s">
         <v>100</v>
       </c>
@@ -11836,8 +11836,8 @@
       <c r="AL89" s="5"/>
     </row>
     <row r="90" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B90" s="164"/>
-      <c r="D90" s="160"/>
+      <c r="B90" s="178"/>
+      <c r="D90" s="170"/>
       <c r="E90" s="79" t="s">
         <v>100</v>
       </c>
@@ -11938,8 +11938,8 @@
       <c r="AL90" s="5"/>
     </row>
     <row r="91" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B91" s="164"/>
-      <c r="D91" s="160"/>
+      <c r="B91" s="178"/>
+      <c r="D91" s="170"/>
       <c r="E91" s="79" t="s">
         <v>102</v>
       </c>
@@ -12040,8 +12040,8 @@
       <c r="AL91" s="5"/>
     </row>
     <row r="92" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B92" s="164"/>
-      <c r="D92" s="160"/>
+      <c r="B92" s="178"/>
+      <c r="D92" s="170"/>
       <c r="E92" s="79" t="s">
         <v>102</v>
       </c>
@@ -12142,8 +12142,8 @@
       <c r="AL92" s="5"/>
     </row>
     <row r="93" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B93" s="164"/>
-      <c r="D93" s="160"/>
+      <c r="B93" s="178"/>
+      <c r="D93" s="170"/>
       <c r="E93" s="79" t="s">
         <v>102</v>
       </c>
@@ -12244,12 +12244,12 @@
       <c r="AL93" s="5"/>
     </row>
     <row r="94" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B94" s="164"/>
+      <c r="B94" s="178"/>
     </row>
     <row r="95" spans="2:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="164"/>
+      <c r="B95" s="178"/>
       <c r="G95" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H95" s="1">
         <v>2022</v>
@@ -12340,8 +12340,8 @@
       </c>
     </row>
     <row r="96" spans="2:41" x14ac:dyDescent="0.25">
-      <c r="B96" s="164"/>
-      <c r="D96" s="158" t="s">
+      <c r="B96" s="178"/>
+      <c r="D96" s="168" t="s">
         <v>109</v>
       </c>
       <c r="E96" s="79" t="s">
@@ -12442,8 +12442,8 @@
       </c>
     </row>
     <row r="97" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B97" s="164"/>
-      <c r="D97" s="159"/>
+      <c r="B97" s="178"/>
+      <c r="D97" s="169"/>
       <c r="E97" s="82" t="s">
         <v>91</v>
       </c>
@@ -12542,8 +12542,8 @@
       </c>
     </row>
     <row r="98" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B98" s="164"/>
-      <c r="D98" s="159"/>
+      <c r="B98" s="178"/>
+      <c r="D98" s="169"/>
       <c r="E98" s="83" t="s">
         <v>91</v>
       </c>
@@ -12642,8 +12642,8 @@
       </c>
     </row>
     <row r="99" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B99" s="164"/>
-      <c r="D99" s="160"/>
+      <c r="B99" s="178"/>
+      <c r="D99" s="170"/>
       <c r="E99" s="79" t="s">
         <v>96</v>
       </c>
@@ -12742,8 +12742,8 @@
       </c>
     </row>
     <row r="100" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B100" s="164"/>
-      <c r="D100" s="160"/>
+      <c r="B100" s="178"/>
+      <c r="D100" s="170"/>
       <c r="E100" s="79" t="s">
         <v>96</v>
       </c>
@@ -12842,8 +12842,8 @@
       </c>
     </row>
     <row r="101" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B101" s="164"/>
-      <c r="D101" s="160"/>
+      <c r="B101" s="178"/>
+      <c r="D101" s="170"/>
       <c r="E101" s="79" t="s">
         <v>96</v>
       </c>
@@ -12942,8 +12942,8 @@
       </c>
     </row>
     <row r="102" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B102" s="164"/>
-      <c r="D102" s="160"/>
+      <c r="B102" s="178"/>
+      <c r="D102" s="170"/>
       <c r="E102" s="79" t="s">
         <v>98</v>
       </c>
@@ -13042,8 +13042,8 @@
       </c>
     </row>
     <row r="103" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B103" s="164"/>
-      <c r="D103" s="160"/>
+      <c r="B103" s="178"/>
+      <c r="D103" s="170"/>
       <c r="E103" s="79" t="s">
         <v>98</v>
       </c>
@@ -13142,8 +13142,8 @@
       </c>
     </row>
     <row r="104" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B104" s="164"/>
-      <c r="D104" s="160"/>
+      <c r="B104" s="178"/>
+      <c r="D104" s="170"/>
       <c r="E104" s="79" t="s">
         <v>98</v>
       </c>
@@ -13242,8 +13242,8 @@
       </c>
     </row>
     <row r="105" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B105" s="164"/>
-      <c r="D105" s="160"/>
+      <c r="B105" s="178"/>
+      <c r="D105" s="170"/>
       <c r="E105" s="79" t="s">
         <v>100</v>
       </c>
@@ -13342,8 +13342,8 @@
       </c>
     </row>
     <row r="106" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B106" s="164"/>
-      <c r="D106" s="160"/>
+      <c r="B106" s="178"/>
+      <c r="D106" s="170"/>
       <c r="E106" s="79" t="s">
         <v>100</v>
       </c>
@@ -13442,8 +13442,8 @@
       </c>
     </row>
     <row r="107" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B107" s="164"/>
-      <c r="D107" s="160"/>
+      <c r="B107" s="178"/>
+      <c r="D107" s="170"/>
       <c r="E107" s="79" t="s">
         <v>100</v>
       </c>
@@ -13542,8 +13542,8 @@
       </c>
     </row>
     <row r="108" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B108" s="164"/>
-      <c r="D108" s="160"/>
+      <c r="B108" s="178"/>
+      <c r="D108" s="170"/>
       <c r="E108" s="79" t="s">
         <v>102</v>
       </c>
@@ -13642,8 +13642,8 @@
       </c>
     </row>
     <row r="109" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B109" s="164"/>
-      <c r="D109" s="160"/>
+      <c r="B109" s="178"/>
+      <c r="D109" s="170"/>
       <c r="E109" s="79" t="s">
         <v>102</v>
       </c>
@@ -13742,8 +13742,8 @@
       </c>
     </row>
     <row r="110" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B110" s="164"/>
-      <c r="D110" s="160"/>
+      <c r="B110" s="178"/>
+      <c r="D110" s="170"/>
       <c r="E110" s="79" t="s">
         <v>102</v>
       </c>
@@ -13842,12 +13842,12 @@
       </c>
     </row>
     <row r="111" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B111" s="164"/>
+      <c r="B111" s="178"/>
     </row>
     <row r="112" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B112" s="164"/>
+      <c r="B112" s="178"/>
       <c r="G112" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H112" s="1">
         <v>2022</v>
@@ -13938,8 +13938,8 @@
       </c>
     </row>
     <row r="113" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B113" s="164"/>
-      <c r="D113" s="158" t="s">
+      <c r="B113" s="178"/>
+      <c r="D113" s="168" t="s">
         <v>110</v>
       </c>
       <c r="E113" s="79" t="s">
@@ -14041,8 +14041,8 @@
       </c>
     </row>
     <row r="114" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B114" s="164"/>
-      <c r="D114" s="159"/>
+      <c r="B114" s="178"/>
+      <c r="D114" s="169"/>
       <c r="E114" s="82" t="s">
         <v>91</v>
       </c>
@@ -14142,8 +14142,8 @@
       </c>
     </row>
     <row r="115" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B115" s="164"/>
-      <c r="D115" s="159"/>
+      <c r="B115" s="178"/>
+      <c r="D115" s="169"/>
       <c r="E115" s="83" t="s">
         <v>91</v>
       </c>
@@ -14243,8 +14243,8 @@
       </c>
     </row>
     <row r="116" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B116" s="164"/>
-      <c r="D116" s="160"/>
+      <c r="B116" s="178"/>
+      <c r="D116" s="170"/>
       <c r="E116" s="79" t="s">
         <v>96</v>
       </c>
@@ -14344,8 +14344,8 @@
       </c>
     </row>
     <row r="117" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B117" s="164"/>
-      <c r="D117" s="160"/>
+      <c r="B117" s="178"/>
+      <c r="D117" s="170"/>
       <c r="E117" s="79" t="s">
         <v>96</v>
       </c>
@@ -14445,8 +14445,8 @@
       </c>
     </row>
     <row r="118" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B118" s="164"/>
-      <c r="D118" s="160"/>
+      <c r="B118" s="178"/>
+      <c r="D118" s="170"/>
       <c r="E118" s="79" t="s">
         <v>96</v>
       </c>
@@ -14546,8 +14546,8 @@
       </c>
     </row>
     <row r="119" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B119" s="164"/>
-      <c r="D119" s="160"/>
+      <c r="B119" s="178"/>
+      <c r="D119" s="170"/>
       <c r="E119" s="79" t="s">
         <v>98</v>
       </c>
@@ -14647,8 +14647,8 @@
       </c>
     </row>
     <row r="120" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B120" s="164"/>
-      <c r="D120" s="160"/>
+      <c r="B120" s="178"/>
+      <c r="D120" s="170"/>
       <c r="E120" s="79" t="s">
         <v>98</v>
       </c>
@@ -14748,8 +14748,8 @@
       </c>
     </row>
     <row r="121" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B121" s="164"/>
-      <c r="D121" s="160"/>
+      <c r="B121" s="178"/>
+      <c r="D121" s="170"/>
       <c r="E121" s="79" t="s">
         <v>98</v>
       </c>
@@ -14849,8 +14849,8 @@
       </c>
     </row>
     <row r="122" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B122" s="164"/>
-      <c r="D122" s="160"/>
+      <c r="B122" s="178"/>
+      <c r="D122" s="170"/>
       <c r="E122" s="79" t="s">
         <v>100</v>
       </c>
@@ -14950,8 +14950,8 @@
       </c>
     </row>
     <row r="123" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B123" s="164"/>
-      <c r="D123" s="160"/>
+      <c r="B123" s="178"/>
+      <c r="D123" s="170"/>
       <c r="E123" s="79" t="s">
         <v>100</v>
       </c>
@@ -15051,8 +15051,8 @@
       </c>
     </row>
     <row r="124" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B124" s="164"/>
-      <c r="D124" s="160"/>
+      <c r="B124" s="178"/>
+      <c r="D124" s="170"/>
       <c r="E124" s="79" t="s">
         <v>100</v>
       </c>
@@ -15152,8 +15152,8 @@
       </c>
     </row>
     <row r="125" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B125" s="164"/>
-      <c r="D125" s="160"/>
+      <c r="B125" s="178"/>
+      <c r="D125" s="170"/>
       <c r="E125" s="79" t="s">
         <v>102</v>
       </c>
@@ -15253,8 +15253,8 @@
       </c>
     </row>
     <row r="126" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B126" s="164"/>
-      <c r="D126" s="160"/>
+      <c r="B126" s="178"/>
+      <c r="D126" s="170"/>
       <c r="E126" s="79" t="s">
         <v>102</v>
       </c>
@@ -15354,8 +15354,8 @@
       </c>
     </row>
     <row r="127" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B127" s="164"/>
-      <c r="D127" s="160"/>
+      <c r="B127" s="178"/>
+      <c r="D127" s="170"/>
       <c r="E127" s="79" t="s">
         <v>102</v>
       </c>
@@ -15458,23 +15458,23 @@
       <c r="B128" s="87"/>
     </row>
     <row r="129" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B129" s="162" t="s">
+      <c r="B129" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C129" s="161"/>
-      <c r="D129" s="161"/>
-      <c r="E129" s="161"/>
-      <c r="F129" s="161"/>
-      <c r="G129" s="161"/>
-      <c r="H129" s="161"/>
-      <c r="I129" s="161"/>
-      <c r="J129" s="161"/>
-      <c r="K129" s="161"/>
-      <c r="L129" s="161"/>
-      <c r="M129" s="161"/>
-      <c r="N129" s="161"/>
-      <c r="O129" s="161"/>
-      <c r="P129" s="161"/>
+      <c r="C129" s="145"/>
+      <c r="D129" s="145"/>
+      <c r="E129" s="145"/>
+      <c r="F129" s="145"/>
+      <c r="G129" s="145"/>
+      <c r="H129" s="145"/>
+      <c r="I129" s="145"/>
+      <c r="J129" s="145"/>
+      <c r="K129" s="145"/>
+      <c r="L129" s="145"/>
+      <c r="M129" s="145"/>
+      <c r="N129" s="145"/>
+      <c r="O129" s="145"/>
+      <c r="P129" s="145"/>
       <c r="Q129" s="50"/>
       <c r="R129" s="50"/>
       <c r="S129" s="50"/>
@@ -15509,21 +15509,21 @@
     </row>
     <row r="131" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B131" s="40"/>
-      <c r="C131" s="152" t="s">
+      <c r="C131" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="D131" s="153"/>
-      <c r="E131" s="153"/>
-      <c r="F131" s="153"/>
-      <c r="G131" s="153"/>
-      <c r="H131" s="153"/>
-      <c r="I131" s="155" t="s">
+      <c r="D131" s="173"/>
+      <c r="E131" s="173"/>
+      <c r="F131" s="173"/>
+      <c r="G131" s="173"/>
+      <c r="H131" s="173"/>
+      <c r="I131" s="174" t="s">
         <v>113</v>
       </c>
-      <c r="J131" s="156"/>
-      <c r="K131" s="156"/>
-      <c r="L131" s="156"/>
-      <c r="M131" s="157"/>
+      <c r="J131" s="175"/>
+      <c r="K131" s="175"/>
+      <c r="L131" s="175"/>
+      <c r="M131" s="176"/>
       <c r="N131" s="89" t="s">
         <v>114</v>
       </c>
@@ -15541,14 +15541,14 @@
     </row>
     <row r="132" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="40"/>
-      <c r="C132" s="142" t="s">
+      <c r="C132" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="D132" s="143"/>
-      <c r="E132" s="143"/>
-      <c r="F132" s="143"/>
-      <c r="G132" s="143"/>
-      <c r="H132" s="144"/>
+      <c r="D132" s="163"/>
+      <c r="E132" s="163"/>
+      <c r="F132" s="163"/>
+      <c r="G132" s="163"/>
+      <c r="H132" s="164"/>
       <c r="I132" t="s">
         <v>93</v>
       </c>
@@ -15559,14 +15559,14 @@
     </row>
     <row r="133" spans="2:28" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="40"/>
-      <c r="C133" s="142" t="s">
+      <c r="C133" s="162" t="s">
         <v>117</v>
       </c>
-      <c r="D133" s="143"/>
-      <c r="E133" s="143"/>
-      <c r="F133" s="143"/>
-      <c r="G133" s="143"/>
-      <c r="H133" s="144"/>
+      <c r="D133" s="163"/>
+      <c r="E133" s="163"/>
+      <c r="F133" s="163"/>
+      <c r="G133" s="163"/>
+      <c r="H133" s="164"/>
       <c r="I133" s="100" t="s">
         <v>93</v>
       </c>
@@ -15589,21 +15589,21 @@
     </row>
     <row r="134" spans="2:28" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="40"/>
-      <c r="C134" s="142" t="s">
+      <c r="C134" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="D134" s="143"/>
-      <c r="E134" s="143"/>
-      <c r="F134" s="143"/>
-      <c r="G134" s="143"/>
-      <c r="H134" s="144"/>
-      <c r="I134" s="148" t="s">
+      <c r="D134" s="163"/>
+      <c r="E134" s="163"/>
+      <c r="F134" s="163"/>
+      <c r="G134" s="163"/>
+      <c r="H134" s="164"/>
+      <c r="I134" s="165" t="s">
         <v>119</v>
       </c>
-      <c r="J134" s="149"/>
-      <c r="K134" s="149"/>
-      <c r="L134" s="149"/>
-      <c r="M134" s="150"/>
+      <c r="J134" s="166"/>
+      <c r="K134" s="166"/>
+      <c r="L134" s="166"/>
+      <c r="M134" s="167"/>
       <c r="N134" s="105"/>
       <c r="O134" s="105"/>
       <c r="P134" s="106"/>
@@ -15617,21 +15617,21 @@
     </row>
     <row r="135" spans="2:28" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="40"/>
-      <c r="C135" s="142" t="s">
+      <c r="C135" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="D135" s="143"/>
-      <c r="E135" s="143"/>
-      <c r="F135" s="143"/>
-      <c r="G135" s="143"/>
-      <c r="H135" s="144"/>
-      <c r="I135" s="148" t="s">
+      <c r="D135" s="163"/>
+      <c r="E135" s="163"/>
+      <c r="F135" s="163"/>
+      <c r="G135" s="163"/>
+      <c r="H135" s="164"/>
+      <c r="I135" s="165" t="s">
         <v>121</v>
       </c>
-      <c r="J135" s="149"/>
-      <c r="K135" s="149"/>
-      <c r="L135" s="149"/>
-      <c r="M135" s="150"/>
+      <c r="J135" s="166"/>
+      <c r="K135" s="166"/>
+      <c r="L135" s="166"/>
+      <c r="M135" s="167"/>
       <c r="N135" s="105"/>
       <c r="O135" s="105"/>
       <c r="P135" s="106"/>
@@ -15645,14 +15645,14 @@
     </row>
     <row r="136" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B136" s="40"/>
-      <c r="C136" s="142" t="s">
+      <c r="C136" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="D136" s="143"/>
-      <c r="E136" s="143"/>
-      <c r="F136" s="143"/>
-      <c r="G136" s="143"/>
-      <c r="H136" s="144"/>
+      <c r="D136" s="163"/>
+      <c r="E136" s="163"/>
+      <c r="F136" s="163"/>
+      <c r="G136" s="163"/>
+      <c r="H136" s="164"/>
       <c r="I136" s="108" t="s">
         <v>93</v>
       </c>
@@ -15673,14 +15673,14 @@
     </row>
     <row r="137" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="40"/>
-      <c r="C137" s="145" t="s">
+      <c r="C137" s="179" t="s">
         <v>123</v>
       </c>
-      <c r="D137" s="146"/>
-      <c r="E137" s="146"/>
-      <c r="F137" s="146"/>
-      <c r="G137" s="146"/>
-      <c r="H137" s="147"/>
+      <c r="D137" s="180"/>
+      <c r="E137" s="180"/>
+      <c r="F137" s="180"/>
+      <c r="G137" s="180"/>
+      <c r="H137" s="181"/>
       <c r="I137" s="112" t="s">
         <v>93</v>
       </c>
@@ -15701,12 +15701,12 @@
     </row>
     <row r="138" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="40"/>
-      <c r="C138" s="151"/>
-      <c r="D138" s="151"/>
-      <c r="E138" s="151"/>
-      <c r="F138" s="151"/>
-      <c r="G138" s="151"/>
-      <c r="H138" s="151"/>
+      <c r="C138" s="182"/>
+      <c r="D138" s="182"/>
+      <c r="E138" s="182"/>
+      <c r="F138" s="182"/>
+      <c r="G138" s="182"/>
+      <c r="H138" s="182"/>
       <c r="I138" s="116"/>
       <c r="J138" s="116"/>
       <c r="K138" s="116"/>
@@ -15725,21 +15725,21 @@
     </row>
     <row r="139" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B139" s="40"/>
-      <c r="C139" s="152" t="s">
+      <c r="C139" s="172" t="s">
         <v>124</v>
       </c>
-      <c r="D139" s="153"/>
-      <c r="E139" s="153"/>
-      <c r="F139" s="153"/>
-      <c r="G139" s="153"/>
-      <c r="H139" s="154"/>
-      <c r="I139" s="155" t="s">
+      <c r="D139" s="173"/>
+      <c r="E139" s="173"/>
+      <c r="F139" s="173"/>
+      <c r="G139" s="173"/>
+      <c r="H139" s="183"/>
+      <c r="I139" s="174" t="s">
         <v>113</v>
       </c>
-      <c r="J139" s="156"/>
-      <c r="K139" s="156"/>
-      <c r="L139" s="156"/>
-      <c r="M139" s="157"/>
+      <c r="J139" s="175"/>
+      <c r="K139" s="175"/>
+      <c r="L139" s="175"/>
+      <c r="M139" s="176"/>
       <c r="N139" s="89" t="s">
         <v>114</v>
       </c>
@@ -15757,14 +15757,14 @@
     </row>
     <row r="140" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B140" s="40"/>
-      <c r="C140" s="142" t="s">
+      <c r="C140" s="162" t="s">
         <v>117</v>
       </c>
-      <c r="D140" s="143"/>
-      <c r="E140" s="143"/>
-      <c r="F140" s="143"/>
-      <c r="G140" s="143"/>
-      <c r="H140" s="144"/>
+      <c r="D140" s="163"/>
+      <c r="E140" s="163"/>
+      <c r="F140" s="163"/>
+      <c r="G140" s="163"/>
+      <c r="H140" s="164"/>
       <c r="I140" s="100" t="s">
         <v>93</v>
       </c>
@@ -15848,14 +15848,14 @@
     </row>
     <row r="143" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B143" s="40"/>
-      <c r="C143" s="142" t="s">
+      <c r="C143" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="D143" s="143"/>
-      <c r="E143" s="143"/>
-      <c r="F143" s="143"/>
-      <c r="G143" s="143"/>
-      <c r="H143" s="144"/>
+      <c r="D143" s="163"/>
+      <c r="E143" s="163"/>
+      <c r="F143" s="163"/>
+      <c r="G143" s="163"/>
+      <c r="H143" s="164"/>
       <c r="I143" s="122" t="s">
         <v>125</v>
       </c>
@@ -15876,14 +15876,14 @@
     </row>
     <row r="144" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B144" s="40"/>
-      <c r="C144" s="142" t="s">
+      <c r="C144" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="D144" s="143"/>
-      <c r="E144" s="143"/>
-      <c r="F144" s="143"/>
-      <c r="G144" s="143"/>
-      <c r="H144" s="144"/>
+      <c r="D144" s="163"/>
+      <c r="E144" s="163"/>
+      <c r="F144" s="163"/>
+      <c r="G144" s="163"/>
+      <c r="H144" s="164"/>
       <c r="I144" s="122" t="s">
         <v>125</v>
       </c>
@@ -15904,14 +15904,14 @@
     </row>
     <row r="145" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="40"/>
-      <c r="C145" s="145" t="s">
+      <c r="C145" s="179" t="s">
         <v>128</v>
       </c>
-      <c r="D145" s="146"/>
-      <c r="E145" s="146"/>
-      <c r="F145" s="146"/>
-      <c r="G145" s="146"/>
-      <c r="H145" s="147"/>
+      <c r="D145" s="180"/>
+      <c r="E145" s="180"/>
+      <c r="F145" s="180"/>
+      <c r="G145" s="180"/>
+      <c r="H145" s="181"/>
       <c r="I145" s="112" t="s">
         <v>93</v>
       </c>
@@ -16163,16 +16163,17 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="C7:Q7"/>
-    <mergeCell ref="B9:B36"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="D13:L13"/>
-    <mergeCell ref="C15:P16"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="I135:M135"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="I139:M139"/>
     <mergeCell ref="C134:H134"/>
     <mergeCell ref="I134:M134"/>
     <mergeCell ref="D17:D27"/>
@@ -16189,17 +16190,16 @@
     <mergeCell ref="D79:D93"/>
     <mergeCell ref="D96:D110"/>
     <mergeCell ref="D113:D127"/>
-    <mergeCell ref="I135:M135"/>
-    <mergeCell ref="C136:H136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="I139:M139"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="C7:Q7"/>
+    <mergeCell ref="B9:B36"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C15:P16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M1" r:id="rId1" display="https://atb.nrel.gov/electricity/2022/utility-scale_battery_storage" xr:uid="{7816EC9A-0454-4087-A6E1-F971C99AA20E}"/>
@@ -17057,7 +17057,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B2">
         <v>272875</v>
@@ -17164,94 +17164,94 @@
         <v>303546</v>
       </c>
       <c r="E2">
-        <v>275720</v>
+        <v>274986</v>
       </c>
       <c r="F2">
-        <v>254008</v>
+        <v>253296</v>
       </c>
       <c r="G2">
-        <v>237399</v>
+        <v>236734</v>
       </c>
       <c r="H2">
-        <v>223663</v>
+        <v>223030</v>
       </c>
       <c r="I2">
-        <v>212018</v>
+        <v>211554</v>
       </c>
       <c r="J2">
-        <v>202332</v>
+        <v>201954</v>
       </c>
       <c r="K2">
-        <v>194107</v>
+        <v>193764</v>
       </c>
       <c r="L2">
-        <v>186872</v>
+        <v>186541</v>
       </c>
       <c r="M2">
-        <v>180500</v>
+        <v>180196</v>
       </c>
       <c r="N2">
-        <v>174745</v>
+        <v>174552</v>
       </c>
       <c r="O2">
-        <v>169959</v>
+        <v>169876</v>
       </c>
       <c r="P2">
-        <v>165780</v>
+        <v>165776</v>
       </c>
       <c r="Q2">
-        <v>162166</v>
+        <v>162216</v>
       </c>
       <c r="R2">
-        <v>159002</v>
+        <v>159077</v>
       </c>
       <c r="S2">
-        <v>156172</v>
+        <v>156257</v>
       </c>
       <c r="T2">
-        <v>153632</v>
+        <v>153722</v>
       </c>
       <c r="U2">
-        <v>151363</v>
+        <v>151442</v>
       </c>
       <c r="V2">
-        <v>149361</v>
+        <v>149428</v>
       </c>
       <c r="W2">
-        <v>147535</v>
+        <v>147587</v>
       </c>
       <c r="X2">
-        <v>145853</v>
+        <v>145898</v>
       </c>
       <c r="Y2">
-        <v>144309</v>
+        <v>144352</v>
       </c>
       <c r="Z2">
-        <v>142883</v>
+        <v>142921</v>
       </c>
       <c r="AA2">
-        <v>141583</v>
+        <v>141617</v>
       </c>
       <c r="AB2">
-        <v>140367</v>
+        <v>140396</v>
       </c>
       <c r="AC2">
-        <v>139237</v>
+        <v>139257</v>
       </c>
       <c r="AD2">
-        <v>138175</v>
+        <v>138188</v>
       </c>
       <c r="AE2">
-        <v>137182</v>
+        <v>137190</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C3">
-        <f t="shared" ref="C3:AE3" si="0">C9*$B$12*1000</f>
+        <f>C9*$B$12*1000</f>
         <v>306878.94936720002</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C3:AE3" si="0">D9*$B$12*1000</f>
         <v>303731.66899460001</v>
       </c>
       <c r="E3">
@@ -17365,7 +17365,7 @@
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5">
         <v>2021</v>
@@ -17460,7 +17460,7 @@
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B6">
         <v>253384</v>
@@ -17673,7 +17673,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
@@ -17768,7 +17768,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
         <v>81</v>
@@ -17863,7 +17863,7 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B12">
         <v>0.78500000000000003</v>
